--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -781,7 +781,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -913,7 +913,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3427,7 +3427,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4125,7 +4125,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5227,7 +5227,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6593,7 +6593,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7175,7 +7175,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -8013,7 +8013,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -8145,7 +8145,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8207,7 +8207,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8665,7 +8665,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10333,7 +10333,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10395,7 +10395,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10783,7 +10783,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11295,7 +11295,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11357,7 +11357,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11613,7 +11613,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -12125,7 +12125,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -12187,7 +12187,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -12311,7 +12311,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12373,7 +12373,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -13133,7 +13133,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -13195,7 +13195,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -13319,7 +13319,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13637,7 +13637,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13694,38 +13694,30 @@
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H204" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I204" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="H204" s="5" t="n">
+        <v>9978000</v>
+      </c>
+      <c r="I204" s="5" t="n">
+        <v>18546</v>
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K204" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L204" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K204" s="5" t="n">
+        <v>9978000</v>
+      </c>
+      <c r="L204" s="5" t="n">
+        <v>18546</v>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
@@ -13734,7 +13726,7 @@
       </c>
       <c r="N204" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -13769,7 +13761,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13831,7 +13823,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13893,7 +13885,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13955,7 +13947,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -14149,7 +14141,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -14281,7 +14273,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -14343,7 +14335,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14405,7 +14397,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14467,7 +14459,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14661,7 +14653,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14723,7 +14715,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14785,7 +14777,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14847,7 +14839,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14909,7 +14901,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14971,7 +14963,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -15165,7 +15157,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -15227,7 +15219,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -15289,7 +15281,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -15351,7 +15343,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -15413,7 +15405,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -15475,7 +15467,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15669,7 +15661,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15731,7 +15723,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15793,7 +15785,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15855,7 +15847,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15917,7 +15909,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15979,7 +15971,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -16173,7 +16165,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -16235,7 +16227,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -16297,7 +16289,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -16359,7 +16351,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -16421,7 +16413,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16483,7 +16475,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16677,7 +16669,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16739,7 +16731,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16801,7 +16793,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16863,7 +16855,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16925,7 +16917,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16987,7 +16979,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -17181,7 +17173,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -17243,7 +17235,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -17305,7 +17297,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -17367,7 +17359,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17429,7 +17421,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -17491,7 +17483,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17685,7 +17677,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17747,7 +17739,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17809,7 +17801,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17871,7 +17863,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17933,7 +17925,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17995,7 +17987,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -18189,7 +18181,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -18251,7 +18243,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -18313,7 +18305,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -18375,7 +18367,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -18437,7 +18429,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -18499,7 +18491,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -19323,7 +19315,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -19571,7 +19563,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19843,7 +19835,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -20029,7 +20021,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -20091,7 +20083,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -20363,7 +20355,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -20611,7 +20603,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -20883,7 +20875,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -21131,7 +21123,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -21403,7 +21395,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -21651,7 +21643,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21923,7 +21915,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -22109,7 +22101,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -22171,7 +22163,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -22443,7 +22435,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -22505,7 +22497,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -22629,7 +22621,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -22691,7 +22683,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -22963,7 +22955,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -23025,7 +23017,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -23149,7 +23141,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -23211,7 +23203,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -23413,7 +23405,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -23475,7 +23467,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -23537,7 +23529,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -23661,7 +23653,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -23723,7 +23715,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -23995,7 +23987,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -24057,7 +24049,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -24181,7 +24173,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -24243,7 +24235,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -24515,7 +24507,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -24577,7 +24569,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -24701,7 +24693,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -24763,7 +24755,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -25035,7 +25027,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -25221,7 +25213,7 @@
       </c>
       <c r="G383" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H383" s="5" t="n">
@@ -25283,7 +25275,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -25485,7 +25477,7 @@
       </c>
       <c r="G387" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="H387" s="5" t="n">
@@ -25547,7 +25539,7 @@
       </c>
       <c r="G388" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H388" s="5" t="n">
@@ -25733,7 +25725,7 @@
       </c>
       <c r="G391" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H391" s="5" t="n">
@@ -25795,7 +25787,7 @@
       </c>
       <c r="G392" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H392" s="5" t="n">
@@ -26067,7 +26059,7 @@
       </c>
       <c r="G396" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H396" s="5" t="n">
@@ -26253,7 +26245,7 @@
       </c>
       <c r="G399" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H399" s="5" t="n">
@@ -26315,7 +26307,7 @@
       </c>
       <c r="G400" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H400" s="5" t="n">
@@ -26587,7 +26579,7 @@
       </c>
       <c r="G404" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H404" s="5" t="n">
@@ -26649,7 +26641,7 @@
       </c>
       <c r="G405" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H405" s="5" t="n">
@@ -26773,7 +26765,7 @@
       </c>
       <c r="G407" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H407" s="5" t="n">
@@ -26835,7 +26827,7 @@
       </c>
       <c r="G408" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H408" s="5" t="n">
@@ -27107,7 +27099,7 @@
       </c>
       <c r="G412" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H412" s="5" t="n">
@@ -27169,7 +27161,7 @@
       </c>
       <c r="G413" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H413" s="5" t="n">
@@ -27293,7 +27285,7 @@
       </c>
       <c r="G415" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H415" s="5" t="n">
@@ -27355,7 +27347,7 @@
       </c>
       <c r="G416" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H416" s="5" t="n">
@@ -27557,7 +27549,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -27619,7 +27611,7 @@
       </c>
       <c r="G420" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H420" s="5" t="n">
@@ -27681,7 +27673,7 @@
       </c>
       <c r="G421" s="3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H421" s="5" t="n">
@@ -27805,7 +27797,7 @@
       </c>
       <c r="G423" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H423" s="5" t="n">
@@ -27867,7 +27859,7 @@
       </c>
       <c r="G424" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H424" s="5" t="n">
@@ -28139,7 +28131,7 @@
       </c>
       <c r="G428" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H428" s="5" t="n">
@@ -28201,7 +28193,7 @@
       </c>
       <c r="G429" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H429" s="5" t="n">
@@ -28325,7 +28317,7 @@
       </c>
       <c r="G431" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H431" s="5" t="n">
@@ -28387,7 +28379,7 @@
       </c>
       <c r="G432" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H432" s="5" t="n">
@@ -28659,7 +28651,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -28721,7 +28713,7 @@
       </c>
       <c r="G437" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H437" s="5" t="n">
@@ -28845,7 +28837,7 @@
       </c>
       <c r="G439" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H439" s="5" t="n">
@@ -28907,7 +28899,7 @@
       </c>
       <c r="G440" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H440" s="5" t="n">
@@ -29179,7 +29171,7 @@
       </c>
       <c r="G444" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H444" s="5" t="n">
@@ -29241,7 +29233,7 @@
       </c>
       <c r="G445" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H445" s="5" t="n">
@@ -29303,7 +29295,7 @@
       </c>
       <c r="G446" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H446" s="5" t="n">
@@ -29365,7 +29357,7 @@
       </c>
       <c r="G447" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H447" s="5" t="n">
@@ -29427,7 +29419,7 @@
       </c>
       <c r="G448" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H448" s="5" t="n">
@@ -29699,7 +29691,7 @@
       </c>
       <c r="G452" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H452" s="5" t="n">
@@ -29761,7 +29753,7 @@
       </c>
       <c r="G453" s="3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="H453" s="5" t="n">
@@ -29885,7 +29877,7 @@
       </c>
       <c r="G455" s="3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H455" s="5" t="n">
@@ -29947,7 +29939,7 @@
       </c>
       <c r="G456" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H456" s="5" t="n">
@@ -30219,7 +30211,7 @@
       </c>
       <c r="G460" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H460" s="5" t="n">
@@ -30281,7 +30273,7 @@
       </c>
       <c r="G461" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H461" s="5" t="n">
@@ -30405,7 +30397,7 @@
       </c>
       <c r="G463" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H463" s="5" t="n">
@@ -30467,7 +30459,7 @@
       </c>
       <c r="G464" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="H464" s="5" t="n">
@@ -30739,7 +30731,7 @@
       </c>
       <c r="G468" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H468" s="5" t="n">
@@ -30801,7 +30793,7 @@
       </c>
       <c r="G469" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H469" s="5" t="n">
@@ -30863,7 +30855,7 @@
       </c>
       <c r="G470" s="3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="H470" s="5" t="n">
@@ -30925,7 +30917,7 @@
       </c>
       <c r="G471" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H471" s="5" t="n">
@@ -30987,7 +30979,7 @@
       </c>
       <c r="G472" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H472" s="5" t="n">
@@ -31259,7 +31251,7 @@
       </c>
       <c r="G476" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H476" s="5" t="n">
@@ -31321,7 +31313,7 @@
       </c>
       <c r="G477" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H477" s="5" t="n">
@@ -31383,7 +31375,7 @@
       </c>
       <c r="G478" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H478" s="5" t="n">
@@ -31445,7 +31437,7 @@
       </c>
       <c r="G479" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H479" s="5" t="n">
@@ -31507,7 +31499,7 @@
       </c>
       <c r="G480" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H480" s="5" t="n">
@@ -31779,7 +31771,7 @@
       </c>
       <c r="G484" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H484" s="5" t="n">
@@ -31841,7 +31833,7 @@
       </c>
       <c r="G485" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H485" s="5" t="n">
@@ -31903,7 +31895,7 @@
       </c>
       <c r="G486" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H486" s="5" t="n">
@@ -31965,7 +31957,7 @@
       </c>
       <c r="G487" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H487" s="5" t="n">
@@ -32027,7 +32019,7 @@
       </c>
       <c r="G488" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H488" s="5" t="n">
@@ -32299,7 +32291,7 @@
       </c>
       <c r="G492" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H492" s="5" t="n">
@@ -32361,7 +32353,7 @@
       </c>
       <c r="G493" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H493" s="5" t="n">
@@ -32423,7 +32415,7 @@
       </c>
       <c r="G494" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H494" s="5" t="n">
@@ -32485,7 +32477,7 @@
       </c>
       <c r="G495" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H495" s="5" t="n">
@@ -32547,7 +32539,7 @@
       </c>
       <c r="G496" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H496" s="5" t="n">
@@ -32819,7 +32811,7 @@
       </c>
       <c r="G500" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H500" s="5" t="n">
@@ -32881,7 +32873,7 @@
       </c>
       <c r="G501" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H501" s="5" t="n">
@@ -32943,7 +32935,7 @@
       </c>
       <c r="G502" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H502" s="5" t="n">
@@ -33005,7 +32997,7 @@
       </c>
       <c r="G503" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H503" s="5" t="n">
@@ -33067,7 +33059,7 @@
       </c>
       <c r="G504" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H504" s="5" t="n">
@@ -33269,7 +33261,7 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H507" s="5" t="n">
@@ -33331,7 +33323,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H508" s="5" t="n">
@@ -33393,7 +33385,7 @@
       </c>
       <c r="G509" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H509" s="5" t="n">
@@ -33455,7 +33447,7 @@
       </c>
       <c r="G510" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="H510" s="5" t="n">
@@ -33517,7 +33509,7 @@
       </c>
       <c r="G511" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H511" s="5" t="n">
@@ -33579,7 +33571,7 @@
       </c>
       <c r="G512" s="3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H512" s="5" t="n">
@@ -33851,7 +33843,7 @@
       </c>
       <c r="G516" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H516" s="5" t="n">
@@ -33913,7 +33905,7 @@
       </c>
       <c r="G517" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H517" s="5" t="n">
@@ -33975,7 +33967,7 @@
       </c>
       <c r="G518" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H518" s="5" t="n">
@@ -34037,7 +34029,7 @@
       </c>
       <c r="G519" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H519" s="5" t="n">
@@ -34099,7 +34091,7 @@
       </c>
       <c r="G520" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H520" s="5" t="n">
@@ -34301,7 +34293,7 @@
       </c>
       <c r="G523" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H523" s="5" t="n">
@@ -34363,7 +34355,7 @@
       </c>
       <c r="G524" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H524" s="5" t="n">
@@ -34425,7 +34417,7 @@
       </c>
       <c r="G525" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H525" s="5" t="n">
@@ -34487,7 +34479,7 @@
       </c>
       <c r="G526" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H526" s="5" t="n">
@@ -34549,7 +34541,7 @@
       </c>
       <c r="G527" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H527" s="5" t="n">
@@ -34611,7 +34603,7 @@
       </c>
       <c r="G528" s="3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="H528" s="5" t="n">
@@ -34813,7 +34805,7 @@
       </c>
       <c r="G531" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H531" s="5" t="n">
@@ -34875,7 +34867,7 @@
       </c>
       <c r="G532" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H532" s="5" t="n">
@@ -34937,7 +34929,7 @@
       </c>
       <c r="G533" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H533" s="5" t="n">
@@ -34999,7 +34991,7 @@
       </c>
       <c r="G534" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="H534" s="5" t="n">
@@ -35061,7 +35053,7 @@
       </c>
       <c r="G535" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H535" s="5" t="n">
@@ -35123,7 +35115,7 @@
       </c>
       <c r="G536" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H536" s="5" t="n">
@@ -35325,7 +35317,7 @@
       </c>
       <c r="G539" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H539" s="5" t="n">
@@ -35387,7 +35379,7 @@
       </c>
       <c r="G540" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H540" s="5" t="n">
@@ -35449,7 +35441,7 @@
       </c>
       <c r="G541" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H541" s="5" t="n">
@@ -35511,7 +35503,7 @@
       </c>
       <c r="G542" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H542" s="5" t="n">
@@ -35573,7 +35565,7 @@
       </c>
       <c r="G543" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H543" s="5" t="n">
@@ -35635,7 +35627,7 @@
       </c>
       <c r="G544" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H544" s="5" t="n">
@@ -35837,7 +35829,7 @@
       </c>
       <c r="G547" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H547" s="5" t="n">
@@ -35899,7 +35891,7 @@
       </c>
       <c r="G548" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H548" s="5" t="n">
@@ -35961,7 +35953,7 @@
       </c>
       <c r="G549" s="3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H549" s="5" t="n">
@@ -36023,7 +36015,7 @@
       </c>
       <c r="G550" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="H550" s="5" t="n">
@@ -36085,7 +36077,7 @@
       </c>
       <c r="G551" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H551" s="5" t="n">
@@ -36147,7 +36139,7 @@
       </c>
       <c r="G552" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H552" s="5" t="n">
@@ -36349,7 +36341,7 @@
       </c>
       <c r="G555" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H555" s="5" t="n">
@@ -36411,7 +36403,7 @@
       </c>
       <c r="G556" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H556" s="5" t="n">
@@ -36473,7 +36465,7 @@
       </c>
       <c r="G557" s="3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="H557" s="5" t="n">
@@ -36535,7 +36527,7 @@
       </c>
       <c r="G558" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H558" s="5" t="n">
@@ -36597,7 +36589,7 @@
       </c>
       <c r="G559" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H559" s="5" t="n">
@@ -36659,7 +36651,7 @@
       </c>
       <c r="G560" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H560" s="5" t="n">
@@ -36861,7 +36853,7 @@
       </c>
       <c r="G563" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H563" s="5" t="n">
@@ -36923,7 +36915,7 @@
       </c>
       <c r="G564" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H564" s="5" t="n">
@@ -36985,7 +36977,7 @@
       </c>
       <c r="G565" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H565" s="5" t="n">
@@ -37047,7 +37039,7 @@
       </c>
       <c r="G566" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H566" s="5" t="n">
@@ -37109,7 +37101,7 @@
       </c>
       <c r="G567" s="3" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="H567" s="5" t="n">
@@ -37171,7 +37163,7 @@
       </c>
       <c r="G568" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H568" s="5" t="n">
@@ -37373,7 +37365,7 @@
       </c>
       <c r="G571" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="H571" s="5" t="n">
@@ -37435,7 +37427,7 @@
       </c>
       <c r="G572" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H572" s="5" t="n">
@@ -37497,7 +37489,7 @@
       </c>
       <c r="G573" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H573" s="5" t="n">
@@ -37559,7 +37551,7 @@
       </c>
       <c r="G574" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H574" s="5" t="n">
@@ -37621,7 +37613,7 @@
       </c>
       <c r="G575" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="H575" s="5" t="n">
@@ -37683,7 +37675,7 @@
       </c>
       <c r="G576" s="3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H576" s="5" t="n">
@@ -37885,7 +37877,7 @@
       </c>
       <c r="G579" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H579" s="5" t="n">
@@ -37947,7 +37939,7 @@
       </c>
       <c r="G580" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H580" s="5" t="n">
@@ -38009,7 +38001,7 @@
       </c>
       <c r="G581" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H581" s="5" t="n">
@@ -38071,7 +38063,7 @@
       </c>
       <c r="G582" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H582" s="5" t="n">
@@ -38133,7 +38125,7 @@
       </c>
       <c r="G583" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H583" s="5" t="n">
@@ -38195,7 +38187,7 @@
       </c>
       <c r="G584" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H584" s="5" t="n">
@@ -39002,7 +38994,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -39012,7 +39004,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>190</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -39100,7 +39092,7 @@
           <t>C | 522呎 (2房)
 $940万
 $18,000/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -39116,7 +39108,7 @@
           <t>E | 437呎 (1房)
 $777万
 $17,785/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -39124,7 +39116,7 @@
           <t>F | 418呎 (1房)
 $742万
 $17,751/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -39140,7 +39132,7 @@
           <t>H | 571呎 (2房)
 $1236万
 $21,651/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
     </row>
@@ -39171,7 +39163,7 @@
           <t>C | 522呎 (2房)
 $933万
 $17,874/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -39179,7 +39171,7 @@
           <t>D | 518呎 (2房)
 $943万
 $18,197/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="F6" s="21" t="inlineStr">
@@ -39187,7 +39179,7 @@
           <t>E | 437呎 (1房)
 $772万
 $17,664/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="G6" s="21" t="inlineStr">
@@ -39195,7 +39187,7 @@
           <t>F | 418呎 (1房)
 $737万
 $17,627/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -39211,7 +39203,7 @@
           <t>H | 573呎 (2房)
 $1215万
 $21,208/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -39242,7 +39234,7 @@
           <t>C | 522呎 (2房)
 $926万
 $17,749/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -39258,7 +39250,7 @@
           <t>E | 437呎 (1房)
 $766万
 $17,538/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr">
@@ -39266,7 +39258,7 @@
           <t>F | 418呎 (1房)
 $732万
 $17,505/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -39274,7 +39266,7 @@
           <t>G | 538呎 (2房)
 $1160万
 $21,556/呎
-(26年-07月-19日)</t>
+(26年-07月-20日)</t>
         </is>
       </c>
       <c r="I7" s="21" t="inlineStr">
@@ -39282,7 +39274,7 @@
           <t>H | 573呎 (2房)
 $1190万
 $20,771/呎
-(26年-06月-10日)</t>
+(26年-06月-11日)</t>
         </is>
       </c>
     </row>
@@ -39313,7 +39305,7 @@
           <t>C | 522呎 (2房)
 $923万
 $17,678/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="E8" s="21" t="inlineStr">
@@ -39321,7 +39313,7 @@
           <t>D | 518呎 (2房)
 $932万
 $17,998/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="F8" s="21" t="inlineStr">
@@ -39329,7 +39321,7 @@
           <t>E | 437呎 (1房)
 $764万
 $17,471/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -39337,7 +39329,7 @@
           <t>F | 418呎 (1房)
 $729万
 $17,435/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -39353,7 +39345,7 @@
           <t>H | 573呎 (2房)
 $1172万
 $20,445/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -39384,7 +39376,7 @@
           <t>C | 522呎 (2房)
 $894万
 $17,125/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="E9" s="21" t="inlineStr">
@@ -39392,7 +39384,7 @@
           <t>D | 518呎 (2房)
 $930万
 $17,961/呎
-(26年-07月-10日)</t>
+(26年-07月-11日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -39400,7 +39392,7 @@
           <t>E | 437呎 (1房)
 $762万
 $17,435/呎
-(26年-06月-23日)</t>
+(26年-06月-24日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr">
@@ -39408,7 +39400,7 @@
           <t>F | 418呎 (1房)
 $753万
 $18,014/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -39416,7 +39408,7 @@
           <t>G | 538呎 (2房)
 $1143万
 $21,238/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="I9" s="21" t="inlineStr">
@@ -39424,7 +39416,7 @@
           <t>H | 573呎 (2房)
 $1159万
 $20,222/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -39455,7 +39447,7 @@
           <t>C | 522呎 (2房)
 $916万
 $17,538/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -39463,7 +39455,7 @@
           <t>D | 518呎 (2房)
 $925万
 $17,853/呎
-(26年-07月-11日)</t>
+(26年-07月-12日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -39471,7 +39463,7 @@
           <t>E | 437呎 (1房)
 $757万
 $17,332/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr">
@@ -39479,7 +39471,7 @@
           <t>F | 418呎 (1房)
 $723万
 $17,297/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="H10" s="21" t="inlineStr">
@@ -39487,7 +39479,7 @@
           <t>G | 538呎 (2房)
 $1129万
 $20,987/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="I10" s="21" t="inlineStr">
@@ -39495,7 +39487,7 @@
           <t>H | 573呎 (2房)
 $1145万
 $19,983/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
     </row>
@@ -39526,7 +39518,7 @@
           <t>C | 522呎 (2房)
 $901万
 $17,264/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -39534,7 +39526,7 @@
           <t>D | 518呎 (2房)
 $921万
 $17,782/呎
-(26年-07月-14日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr">
@@ -39542,7 +39534,7 @@
           <t>E | 437呎 (1房)
 $754万
 $17,263/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -39550,7 +39542,7 @@
           <t>F | 418呎 (1房)
 $720万
 $17,227/呎
-(26年-04月-15日)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -39558,7 +39550,7 @@
           <t>G | 538呎 (2房)
 $1120万
 $20,818/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="I11" s="21" t="inlineStr">
@@ -39566,7 +39558,7 @@
           <t>H | 573呎 (2房)
 $1136万
 $19,824/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -39597,7 +39589,7 @@
           <t>C | 522呎 (2房)
 $908万
 $17,398/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -39605,7 +39597,7 @@
           <t>D | 518呎 (2房)
 $918万
 $17,712/呎
-(26年-07月-17日)</t>
+(26年-07月-18日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">
@@ -39613,7 +39605,7 @@
           <t>E | 437呎 (1房)
 $751万
 $17,192/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr">
@@ -39621,7 +39613,7 @@
           <t>F | 418呎 (1房)
 $717万
 $17,158/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -39637,7 +39629,7 @@
           <t>H | 573呎 (2房)
 $1127万
 $19,665/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -39668,7 +39660,7 @@
           <t>C | 522呎 (2房)
 $905万
 $17,330/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -39676,7 +39668,7 @@
           <t>D | 518呎 (2房)
 $914万
 $17,641/呎
-(26年-06月-26日)</t>
+(26年-07月-24日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr">
@@ -39684,7 +39676,7 @@
           <t>E | 437呎 (1房)
 $748万
 $17,124/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr">
@@ -39692,7 +39684,7 @@
           <t>F | 418呎 (1房)
 $714万
 $17,089/呎
-(26年-05月-07日)</t>
+(26年-05月-08日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -39708,7 +39700,7 @@
           <t>H | 573呎 (2房)
 $1118万
 $19,510/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
     </row>
@@ -39739,7 +39731,7 @@
           <t>C | 522呎 (2房)
 $901万
 $17,261/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -39747,7 +39739,7 @@
           <t>D | 518呎 (2房)
 $910万
 $17,571/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr">
@@ -39755,7 +39747,7 @@
           <t>E | 437呎 (1房)
 $745万
 $17,057/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -39763,7 +39755,7 @@
           <t>F | 418呎 (1房)
 $712万
 $17,022/呎
-(26年-05月-05日)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -39779,7 +39771,7 @@
           <t>H | 573呎 (2房)
 $1109万
 $19,354/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
     </row>
@@ -39810,7 +39802,7 @@
           <t>C | 522呎 (2房)
 $897万
 $17,192/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -39818,7 +39810,7 @@
           <t>D | 518呎 (2房)
 $906万
 $17,500/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr">
@@ -39826,7 +39818,7 @@
           <t>E | 437呎 (1房)
 $742万
 $16,989/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr">
@@ -39834,7 +39826,7 @@
           <t>F | 418呎 (1房)
 $709万
 $16,955/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -39850,7 +39842,7 @@
           <t>H | 573呎 (2房)
 $1100万
 $19,201/呎
-(26年-06月-22日)</t>
+(26年-06月-23日)</t>
         </is>
       </c>
     </row>
@@ -39881,7 +39873,7 @@
           <t>C | 522呎 (2房)
 $894万
 $17,125/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -39889,7 +39881,7 @@
           <t>D | 518呎 (2房)
 $903万
 $17,432/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr">
@@ -39897,7 +39889,7 @@
           <t>E | 437呎 (1房)
 $739万
 $16,920/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr">
@@ -39905,7 +39897,7 @@
           <t>F | 418呎 (1房)
 $706万
 $16,885/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -39913,7 +39905,7 @@
           <t>G | 538呎 (2房)
 $1076万
 $20,007/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="I16" s="21" t="inlineStr">
@@ -39921,7 +39913,7 @@
           <t>H | 573呎 (2房)
 $1092万
 $19,049/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
     </row>
@@ -39952,7 +39944,7 @@
           <t>C | 522呎 (2房)
 $890万
 $17,056/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -39960,7 +39952,7 @@
           <t>D | 518呎 (2房)
 $899万
 $17,363/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr">
@@ -39968,7 +39960,7 @@
           <t>E | 437呎 (1房)
 $736万
 $16,854/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G17" s="21" t="inlineStr">
@@ -39976,7 +39968,7 @@
           <t>F | 418呎 (1房)
 $703万
 $16,818/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -39992,7 +39984,7 @@
           <t>H | 573呎 (2房)
 $1083万
 $18,897/呎
-(26年-06月-21日)</t>
+(26年-06月-22日)</t>
         </is>
       </c>
     </row>
@@ -40023,7 +40015,7 @@
           <t>C | 522呎 (2房)
 $888万
 $17,021/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -40039,7 +40031,7 @@
           <t>E | 437呎 (1房)
 $735万
 $16,819/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="G18" s="21" t="inlineStr">
@@ -40047,7 +40039,7 @@
           <t>F | 418呎 (1房)
 $702万
 $16,787/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="H18" s="21" t="inlineStr">
@@ -40055,7 +40047,7 @@
           <t>G | 538呎 (2房)
 $1064万
 $19,783/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="I18" s="21" t="inlineStr">
@@ -40063,7 +40055,7 @@
           <t>H | 573呎 (2房)
 $1079万
 $18,836/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -40094,7 +40086,7 @@
           <t>C | 522呎 (2房)
 $883万
 $16,920/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -40102,7 +40094,7 @@
           <t>D | 518呎 (2房)
 $892万
 $17,224/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr">
@@ -40110,7 +40102,7 @@
           <t>E | 437呎 (1房)
 $731万
 $16,721/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="G19" s="21" t="inlineStr">
@@ -40118,7 +40110,7 @@
           <t>F | 418呎 (1房)
 $698万
 $16,687/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -40134,7 +40126,7 @@
           <t>H | 573呎 (2房)
 $1069万
 $18,654/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -40165,7 +40157,7 @@
           <t>C | 522呎 (2房)
 $880万
 $16,852/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -40173,7 +40165,7 @@
           <t>D | 518呎 (2房)
 $889万
 $17,156/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr">
@@ -40181,7 +40173,7 @@
           <t>E | 437呎 (1房)
 $728万
 $16,652/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -40189,7 +40181,7 @@
           <t>F | 418呎 (1房)
 $719万
 $17,206/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -40205,7 +40197,7 @@
           <t>H | 573呎 (2房)
 $1064万
 $18,562/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -40236,7 +40228,7 @@
           <t>C | 522呎 (2房)
 $876万
 $16,785/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -40244,7 +40236,7 @@
           <t>D | 518呎 (2房)
 $885万
 $17,087/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr">
@@ -40252,7 +40244,7 @@
           <t>E | 437呎 (1房)
 $725万
 $16,586/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -40260,7 +40252,7 @@
           <t>F | 418呎 (1房)
 $692万
 $16,553/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -40276,7 +40268,7 @@
           <t>H | 573呎 (2房)
 $1027万
 $17,925/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -40307,7 +40299,7 @@
           <t>C | 522呎 (2房)
 $873万
 $16,718/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -40315,7 +40307,7 @@
           <t>D | 518呎 (2房)
 $882万
 $17,019/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr">
@@ -40323,7 +40315,7 @@
           <t>E | 437呎 (1房)
 $722万
 $16,519/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -40331,7 +40323,7 @@
           <t>F | 418呎 (1房)
 $689万
 $16,488/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -40347,7 +40339,7 @@
           <t>H | 573呎 (2房)
 $1053万
 $18,379/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -40378,7 +40370,7 @@
           <t>C | 522呎 (2房)
 $869万
 $16,651/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -40386,7 +40378,7 @@
           <t>D | 518呎 (2房)
 $878万
 $16,952/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr">
@@ -40394,7 +40386,7 @@
           <t>E | 437呎 (1房)
 $719万
 $16,455/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="G23" s="21" t="inlineStr">
@@ -40402,7 +40394,7 @@
           <t>F | 418呎 (1房)
 $711万
 $17,002/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -40418,7 +40410,7 @@
           <t>H | 573呎 (2房)
 $1048万
 $18,286/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
     </row>
@@ -40449,7 +40441,7 @@
           <t>C | 522呎 (2房)
 $856万
 $16,389/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -40457,7 +40449,7 @@
           <t>D | 518呎 (2房)
 $875万
 $16,884/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -40465,7 +40457,7 @@
           <t>E | 437呎 (1房)
 $716万
 $16,389/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -40473,7 +40465,7 @@
           <t>F | 418呎 (1房)
 $684万
 $16,356/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -40489,7 +40481,7 @@
           <t>H | 573呎 (2房)
 $1043万
 $18,195/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
@@ -40520,7 +40512,7 @@
           <t>C | 522呎 (2房)
 $883万
 $16,908/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -40528,7 +40520,7 @@
           <t>D | 518呎 (2房)
 $871万
 $16,817/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr">
@@ -40536,7 +40528,7 @@
           <t>E | 437呎 (1房)
 $713万
 $16,323/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -40544,7 +40536,7 @@
           <t>F | 418呎 (1房)
 $681万
 $16,289/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -40560,7 +40552,7 @@
           <t>H | 573呎 (2房)
 $1074万
 $18,743/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -40591,7 +40583,7 @@
           <t>C | 522呎 (2房)
 $859万
 $16,452/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -40599,7 +40591,7 @@
           <t>D | 518呎 (2房)
 $868万
 $16,749/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr">
@@ -40607,7 +40599,7 @@
           <t>E | 437呎 (1房)
 $710万
 $16,259/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">
@@ -40615,7 +40607,7 @@
           <t>F | 418呎 (1房)
 $702万
 $16,799/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -40631,7 +40623,7 @@
           <t>H | 573呎 (2房)
 $1069万
 $18,651/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -40662,7 +40654,7 @@
           <t>C | 522呎 (2房)
 $857万
 $16,420/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -40670,7 +40662,7 @@
           <t>D | 518呎 (2房)
 $866万
 $16,716/呎
-(26年-06月-29日)</t>
+(26年-06月-30日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -40678,7 +40670,7 @@
           <t>E | 437呎 (1房)
 $709万
 $16,227/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -40686,7 +40678,7 @@
           <t>F | 418呎 (1房)
 $677万
 $16,194/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -40694,7 +40686,7 @@
           <t>G | 538呎 (2房)
 $1015万
 $18,872/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -40702,7 +40694,7 @@
           <t>H | 573呎 (2房)
 $1030万
 $17,970/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
     </row>
@@ -40733,7 +40725,7 @@
           <t>C | 522呎 (2房)
 $852万
 $16,322/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -40741,7 +40733,7 @@
           <t>D | 518呎 (2房)
 $861万
 $16,616/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -40749,7 +40741,7 @@
           <t>E | 437呎 (1房)
 $705万
 $16,128/呎
-(26年-03月-19日)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -40757,7 +40749,7 @@
           <t>F | 418呎 (1房)
 $673万
 $16,098/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -40765,7 +40757,7 @@
           <t>G | 538呎 (2房)
 $1008万
 $18,732/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="I28" s="21" t="inlineStr">
@@ -40773,7 +40765,7 @@
           <t>H | 573呎 (2房)
 $1022万
 $17,836/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
     </row>
@@ -40804,7 +40796,7 @@
           <t>C | 522呎 (2房)
 $849万
 $16,257/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -40812,7 +40804,7 @@
           <t>D | 518呎 (2房)
 $857万
 $16,550/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -40820,7 +40812,7 @@
           <t>E | 437呎 (1房)
 $702万
 $16,064/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -40828,7 +40820,7 @@
           <t>F | 418呎 (1房)
 $670万
 $16,033/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -40836,7 +40828,7 @@
           <t>G | 538呎 (2房)
 $1003万
 $18,638/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="I29" s="21" t="inlineStr">
@@ -40844,7 +40836,7 @@
           <t>H | 573呎 (2房)
 $1017万
 $17,747/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -40875,7 +40867,7 @@
           <t>C | 522呎 (2房)
 $845万
 $16,192/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -40883,7 +40875,7 @@
           <t>D | 518呎 (2房)
 $854万
 $16,485/呎
-(26年-07月-01日)</t>
+(26年-07月-02日)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -40891,7 +40883,7 @@
           <t>E | 437呎 (1房)
 $699万
 $16,000/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -40899,10 +40891,81 @@
           <t>F | 418呎 (1房)
 $668万
 $15,969/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="H30" s="22" t="inlineStr">
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$998万
+$18,546/呎
+(26年-07月-29日)</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1012万
+$17,658/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+$2107万
+$23,437/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D31" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$842万
+$16,128/呎
+(25年-10月-09日)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$850万
+$16,419/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$696万
+$15,938/呎
+(26年-01月-22日)</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$665万
+$15,907/呎
+(25年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -40910,22 +40973,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I30" s="21" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1012万
-$17,658/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
+$1007万
+$17,571/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40933,70 +40996,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2107万
-$23,437/呎
+$2096万
+$23,320/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$842万
-$16,128/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="E31" s="21" t="inlineStr">
+$838万
+$16,063/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$850万
-$16,419/呎
+$847万
+$16,353/呎
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$696万
-$15,938/呎
-(26年-01月-21日)</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
+$694万
+$15,874/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$665万
-$15,907/呎
-(25年-10月-07日)</t>
-        </is>
-      </c>
-      <c r="H31" s="22" t="inlineStr">
+$686万
+$16,402/呎
+(25年-10月-23日)</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I31" s="21" t="inlineStr">
+$988万
+$18,362/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1007万
-$17,571/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
+$1002万
+$17,483/呎
+(26年-04月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -41004,70 +41067,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2096万
-$23,320/呎
+$2086万
+$23,205/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$838万
-$16,063/呎
-(25年-09月-25日)</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
+$835万
+$15,992/呎
+(26年-01月-21日)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$847万
-$16,353/呎
-(26年-06月-28日)</t>
-        </is>
-      </c>
-      <c r="F32" s="21" t="inlineStr">
+$843万
+$16,280/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$694万
-$15,874/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="G32" s="21" t="inlineStr">
+$690万
+$15,801/呎
+(26年-02月-27日)</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$686万
-$16,402/呎
-(25年-10月-22日)</t>
-        </is>
-      </c>
-      <c r="H32" s="21" t="inlineStr">
+$659万
+$15,773/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$988万
-$18,362/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="I32" s="21" t="inlineStr">
+$983万
+$18,270/呎
+(26年-07月-12日)</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1002万
-$17,483/呎
-(26年-04月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="inlineStr">
+$997万
+$17,396/呎
+(26年-04月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -41075,70 +41138,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2086万
-$23,205/呎
+$2076万
+$23,089/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$835万
-$15,992/呎
-(26年-01月-20日)</t>
-        </is>
-      </c>
-      <c r="E33" s="21" t="inlineStr">
+$831万
+$15,920/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$843万
-$16,280/呎
-(26年-06月-28日)</t>
-        </is>
-      </c>
-      <c r="F33" s="21" t="inlineStr">
+$840万
+$16,207/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$690万
-$15,801/呎
-(26年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="G33" s="21" t="inlineStr">
+$688万
+$15,732/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$659万
-$15,773/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="H33" s="21" t="inlineStr">
+$656万
+$15,701/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$983万
-$18,270/呎
-(26年-07月-11日)</t>
-        </is>
-      </c>
-      <c r="I33" s="21" t="inlineStr">
+$978万
+$18,180/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$997万
-$17,396/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="58" customHeight="1">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B34" s="20" t="inlineStr">
+$992万
+$17,311/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -41146,70 +41209,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2076万
-$23,089/呎
+$2065万
+$22,974/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$831万
-$15,920/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
+$827万
+$15,841/呎
+(26年-01月-05日)</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$840万
-$16,207/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="F34" s="21" t="inlineStr">
+$835万
+$16,125/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$688万
-$15,732/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="G34" s="21" t="inlineStr">
+$684万
+$15,654/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$656万
-$15,701/呎
-(25年-09月-28日)</t>
-        </is>
-      </c>
-      <c r="H34" s="21" t="inlineStr">
+$653万
+$15,624/呎
+(25年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$978万
-$18,180/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="I34" s="21" t="inlineStr">
+$973万
+$18,089/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$992万
-$17,311/呎
-(25年-09月-28日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="inlineStr">
+$987万
+$17,223/呎
+(26年-03月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -41217,70 +41280,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2065万
-$22,974/呎
+$2060万
+$22,917/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D35" s="21" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$827万
-$15,841/呎
-(26年-01月-04日)</t>
-        </is>
-      </c>
-      <c r="E35" s="21" t="inlineStr">
+$815万
+$15,615/呎
+(26年-02月-23日)</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$835万
-$16,125/呎
+$833万
+$16,087/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$682万
+$15,616/呎
+(26年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$674万
+$16,132/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="H36" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$971万
+$18,045/呎
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="F35" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$684万
-$15,654/呎
-(26年-04月-01日)</t>
-        </is>
-      </c>
-      <c r="G35" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$653万
-$15,624/呎
-(25年-10月-05日)</t>
-        </is>
-      </c>
-      <c r="H35" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
+      <c r="I36" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
 $973万
-$18,089/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="I35" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$987万
-$17,223/呎
-(26年-03月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="inlineStr">
+$16,979/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -41288,70 +41351,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C37" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2060万
-$22,917/呎
+$2045万
+$22,746/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$815万
-$15,615/呎
-(26年-02月-22日)</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="inlineStr">
+$819万
+$15,684/呎
+(26年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$833万
-$16,087/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="F36" s="21" t="inlineStr">
+$827万
+$15,967/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$682万
-$15,616/呎
-(26年-03月-31日)</t>
-        </is>
-      </c>
-      <c r="G36" s="21" t="inlineStr">
+$677万
+$15,499/呎
+(26年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$674万
-$16,132/呎
-(25年-09月-25日)</t>
-        </is>
-      </c>
-      <c r="H36" s="21" t="inlineStr">
+$639万
+$15,285/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$971万
-$18,045/呎
-(26年-07月-01日)</t>
-        </is>
-      </c>
-      <c r="I36" s="21" t="inlineStr">
+$964万
+$17,911/呎
+(26年-07月-12日)</t>
+        </is>
+      </c>
+      <c r="I37" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$973万
-$16,979/呎
-(26年-04月-14日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B37" s="20" t="inlineStr">
+$966万
+$16,853/呎
+(26年-04月-16日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -41359,70 +41422,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C38" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2045万
-$22,746/呎
+$2035万
+$22,633/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D37" s="21" t="inlineStr">
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$819万
-$15,684/呎
-(26年-02月-25日)</t>
-        </is>
-      </c>
-      <c r="E37" s="21" t="inlineStr">
+$805万
+$15,423/呎
+(26年-02月-27日)</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$827万
-$15,967/呎
+$823万
+$15,888/呎
 (26年-06月-29日)</t>
         </is>
       </c>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="F38" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$677万
-$15,499/呎
-(26年-04月-07日)</t>
-        </is>
-      </c>
-      <c r="G37" s="21" t="inlineStr">
+$674万
+$15,421/呎
+(26年-04月-10日)</t>
+        </is>
+      </c>
+      <c r="G38" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$639万
-$15,285/呎
-(25年-10月-01日)</t>
-        </is>
-      </c>
-      <c r="H37" s="21" t="inlineStr">
+$643万
+$15,392/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H38" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$964万
-$17,911/呎
-(26年-07月-11日)</t>
-        </is>
-      </c>
-      <c r="I37" s="21" t="inlineStr">
+$959万
+$17,820/呎
+(26年-07月-12日)</t>
+        </is>
+      </c>
+      <c r="I38" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$966万
-$16,853/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="58" customHeight="1">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
+$972万
+$16,967/呎
+(26年-04月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -41430,77 +41493,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2035万
-$22,633/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$805万
-$15,423/呎
-(26年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="E38" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$823万
-$15,888/呎
-(26年-06月-28日)</t>
-        </is>
-      </c>
-      <c r="F38" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$674万
-$15,421/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="G38" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$643万
-$15,392/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="H38" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$959万
-$17,820/呎
-(26年-07月-11日)</t>
-        </is>
-      </c>
-      <c r="I38" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$972万
-$16,967/呎
-(26年-04月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
@@ -41514,7 +41506,7 @@
           <t>C | 522呎 (2房)
 $811万
 $15,529/呎
-(26年-02月-25日)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
@@ -41522,7 +41514,7 @@
           <t>D | 518呎 (2房)
 $819万
 $15,807/呎
-(26年-07月-02日)</t>
+(26年-07月-03日)</t>
         </is>
       </c>
       <c r="F39" s="21" t="inlineStr">
@@ -41530,7 +41522,7 @@
           <t>E | 437呎 (1房)
 $671万
 $15,346/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="G39" s="21" t="inlineStr">
@@ -41538,7 +41530,7 @@
           <t>F | 418呎 (1房)
 $633万
 $15,148/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="H39" s="21" t="inlineStr">
@@ -41546,7 +41538,7 @@
           <t>G | 538呎 (2房)
 $954万
 $17,732/呎
-(26年-07月-17日)</t>
+(26年-07月-18日)</t>
         </is>
       </c>
       <c r="I39" s="21" t="inlineStr">
@@ -41554,7 +41546,7 @@
           <t>H | 573呎 (2房)
 $968万
 $16,885/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
     </row>
@@ -41803,7 +41795,7 @@
           <t>C | 547呎 (2房)
 $1039万
 $18,987/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
@@ -41835,7 +41827,7 @@
           <t>G | 554呎 (2房)
 $1175万
 $21,215/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr">
@@ -41874,7 +41866,7 @@
           <t>C | 547呎 (2房)
 $1023万
 $18,707/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
@@ -41882,7 +41874,7 @@
           <t>D | 538呎 (2房)
 $994万
 $18,485/呎
-(26年-07月-09日)</t>
+(26年-07月-10日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -41906,7 +41898,7 @@
           <t>G | 554呎 (2房)
 $1158万
 $20,903/呎
-(26年-05月-13日)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
@@ -41945,7 +41937,7 @@
           <t>C | 547呎 (2房)
 $1008万
 $18,431/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -41977,7 +41969,7 @@
           <t>G | 554呎 (2房)
 $1141万
 $20,592/呎
-(26年-05月-04日)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
@@ -42016,7 +42008,7 @@
           <t>C | 547呎 (2房)
 $996万
 $18,212/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -42048,7 +42040,7 @@
           <t>G | 554呎 (2房)
 $1127万
 $20,348/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -42087,7 +42079,7 @@
           <t>C | 547呎 (2房)
 $984万
 $17,996/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -42119,7 +42111,7 @@
           <t>G | 554呎 (2房)
 $1114万
 $20,106/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -42158,7 +42150,7 @@
           <t>C | 547呎 (2房)
 $977万
 $17,854/呎
-(26年-04月-21日)</t>
+(26年-04月-22日)</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -42166,7 +42158,7 @@
           <t>D | 538呎 (2房)
 $976万
 $18,139/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -42190,7 +42182,7 @@
           <t>G | 554呎 (2房)
 $1103万
 $19,908/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -42229,7 +42221,7 @@
           <t>C | 547呎 (2房)
 $973万
 $17,782/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -42237,7 +42229,7 @@
           <t>D | 538呎 (2房)
 $955万
 $17,747/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -42253,7 +42245,7 @@
           <t>F | 512呎 (2房)
 $893万
 $17,436/呎
-(26年-05月-28日)</t>
+(26年-05月-29日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr">
@@ -42261,7 +42253,7 @@
           <t>G | 554呎 (2房)
 $1097万
 $19,809/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -42300,7 +42292,7 @@
           <t>C | 547呎 (2房)
 $967万
 $17,676/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
@@ -42308,7 +42300,7 @@
           <t>D | 538呎 (2房)
 $949万
 $17,641/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -42324,7 +42316,7 @@
           <t>F | 512呎 (2房)
 $887万
 $17,330/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="H12" s="21" t="inlineStr">
@@ -42332,7 +42324,7 @@
           <t>G | 554呎 (2房)
 $1084万
 $19,574/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -42371,7 +42363,7 @@
           <t>C | 547呎 (2房)
 $963万
 $17,607/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
@@ -42379,7 +42371,7 @@
           <t>D | 538呎 (2房)
 $945万
 $17,572/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -42395,7 +42387,7 @@
           <t>F | 512呎 (2房)
 $884万
 $17,262/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="H13" s="21" t="inlineStr">
@@ -42403,7 +42395,7 @@
           <t>G | 554呎 (2房)
 $1076万
 $19,419/呎
-(25年-11月-26日)</t>
+(25年-11月-27日)</t>
         </is>
       </c>
       <c r="I13" s="21" t="inlineStr">
@@ -42411,7 +42403,7 @@
           <t>H | 573呎 (2房)
 $1197万
 $20,883/呎
-(26年-07月-06日)</t>
+(26年-07月-28日)</t>
         </is>
       </c>
     </row>
@@ -42442,7 +42434,7 @@
           <t>C | 547呎 (2房)
 $959万
 $17,536/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
@@ -42450,7 +42442,7 @@
           <t>D | 538呎 (2房)
 $942万
 $17,500/呎
-(26年-05月-14日)</t>
+(26年-05月-15日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -42466,7 +42458,7 @@
           <t>F | 512呎 (2房)
 $880万
 $17,193/呎
-(26年-06月-07日)</t>
+(26年-06月-08日)</t>
         </is>
       </c>
       <c r="H14" s="21" t="inlineStr">
@@ -42474,7 +42466,7 @@
           <t>G | 554呎 (2房)
 $1067万
 $19,265/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -42513,7 +42505,7 @@
           <t>C | 547呎 (2房)
 $955万
 $17,466/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E15" s="21" t="inlineStr">
@@ -42521,7 +42513,7 @@
           <t>D | 538呎 (2房)
 $938万
 $17,431/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -42537,7 +42529,7 @@
           <t>F | 512呎 (2房)
 $877万
 $17,125/呎
-(26年-06月-08日)</t>
+(26年-06月-09日)</t>
         </is>
       </c>
       <c r="H15" s="21" t="inlineStr">
@@ -42545,7 +42537,7 @@
           <t>G | 554呎 (2房)
 $1059万
 $19,112/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -42584,7 +42576,7 @@
           <t>C | 547呎 (2房)
 $952万
 $17,397/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="E16" s="21" t="inlineStr">
@@ -42592,7 +42584,7 @@
           <t>D | 538呎 (2房)
 $934万
 $17,362/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -42616,7 +42608,7 @@
           <t>G | 554呎 (2房)
 $1050万
 $18,958/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -42655,7 +42647,7 @@
           <t>C | 547呎 (2房)
 $937万
 $17,122/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
@@ -42663,7 +42655,7 @@
           <t>D | 538呎 (2房)
 $930万
 $17,294/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -42687,7 +42679,7 @@
           <t>G | 554呎 (2房)
 $1042万
 $18,809/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="I17" s="21" t="inlineStr">
@@ -42695,7 +42687,7 @@
           <t>H | 573呎 (2房)
 $1159万
 $20,229/呎
-(26年-07月-06日)</t>
+(26年-07月-28日)</t>
         </is>
       </c>
     </row>
@@ -42726,7 +42718,7 @@
           <t>C | 547呎 (2房)
 $944万
 $17,258/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
@@ -42734,7 +42726,7 @@
           <t>D | 538呎 (2房)
 $927万
 $17,225/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -42758,7 +42750,7 @@
           <t>G | 554呎 (2房)
 $1034万
 $18,661/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -42797,7 +42789,7 @@
           <t>C | 547呎 (2房)
 $940万
 $17,190/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
@@ -42805,7 +42797,7 @@
           <t>D | 538呎 (2房)
 $923万
 $17,154/呎
-(26年-05月-12日)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -42821,7 +42813,7 @@
           <t>F | 512呎 (2房)
 $880万
 $17,191/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="H19" s="21" t="inlineStr">
@@ -42829,7 +42821,7 @@
           <t>G | 554呎 (2房)
 $1026万
 $18,511/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -42868,7 +42860,7 @@
           <t>C | 547呎 (2房)
 $938万
 $17,155/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
@@ -42876,7 +42868,7 @@
           <t>D | 538呎 (2房)
 $921万
 $17,121/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -42892,7 +42884,7 @@
           <t>F | 512呎 (2房)
 $878万
 $17,156/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="H20" s="21" t="inlineStr">
@@ -42900,7 +42892,7 @@
           <t>G | 554呎 (2房)
 $1022万
 $18,451/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -42939,7 +42931,7 @@
           <t>C | 547呎 (2房)
 $933万
 $17,053/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
@@ -42947,7 +42939,7 @@
           <t>D | 538呎 (2房)
 $905万
 $16,818/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -42963,7 +42955,7 @@
           <t>F | 512呎 (2房)
 $856万
 $16,719/呎
-(26年-05月-31日)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="H21" s="21" t="inlineStr">
@@ -42971,7 +42963,7 @@
           <t>G | 554呎 (2房)
 $1012万
 $18,274/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -42979,7 +42971,7 @@
           <t>H | 573呎 (2房)
 $1126万
 $19,653/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -43010,7 +43002,7 @@
           <t>C | 547呎 (2房)
 $902万
 $16,484/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
@@ -43018,7 +43010,7 @@
           <t>D | 538呎 (2房)
 $912万
 $16,952/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -43034,7 +43026,7 @@
           <t>F | 512呎 (2房)
 $853万
 $16,652/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="H22" s="21" t="inlineStr">
@@ -43042,7 +43034,7 @@
           <t>G | 554呎 (2房)
 $996万
 $17,969/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -43081,7 +43073,7 @@
           <t>C | 547呎 (2房)
 $914万
 $16,718/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
@@ -43089,7 +43081,7 @@
           <t>D | 538呎 (2房)
 $908万
 $16,885/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -43105,7 +43097,7 @@
           <t>F | 512呎 (2房)
 $849万
 $16,586/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="H23" s="21" t="inlineStr">
@@ -43113,7 +43105,7 @@
           <t>G | 554呎 (2房)
 $1002万
 $18,092/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -43152,7 +43144,7 @@
           <t>C | 547呎 (2房)
 $922万
 $16,850/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
@@ -43160,7 +43152,7 @@
           <t>D | 538呎 (2房)
 $894万
 $16,619/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr">
@@ -43168,7 +43160,7 @@
           <t>E | 537呎 (2房)
 $907万
 $16,885/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="G24" s="21" t="inlineStr">
@@ -43176,7 +43168,7 @@
           <t>F | 512呎 (2房)
 $846万
 $16,520/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="H24" s="21" t="inlineStr">
@@ -43184,7 +43176,7 @@
           <t>G | 554呎 (2房)
 $986万
 $17,791/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -43223,7 +43215,7 @@
           <t>C | 547呎 (2房)
 $918万
 $16,782/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
@@ -43231,7 +43223,7 @@
           <t>D | 538呎 (2房)
 $901万
 $16,751/呎
-(26年-03月-17日)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -43247,7 +43239,7 @@
           <t>F | 512呎 (2房)
 $842万
 $16,453/呎
-(26年-05月-20日)</t>
+(26年-05月-21日)</t>
         </is>
       </c>
       <c r="H25" s="21" t="inlineStr">
@@ -43255,7 +43247,7 @@
           <t>G | 554呎 (2房)
 $992万
 $17,913/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -43294,7 +43286,7 @@
           <t>C | 547呎 (2房)
 $914万
 $16,715/呎
-(26年-04月-09日)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
@@ -43302,7 +43294,7 @@
           <t>D | 538呎 (2房)
 $887万
 $16,487/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -43318,7 +43310,7 @@
           <t>F | 512呎 (2房)
 $839万
 $16,389/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="H26" s="21" t="inlineStr">
@@ -43326,7 +43318,7 @@
           <t>G | 554呎 (2房)
 $987万
 $17,823/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -43365,7 +43357,7 @@
           <t>C | 547呎 (2房)
 $911万
 $16,649/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
@@ -43373,7 +43365,7 @@
           <t>D | 538呎 (2房)
 $894万
 $16,615/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="F27" s="21" t="inlineStr">
@@ -43381,7 +43373,7 @@
           <t>E | 537呎 (2房)
 $878万
 $16,356/呎
-(26年-06月-03日)</t>
+(26年-06月-04日)</t>
         </is>
       </c>
       <c r="G27" s="21" t="inlineStr">
@@ -43389,7 +43381,7 @@
           <t>F | 512呎 (2房)
 $836万
 $16,324/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="H27" s="21" t="inlineStr">
@@ -43397,7 +43389,7 @@
           <t>G | 554呎 (2房)
 $982万
 $17,735/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -43436,7 +43428,7 @@
           <t>C | 547呎 (2房)
 $907万
 $16,581/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
@@ -43444,7 +43436,7 @@
           <t>D | 538呎 (2房)
 $922万
 $17,134/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="F28" s="21" t="inlineStr">
@@ -43452,7 +43444,7 @@
           <t>E | 537呎 (2房)
 $875万
 $16,291/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="G28" s="21" t="inlineStr">
@@ -43460,7 +43452,7 @@
           <t>F | 512呎 (2房)
 $832万
 $16,258/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="H28" s="21" t="inlineStr">
@@ -43468,7 +43460,7 @@
           <t>G | 554呎 (2房)
 $978万
 $17,648/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -43507,7 +43499,7 @@
           <t>C | 547呎 (2房)
 $905万
 $16,550/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E29" s="21" t="inlineStr">
@@ -43515,7 +43507,7 @@
           <t>D | 538呎 (2房)
 $889万
 $16,517/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="F29" s="21" t="inlineStr">
@@ -43523,7 +43515,7 @@
           <t>E | 537呎 (2房)
 $873万
 $16,259/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="G29" s="21" t="inlineStr">
@@ -43531,7 +43523,7 @@
           <t>F | 512呎 (2房)
 $831万
 $16,227/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="H29" s="21" t="inlineStr">
@@ -43539,7 +43531,7 @@
           <t>G | 554呎 (2房)
 $964万
 $17,395/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -43578,7 +43570,7 @@
           <t>C | 547呎 (2房)
 $900万
 $16,452/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
@@ -43586,7 +43578,7 @@
           <t>D | 538呎 (2房)
 $883万
 $16,418/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="F30" s="21" t="inlineStr">
@@ -43594,7 +43586,7 @@
           <t>E | 537呎 (2房)
 $868万
 $16,162/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="G30" s="21" t="inlineStr">
@@ -43602,7 +43594,7 @@
           <t>F | 512呎 (2房)
 $826万
 $16,131/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="H30" s="21" t="inlineStr">
@@ -43610,7 +43602,7 @@
           <t>G | 554呎 (2房)
 $968万
 $17,471/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="I30" s="22" t="inlineStr">
@@ -43649,7 +43641,7 @@
           <t>C | 547呎 (2房)
 $896万
 $16,384/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="E31" s="21" t="inlineStr">
@@ -43657,7 +43649,7 @@
           <t>D | 538呎 (2房)
 $870万
 $16,162/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="F31" s="21" t="inlineStr">
@@ -43665,7 +43657,7 @@
           <t>E | 537呎 (2房)
 $864万
 $16,099/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
       <c r="G31" s="21" t="inlineStr">
@@ -43673,7 +43665,7 @@
           <t>F | 512呎 (2房)
 $822万
 $16,064/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="H31" s="21" t="inlineStr">
@@ -43681,7 +43673,7 @@
           <t>G | 554呎 (2房)
 $963万
 $17,384/呎
-(26年-03月-18日)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
@@ -43720,7 +43712,7 @@
           <t>C | 547呎 (2房)
 $893万
 $16,320/呎
-(26年-05月-17日)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
@@ -43728,7 +43720,7 @@
           <t>D | 538呎 (2房)
 $876万
 $16,288/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="F32" s="21" t="inlineStr">
@@ -43736,7 +43728,7 @@
           <t>E | 537呎 (2房)
 $861万
 $16,034/呎
-(26年-06月-04日)</t>
+(26年-06月-05日)</t>
         </is>
       </c>
       <c r="G32" s="21" t="inlineStr">
@@ -43744,7 +43736,7 @@
           <t>F | 512呎 (2房)
 $819万
 $16,000/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="H32" s="21" t="inlineStr">
@@ -43752,7 +43744,7 @@
           <t>G | 554呎 (2房)
 $992万
 $17,908/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="I32" s="21" t="inlineStr">
@@ -43760,7 +43752,7 @@
           <t>H | 573呎 (2房)
 $1066万
 $18,604/呎
-(26年-07月-12日)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -43791,7 +43783,7 @@
           <t>C | 547呎 (2房)
 $889万
 $16,256/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
@@ -43799,7 +43791,7 @@
           <t>D | 538呎 (2房)
 $873万
 $16,223/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="F33" s="21" t="inlineStr">
@@ -43807,7 +43799,7 @@
           <t>E | 537呎 (2房)
 $858万
 $15,970/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="G33" s="21" t="inlineStr">
@@ -43815,7 +43807,7 @@
           <t>F | 512呎 (2房)
 $816万
 $15,938/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="H33" s="21" t="inlineStr">
@@ -43823,7 +43815,7 @@
           <t>G | 554呎 (2房)
 $954万
 $17,211/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr">
@@ -43862,7 +43854,7 @@
           <t>C | 547呎 (2房)
 $886万
 $16,190/呎
-(26年-04月-28日)</t>
+(26年-04月-29日)</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
@@ -43870,7 +43862,7 @@
           <t>D | 538呎 (2房)
 $869万
 $16,158/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="F34" s="21" t="inlineStr">
@@ -43878,7 +43870,7 @@
           <t>E | 537呎 (2房)
 $854万
 $15,907/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="G34" s="21" t="inlineStr">
@@ -43886,7 +43878,7 @@
           <t>F | 512呎 (2房)
 $813万
 $15,875/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="H34" s="21" t="inlineStr">
@@ -43894,7 +43886,7 @@
           <t>G | 554呎 (2房)
 $949万
 $17,128/呎
-(26年-03月-05日)</t>
+(26年-03月-06日)</t>
         </is>
       </c>
       <c r="I34" s="21" t="inlineStr">
@@ -43902,7 +43894,7 @@
           <t>H | 573呎 (2房)
 $1045万
 $18,237/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -43933,7 +43925,7 @@
           <t>C | 547呎 (2房)
 $882万
 $16,117/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
@@ -43941,7 +43933,7 @@
           <t>D | 538呎 (2房)
 $866万
 $16,087/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="F35" s="21" t="inlineStr">
@@ -43949,7 +43941,7 @@
           <t>E | 537呎 (2房)
 $850万
 $15,834/呎
-(26年-05月-25日)</t>
+(26年-05月-26日)</t>
         </is>
       </c>
       <c r="G35" s="21" t="inlineStr">
@@ -43957,7 +43949,7 @@
           <t>F | 512呎 (2房)
 $809万
 $15,803/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="H35" s="21" t="inlineStr">
@@ -43965,7 +43957,7 @@
           <t>G | 554呎 (2房)
 $944万
 $17,042/呎
-(26年-03月-11日)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="I35" s="21" t="inlineStr">
@@ -43973,7 +43965,7 @@
           <t>H | 573呎 (2房)
 $1040万
 $18,147/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -44004,7 +43996,7 @@
           <t>C | 547呎 (2房)
 $878万
 $16,046/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
@@ -44012,7 +44004,7 @@
           <t>D | 538呎 (2房)
 $862万
 $16,015/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="F36" s="21" t="inlineStr">
@@ -44020,7 +44012,7 @@
           <t>E | 537呎 (2房)
 $846万
 $15,764/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
       <c r="G36" s="21" t="inlineStr">
@@ -44028,7 +44020,7 @@
           <t>F | 512呎 (2房)
 $834万
 $16,287/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="H36" s="21" t="inlineStr">
@@ -44036,7 +44028,7 @@
           <t>G | 554呎 (2房)
 $939万
 $16,957/呎
-(26年-03月-11日)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="I36" s="21" t="inlineStr">
@@ -44044,7 +44036,7 @@
           <t>H | 573呎 (2房)
 $1035万
 $18,056/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -44075,7 +44067,7 @@
           <t>C | 547呎 (2房)
 $873万
 $15,965/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
@@ -44083,7 +44075,7 @@
           <t>D | 538呎 (2房)
 $888万
 $16,498/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="F37" s="21" t="inlineStr">
@@ -44091,7 +44083,7 @@
           <t>E | 537呎 (2房)
 $859万
 $15,998/呎
-(26年-07月-08日)</t>
+(26年-07月-09日)</t>
         </is>
       </c>
       <c r="G37" s="21" t="inlineStr">
@@ -44099,7 +44091,7 @@
           <t>F | 512呎 (2房)
 $802万
 $15,654/呎
-(26年-03月-08日)</t>
+(26年-03月-09日)</t>
         </is>
       </c>
       <c r="H37" s="21" t="inlineStr">
@@ -44107,7 +44099,7 @@
           <t>G | 554呎 (2房)
 $924万
 $16,673/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="I37" s="21" t="inlineStr">
@@ -44115,7 +44107,7 @@
           <t>H | 573呎 (2房)
 $1029万
 $17,965/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -44146,7 +44138,7 @@
           <t>C | 547呎 (2房)
 $872万
 $15,934/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
@@ -44154,7 +44146,7 @@
           <t>D | 538呎 (2房)
 $886万
 $16,463/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="F38" s="21" t="inlineStr">
@@ -44162,7 +44154,7 @@
           <t>E | 537呎 (2房)
 $857万
 $15,966/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="G38" s="21" t="inlineStr">
@@ -44170,7 +44162,7 @@
           <t>F | 512呎 (2房)
 $790万
 $15,438/呎
-(25年-10月-02日)</t>
+(25年-10月-03日)</t>
         </is>
       </c>
       <c r="H38" s="21" t="inlineStr">
@@ -44178,7 +44170,7 @@
           <t>G | 554呎 (2房)
 $932万
 $16,830/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="I38" s="21" t="inlineStr">
@@ -44186,7 +44178,7 @@
           <t>H | 573呎 (2房)
 $1027万
 $17,921/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -44217,7 +44209,7 @@
           <t>C | 547呎 (2房)
 $866万
 $15,839/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E39" s="21" t="inlineStr">
@@ -44225,7 +44217,7 @@
           <t>D | 538呎 (2房)
 $850万
 $15,807/呎
-(26年-03月-10日)</t>
+(26年-03月-11日)</t>
         </is>
       </c>
       <c r="F39" s="21" t="inlineStr">
@@ -44233,7 +44225,7 @@
           <t>E | 537呎 (2房)
 $852万
 $15,872/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
       <c r="G39" s="21" t="inlineStr">
@@ -44241,7 +44233,7 @@
           <t>F | 512呎 (2房)
 $795万
 $15,529/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="H39" s="21" t="inlineStr">
@@ -44249,7 +44241,7 @@
           <t>G | 554呎 (2房)
 $926万
 $16,706/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="I39" s="21" t="inlineStr">
@@ -44257,7 +44249,7 @@
           <t>H | 573呎 (2房)
 $1019万
 $17,787/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
     </row>
@@ -44288,7 +44280,7 @@
           <t>C | 547呎 (2房)
 $862万
 $15,761/呎
-(26年-04月-22日)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E40" s="21" t="inlineStr">
@@ -44296,7 +44288,7 @@
           <t>D | 538呎 (2房)
 $846万
 $15,730/呎
-(26年-03月-05日)</t>
+(26年-03月-06日)</t>
         </is>
       </c>
       <c r="F40" s="21" t="inlineStr">
@@ -44304,7 +44296,7 @@
           <t>E | 537呎 (2房)
 $848万
 $15,791/呎
-(26年-07月-15日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="G40" s="21" t="inlineStr">
@@ -44312,7 +44304,7 @@
           <t>F | 512呎 (2房)
 $791万
 $15,453/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="H40" s="21" t="inlineStr">
@@ -44320,7 +44312,7 @@
           <t>G | 554呎 (2房)
 $921万
 $16,623/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="I40" s="21" t="inlineStr">
@@ -44328,7 +44320,7 @@
           <t>H | 573呎 (2房)
 $1014万
 $17,698/呎
-(26年-07月-06日)</t>
+(26年-07月-07日)</t>
         </is>
       </c>
     </row>
@@ -44359,7 +44351,7 @@
           <t>C | 547呎 (2房)
 $858万
 $15,682/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="E41" s="21" t="inlineStr">
@@ -44367,7 +44359,7 @@
           <t>D | 538呎 (2房)
 $842万
 $15,651/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="F41" s="21" t="inlineStr">
@@ -44375,7 +44367,7 @@
           <t>E | 537呎 (2房)
 $844万
 $15,715/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="G41" s="21" t="inlineStr">
@@ -44383,7 +44375,7 @@
           <t>F | 512呎 (2房)
 $788万
 $15,398/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="H41" s="21" t="inlineStr">
@@ -44391,7 +44383,7 @@
           <t>G | 554呎 (2房)
 $916万
 $16,540/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="I41" s="21" t="inlineStr">
@@ -44399,7 +44391,7 @@
           <t>H | 573呎 (2房)
 $1009万
 $17,611/呎
-(26年-07月-05日)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -33261,14 +33261,14 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="H507" s="5" t="n">
-        <v>10660000</v>
+        <v>1066000</v>
       </c>
       <c r="I507" s="5" t="n">
-        <v>18604</v>
+        <v>1860</v>
       </c>
       <c r="J507" s="3" t="inlineStr">
         <is>
@@ -33276,10 +33276,10 @@
         </is>
       </c>
       <c r="K507" s="5" t="n">
-        <v>10660000</v>
+        <v>1066000</v>
       </c>
       <c r="L507" s="5" t="n">
-        <v>18604</v>
+        <v>1860</v>
       </c>
       <c r="M507" s="3" t="inlineStr">
         <is>
@@ -43750,9 +43750,9 @@
       <c r="I32" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1066万
-$18,604/呎
-(26年-07月-13日)</t>
+$107万
+$1,860/呎
+(26年-07月-31日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -26504,38 +26504,30 @@
       </c>
       <c r="F403" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H403" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I403" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="H403" s="5" t="n">
+        <v>11408000</v>
+      </c>
+      <c r="I403" s="5" t="n">
+        <v>19909</v>
       </c>
       <c r="J403" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K403" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L403" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K403" s="5" t="n">
+        <v>11408000</v>
+      </c>
+      <c r="L403" s="5" t="n">
+        <v>19909</v>
       </c>
       <c r="M403" s="3" t="inlineStr">
         <is>
@@ -26544,7 +26536,7 @@
       </c>
       <c r="N403" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -33261,14 +33253,14 @@
       </c>
       <c r="G507" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H507" s="5" t="n">
-        <v>1066000</v>
+        <v>10660000</v>
       </c>
       <c r="I507" s="5" t="n">
-        <v>1860</v>
+        <v>18604</v>
       </c>
       <c r="J507" s="3" t="inlineStr">
         <is>
@@ -33276,10 +33268,10 @@
         </is>
       </c>
       <c r="K507" s="5" t="n">
-        <v>1066000</v>
+        <v>10660000</v>
       </c>
       <c r="L507" s="5" t="n">
-        <v>1860</v>
+        <v>18604</v>
       </c>
       <c r="M507" s="3" t="inlineStr">
         <is>
@@ -41697,7 +41689,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>57</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -41707,7 +41699,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>164</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -42824,7 +42816,78 @@
 (25年-09月-29日)</t>
         </is>
       </c>
-      <c r="I19" s="22" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1141万
+$19,909/呎
+(26年-07月-31日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$938万
+$17,155/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$921万
+$17,121/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1086万
+$20,223/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$878万
+$17,156/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1022万
+$18,451/呎
+(25年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42833,13 +42896,13 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42847,7 +42910,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42855,47 +42918,118 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$938万
-$17,155/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
+$933万
+$17,053/呎
+(26年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$921万
-$17,121/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="inlineStr">
+$905万
+$16,818/呎
+(26年-03月-09日)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1086万
-$20,223/呎
+$1080万
+$20,102/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G20" s="21" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$878万
-$17,156/呎
+$856万
+$16,719/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1012万
+$18,274/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1126万
+$19,653/呎
 (26年-07月-07日)</t>
         </is>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$902万
+$16,484/呎
+(26年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$912万
+$16,952/呎
+(26年-03月-13日)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1075万
+$20,022/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$853万
+$16,652/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1022万
-$18,451/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
+$996万
+$17,969/呎
+(26年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42904,13 +43038,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42918,7 +43052,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42926,62 +43060,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$933万
-$17,053/呎
-(26年-04月-08日)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
+$914万
+$16,718/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$905万
-$16,818/呎
-(26年-03月-09日)</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="inlineStr">
+$908万
+$16,885/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1080万
-$20,102/呎
+$1071万
+$19,944/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$856万
-$16,719/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="H21" s="21" t="inlineStr">
+$849万
+$16,586/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1012万
-$18,274/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
+$1002万
+$18,092/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1126万
-$19,653/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42989,7 +43123,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42997,47 +43131,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$902万
-$16,484/呎
-(26年-04月-01日)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
+$922万
+$16,850/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$912万
-$16,952/呎
-(26年-03月-13日)</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
+$894万
+$16,619/呎
+(26年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1075万
-$20,022/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
+$907万
+$16,885/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$853万
-$16,652/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
+$846万
+$16,520/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$996万
-$17,969/呎
+$986万
+$17,791/呎
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43046,13 +43180,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43060,7 +43194,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43068,47 +43202,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$914万
-$16,718/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
+$918万
+$16,782/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$908万
-$16,885/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
+$901万
+$16,751/呎
+(26年-03月-18日)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1071万
-$19,944/呎
+$1062万
+$19,784/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$849万
-$16,586/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
+$842万
+$16,453/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1002万
-$18,092/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I23" s="22" t="inlineStr">
+$992万
+$17,913/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43117,13 +43251,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43131,7 +43265,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43139,47 +43273,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$922万
-$16,850/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
+$914万
+$16,715/呎
+(26年-04月-10日)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$894万
-$16,619/呎
-(26年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
+$887万
+$16,487/呎
+(26年-03月-02日)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$907万
-$16,885/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
+$1058万
+$19,706/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$846万
-$16,520/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="H24" s="21" t="inlineStr">
+$839万
+$16,389/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$986万
-$17,791/呎
-(26年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="I24" s="22" t="inlineStr">
+$987万
+$17,823/呎
+(26年-03月-31日)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43188,13 +43322,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43202,7 +43336,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43210,47 +43344,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$918万
-$16,782/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
+$911万
+$16,649/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$901万
-$16,751/呎
-(26年-03月-18日)</t>
-        </is>
-      </c>
-      <c r="F25" s="22" t="inlineStr">
+$894万
+$16,615/呎
+(26年-03月-25日)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1062万
-$19,784/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
+$878万
+$16,356/呎
+(26年-06月-04日)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$842万
-$16,453/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
+$836万
+$16,324/呎
+(26年-03月-25日)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$992万
-$17,913/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="I25" s="22" t="inlineStr">
+$982万
+$17,735/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43259,13 +43393,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43273,7 +43407,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43281,47 +43415,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$914万
-$16,715/呎
-(26年-04月-10日)</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
+$907万
+$16,581/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$887万
-$16,487/呎
-(26年-03月-02日)</t>
-        </is>
-      </c>
-      <c r="F26" s="22" t="inlineStr">
+$922万
+$17,134/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1058万
-$19,706/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="inlineStr">
+$875万
+$16,291/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$839万
-$16,389/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="H26" s="21" t="inlineStr">
+$832万
+$16,258/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$987万
-$17,823/呎
-(26年-03月-31日)</t>
-        </is>
-      </c>
-      <c r="I26" s="22" t="inlineStr">
+$978万
+$17,648/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43330,13 +43464,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43344,7 +43478,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43352,47 +43486,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$911万
-$16,649/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
+$905万
+$16,550/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$894万
-$16,615/呎
-(26年-03月-25日)</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
+$889万
+$16,517/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$878万
-$16,356/呎
-(26年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="G27" s="21" t="inlineStr">
+$873万
+$16,259/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$836万
-$16,324/呎
-(26年-03月-25日)</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="inlineStr">
+$831万
+$16,227/呎
+(25年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$982万
-$17,735/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I27" s="22" t="inlineStr">
+$964万
+$17,395/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43401,13 +43535,13 @@
         </is>
       </c>
     </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43415,7 +43549,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43423,47 +43557,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$907万
-$16,581/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
+$900万
+$16,452/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$922万
-$17,134/呎
+$883万
+$16,418/呎
 (25年-09月-30日)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$875万
-$16,291/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
+$868万
+$16,162/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$832万
-$16,258/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
+$826万
+$16,131/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$978万
-$17,648/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="I28" s="22" t="inlineStr">
+$968万
+$17,471/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43472,13 +43606,13 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43486,7 +43620,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43494,47 +43628,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$905万
-$16,550/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="inlineStr">
+$896万
+$16,384/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$889万
-$16,517/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="F29" s="21" t="inlineStr">
+$870万
+$16,162/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$873万
-$16,259/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="G29" s="21" t="inlineStr">
+$864万
+$16,099/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$831万
-$16,227/呎
-(25年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
+$822万
+$16,064/呎
+(26年-03月-09日)</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$964万
-$17,395/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="I29" s="22" t="inlineStr">
+$963万
+$17,384/呎
+(26年-03月-19日)</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43543,13 +43677,13 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43557,7 +43691,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43565,148 +43699,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$900万
-$16,452/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$883万
-$16,418/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="F30" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$868万
-$16,162/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="G30" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$826万
-$16,131/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$968万
-$17,471/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I30" s="22" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$896万
-$16,384/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="E31" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$870万
-$16,162/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$864万
-$16,099/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$822万
-$16,064/呎
-(26年-03月-09日)</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$963万
-$17,384/呎
-(26年-03月-19日)</t>
-        </is>
-      </c>
-      <c r="I31" s="22" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="D32" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
@@ -43750,9 +43742,9 @@
       <c r="I32" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$107万
-$1,860/呎
-(26年-07月-31日)</t>
+$1066万
+$18,604/呎
+(26年-07月-13日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -1032,34 +1032,34 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
-        <v>11166000</v>
+        <v>9491000</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>21556</v>
+        <v>18322</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>9491100</v>
+        <v>9491000</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>18323</v>
+        <v>18322</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -2064,34 +2064,34 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>11011000</v>
+        <v>9359000</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>21257</v>
+        <v>18068</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>9359350</v>
+        <v>9359000</v>
       </c>
       <c r="L23" s="5" t="n">
         <v>18068</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -4446,38 +4446,30 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>11112000</v>
+      </c>
+      <c r="I60" s="5" t="n">
+        <v>20654</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K60" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L60" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K60" s="5" t="n">
+        <v>11112000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>20654</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -4486,7 +4478,7 @@
       </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -11158,38 +11150,30 @@
       </c>
       <c r="F164" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H164" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I164" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="H164" s="5" t="n">
+        <v>10230000</v>
+      </c>
+      <c r="I164" s="5" t="n">
+        <v>19015</v>
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K164" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L164" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K164" s="5" t="n">
+        <v>10230000</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>19015</v>
       </c>
       <c r="M164" s="3" t="inlineStr">
         <is>
@@ -11198,7 +11182,7 @@
       </c>
       <c r="N164" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -11670,38 +11654,30 @@
       </c>
       <c r="F172" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H172" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I172" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H172" s="5" t="n">
+        <v>10179000</v>
+      </c>
+      <c r="I172" s="5" t="n">
+        <v>18920</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K172" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L172" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K172" s="5" t="n">
+        <v>10179000</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>18920</v>
       </c>
       <c r="M172" s="3" t="inlineStr">
         <is>
@@ -11710,7 +11686,7 @@
       </c>
       <c r="N172" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -14198,38 +14174,30 @@
       </c>
       <c r="F212" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H212" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I212" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H212" s="5" t="n">
+        <v>9928000</v>
+      </c>
+      <c r="I212" s="5" t="n">
+        <v>18454</v>
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K212" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L212" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K212" s="5" t="n">
+        <v>9928000</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>18454</v>
       </c>
       <c r="M212" s="3" t="inlineStr">
         <is>
@@ -14238,7 +14206,7 @@
       </c>
       <c r="N212" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -15219,7 +15187,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -17235,7 +17203,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -17739,7 +17707,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -20021,7 +19989,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -21576,34 +21544,34 @@
       </c>
       <c r="F327" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
-        <v>11527000</v>
+        <v>9798000</v>
       </c>
       <c r="I327" s="5" t="n">
-        <v>21426</v>
+        <v>18212</v>
       </c>
       <c r="J327" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K327" s="5" t="n">
-        <v>9797950</v>
+        <v>9798000</v>
       </c>
       <c r="L327" s="5" t="n">
         <v>18212</v>
       </c>
       <c r="M327" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N327" s="3" t="inlineStr">
@@ -22360,38 +22328,30 @@
       </c>
       <c r="F339" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H339" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I339" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H339" s="5" t="n">
+        <v>12207000</v>
+      </c>
+      <c r="I339" s="5" t="n">
+        <v>21304</v>
       </c>
       <c r="J339" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K339" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L339" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K339" s="5" t="n">
+        <v>12207000</v>
+      </c>
+      <c r="L339" s="5" t="n">
+        <v>21304</v>
       </c>
       <c r="M339" s="3" t="inlineStr">
         <is>
@@ -22400,7 +22360,7 @@
       </c>
       <c r="N339" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -22554,34 +22514,34 @@
       </c>
       <c r="F342" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
-        <v>11258000</v>
+        <v>9569000</v>
       </c>
       <c r="I342" s="5" t="n">
-        <v>20965</v>
+        <v>17819</v>
       </c>
       <c r="J342" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K342" s="5" t="n">
-        <v>9569300</v>
+        <v>9569000</v>
       </c>
       <c r="L342" s="5" t="n">
-        <v>17820</v>
+        <v>17819</v>
       </c>
       <c r="M342" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N342" s="3" t="inlineStr">
@@ -27210,23 +27170,23 @@
       </c>
       <c r="F414" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
-        <v>10860000</v>
+        <v>9231000</v>
       </c>
       <c r="I414" s="5" t="n">
-        <v>20223</v>
+        <v>17190</v>
       </c>
       <c r="J414" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K414" s="5" t="n">
@@ -27237,7 +27197,7 @@
       </c>
       <c r="M414" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N414" s="3" t="inlineStr">
@@ -27541,7 +27501,7 @@
       </c>
       <c r="G419" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H419" s="5" t="n">
@@ -38986,7 +38946,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -38996,7 +38956,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>196</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -39087,12 +39047,12 @@
 (26年-03月-02日)</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$1117万
-$21,556/呎
-(在售)</t>
+$949万
+$18,322/呎
+(26年-08月-07日)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -39229,12 +39189,12 @@
 (26年-02月-24日)</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$1101万
-$21,257/呎
-(在售)</t>
+$936万
+$18,068/呎
+(26年-08月-06日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">
@@ -39313,7 +39273,7 @@
           <t>E | 437呎 (1房)
 $764万
 $17,471/呎
-(26年-07月-07日)</t>
+(26年-08月-03日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr">
@@ -39376,7 +39336,7 @@
           <t>D | 518呎 (2房)
 $930万
 $17,961/呎
-(26年-07月-11日)</t>
+(26年-08月-05日)</t>
         </is>
       </c>
       <c r="F9" s="21" t="inlineStr">
@@ -39447,7 +39407,7 @@
           <t>D | 518呎 (2房)
 $925万
 $17,853/呎
-(26年-07月-12日)</t>
+(26年-08月-05日)</t>
         </is>
       </c>
       <c r="F10" s="21" t="inlineStr">
@@ -39608,7 +39568,78 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="H12" s="22" t="inlineStr">
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1111万
+$20,654/呎
+(26年-08月-09日)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1127万
+$19,665/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$905万
+$17,330/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$914万
+$17,641/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$748万
+$17,124/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$714万
+$17,089/呎
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -39616,22 +39647,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I12" s="21" t="inlineStr">
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1127万
-$19,665/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
+$1118万
+$19,510/呎
+(26年-06月-18日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39639,7 +39670,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39647,39 +39678,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$905万
-$17,330/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+$901万
+$17,261/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$914万
-$17,641/呎
-(26年-07月-24日)</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
+$910万
+$17,571/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$748万
-$17,124/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-      <c r="G13" s="21" t="inlineStr">
+$745万
+$17,057/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$714万
-$17,089/呎
-(26年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="H13" s="22" t="inlineStr">
+$712万
+$17,022/呎
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -39687,22 +39718,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr">
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1118万
-$19,510/呎
+$1109万
+$19,354/呎
 (26年-06月-18日)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39710,7 +39741,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39718,39 +39749,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$901万
-$17,261/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
+$897万
+$17,192/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$910万
-$17,571/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
+$906万
+$17,500/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$745万
-$17,057/呎
+$742万
+$16,989/呎
 (26年-06月-22日)</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$712万
-$17,022/呎
-(26年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="inlineStr">
+$709万
+$16,955/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -39758,22 +39789,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1109万
-$19,354/呎
-(26年-06月-18日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
+$1100万
+$19,201/呎
+(26年-06月-23日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39781,7 +39812,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39789,39 +39820,110 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$897万
-$17,192/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
+$894万
+$17,125/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$906万
-$17,500/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="F15" s="21" t="inlineStr">
+$903万
+$17,432/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$742万
-$16,989/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-      <c r="G15" s="21" t="inlineStr">
+$739万
+$16,920/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$709万
-$16,955/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="H15" s="22" t="inlineStr">
+$706万
+$16,885/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1076万
+$20,007/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1092万
+$19,049/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$890万
+$17,056/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$899万
+$17,363/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$736万
+$16,854/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$703万
+$16,818/呎
+(25年-11月-13日)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -39829,22 +39931,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr">
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1100万
-$19,201/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
+$1083万
+$18,897/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39852,7 +39954,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39860,62 +39962,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$894万
-$17,125/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
+$888万
+$17,021/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$903万
-$17,432/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
+$1056万
+$20,384/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$739万
-$16,920/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
+$735万
+$16,819/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$706万
-$16,885/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
+$702万
+$16,787/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1076万
-$20,007/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="I16" s="21" t="inlineStr">
+$1064万
+$19,783/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1092万
-$19,049/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
+$1079万
+$18,836/呎
+(25年-10月-09日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39923,7 +40025,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39931,39 +40033,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$890万
-$17,056/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
+$883万
+$16,920/呎
+(25年-12月-09日)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$899万
-$17,363/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
+$892万
+$17,224/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$736万
-$16,854/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="G17" s="21" t="inlineStr">
+$731万
+$16,721/呎
+(26年-06月-09日)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$703万
-$16,818/呎
-(25年-11月-13日)</t>
-        </is>
-      </c>
-      <c r="H17" s="22" t="inlineStr">
+$698万
+$16,687/呎
+(25年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -39971,22 +40073,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1083万
-$18,897/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
+$1069万
+$18,654/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39994,7 +40096,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -40002,62 +40104,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$888万
-$17,021/呎
+$880万
+$16,852/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$889万
+$17,156/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$728万
+$16,652/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$719万
+$17,206/呎
 (25年-10月-02日)</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$1056万
-$20,384/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$735万
-$16,819/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$702万
-$16,787/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
 $1064万
-$19,783/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="I18" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1079万
-$18,836/呎
-(25年-10月-09日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
+$18,562/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40065,47 +40167,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
+$2377万
+$26,445/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$883万
-$16,920/呎
-(25年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
+$876万
+$16,785/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$892万
-$17,224/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
+$885万
+$17,087/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$731万
-$16,721/呎
-(26年-06月-09日)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
+$725万
+$16,586/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$698万
-$16,687/呎
-(25年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="H19" s="22" t="inlineStr">
+$692万
+$16,553/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -40113,22 +40215,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I19" s="21" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1069万
-$18,654/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
+$1027万
+$17,925/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40136,47 +40238,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
+$2348万
+$26,118/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$880万
-$16,852/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
+$873万
+$16,718/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$889万
-$17,156/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
+$882万
+$17,019/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$728万
-$16,652/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
+$722万
+$16,519/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$719万
-$17,206/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="H20" s="22" t="inlineStr">
+$689万
+$16,488/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -40184,22 +40286,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I20" s="21" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1064万
-$18,562/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
+$1053万
+$18,379/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40207,47 +40309,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2377万
-$26,445/呎
+$2318万
+$25,783/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$876万
-$16,785/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
+$869万
+$16,651/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$885万
-$17,087/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr">
+$878万
+$16,952/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$725万
-$16,586/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
+$719万
+$16,455/呎
+(26年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$692万
-$16,553/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
+$711万
+$17,002/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -40255,22 +40357,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I21" s="21" t="inlineStr">
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1027万
-$17,925/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
+$1048万
+$18,286/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40278,47 +40380,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2348万
-$26,118/呎
+$2288万
+$25,452/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$873万
-$16,718/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
+$856万
+$16,389/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$882万
-$17,019/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
+$875万
+$16,884/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$722万
-$16,519/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
+$716万
+$16,389/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$689万
-$16,488/呎
+$684万
+$16,356/呎
 (25年-09月-30日)</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -40326,22 +40428,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I22" s="21" t="inlineStr">
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1053万
-$18,379/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
+$1043万
+$18,195/呎
+(26年-06月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40349,70 +40451,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2318万
-$25,783/呎
+$2259万
+$25,125/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$869万
-$16,651/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
+$883万
+$16,908/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$878万
-$16,952/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
+$871万
+$16,817/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$719万
-$16,455/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="inlineStr">
+$713万
+$16,323/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$711万
-$17,002/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="H23" s="22" t="inlineStr">
+$681万
+$16,289/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I23" s="21" t="inlineStr">
+$1023万
+$19,015/呎
+(26年-08月-09日)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1048万
-$18,286/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
+$1074万
+$18,743/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40420,70 +40522,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2288万
-$25,452/呎
+$2230万
+$24,803/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$856万
-$16,389/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
+$859万
+$16,452/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$875万
-$16,884/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
+$868万
+$16,749/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$716万
-$16,389/呎
+$710万
+$16,259/呎
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$684万
-$16,356/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="inlineStr">
+$702万
+$16,799/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I24" s="21" t="inlineStr">
+$1018万
+$18,920/呎
+(26年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1043万
-$18,195/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
+$1069万
+$18,651/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40491,70 +40593,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2259万
-$25,125/呎
+$2215万
+$24,643/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$883万
-$16,908/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
+$857万
+$16,420/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$871万
-$16,817/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
+$866万
+$16,716/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$713万
-$16,323/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
+$709万
+$16,227/呎
+(26年-02月-27日)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$681万
-$16,289/呎
+$677万
+$16,194/呎
 (25年-10月-03日)</t>
         </is>
       </c>
-      <c r="H25" s="22" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I25" s="21" t="inlineStr">
+$1015万
+$18,872/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1074万
-$18,743/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
+$1030万
+$17,970/呎
+(25年-10月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40562,70 +40664,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2230万
-$24,803/呎
+$2173万
+$24,171/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$859万
-$16,452/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
+$852万
+$16,322/呎
+(25年-10月-10日)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$868万
-$16,749/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="inlineStr">
+$861万
+$16,616/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$710万
-$16,259/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="inlineStr">
+$705万
+$16,128/呎
+(26年-03月-20日)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$702万
-$16,799/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="H26" s="22" t="inlineStr">
+$673万
+$16,098/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I26" s="21" t="inlineStr">
+$1008万
+$18,732/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1069万
-$18,651/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
+$1022万
+$17,836/呎
+(26年-03月-31日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40633,70 +40735,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2215万
-$24,643/呎
+$2145万
+$23,861/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
+$849万
+$16,257/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
 $857万
-$16,420/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$866万
-$16,716/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
+$16,550/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$709万
-$16,227/呎
-(26年-02月-27日)</t>
-        </is>
-      </c>
-      <c r="G27" s="21" t="inlineStr">
+$702万
+$16,064/呎
+(25年-11月-28日)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$677万
-$16,194/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="inlineStr">
+$670万
+$16,033/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1015万
-$18,872/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="I27" s="21" t="inlineStr">
+$1003万
+$18,638/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1030万
-$17,970/呎
-(25年-10月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
+$1017万
+$17,747/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40704,70 +40806,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2173万
-$24,171/呎
+$2126万
+$23,648/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$852万
-$16,322/呎
-(25年-10月-10日)</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
+$845万
+$16,192/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$861万
-$16,616/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
+$854万
+$16,485/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$705万
-$16,128/呎
-(26年-03月-20日)</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
+$699万
+$16,000/呎
+(25年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$673万
-$16,098/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
+$668万
+$15,969/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1008万
-$18,732/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="I28" s="21" t="inlineStr">
+$998万
+$18,546/呎
+(26年-07月-29日)</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1022万
-$17,836/呎
-(26年-03月-31日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
+$1012万
+$17,658/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40775,70 +40877,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2145万
-$23,861/呎
+$2107万
+$23,437/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$849万
-$16,257/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="inlineStr">
+$842万
+$16,128/呎
+(25年-10月-09日)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$857万
-$16,550/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="F29" s="21" t="inlineStr">
+$850万
+$16,419/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$702万
-$16,064/呎
-(25年-11月-28日)</t>
-        </is>
-      </c>
-      <c r="G29" s="21" t="inlineStr">
+$696万
+$15,938/呎
+(26年-01月-22日)</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$670万
-$16,033/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
+$665万
+$15,907/呎
+(25年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1003万
-$18,638/呎
-(26年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="I29" s="21" t="inlineStr">
+$993万
+$18,454/呎
+(26年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1017万
-$17,747/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
+$1007万
+$17,571/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40846,70 +40948,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2126万
-$23,648/呎
+$2096万
+$23,320/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$845万
-$16,192/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
+$838万
+$16,063/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$854万
-$16,485/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="F30" s="21" t="inlineStr">
+$847万
+$16,353/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$699万
-$16,000/呎
-(25年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="G30" s="21" t="inlineStr">
+$694万
+$15,874/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$668万
-$15,969/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
+$686万
+$16,402/呎
+(25年-10月-23日)</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$998万
-$18,546/呎
-(26年-07月-29日)</t>
-        </is>
-      </c>
-      <c r="I30" s="21" t="inlineStr">
+$988万
+$18,362/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1012万
-$17,658/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
+$1002万
+$17,483/呎
+(26年-04月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40917,70 +41019,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2107万
-$23,437/呎
+$2086万
+$23,205/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$842万
-$16,128/呎
-(25年-10月-09日)</t>
-        </is>
-      </c>
-      <c r="E31" s="21" t="inlineStr">
+$835万
+$15,992/呎
+(26年-01月-21日)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$850万
-$16,419/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
+$843万
+$16,280/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$696万
-$15,938/呎
-(26年-01月-22日)</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
+$690万
+$15,801/呎
+(26年-02月-27日)</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$665万
-$15,907/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="H31" s="22" t="inlineStr">
+$659万
+$15,773/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I31" s="21" t="inlineStr">
+$983万
+$18,270/呎
+(26年-08月-05日)</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1007万
-$17,571/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
+$997万
+$17,396/呎
+(26年-04月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40988,70 +41090,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2096万
-$23,320/呎
+$2076万
+$23,089/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D32" s="21" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$838万
-$16,063/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
+$831万
+$15,920/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$847万
-$16,353/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="F32" s="21" t="inlineStr">
+$840万
+$16,207/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$694万
-$15,874/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="G32" s="21" t="inlineStr">
+$688万
+$15,732/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$686万
-$16,402/呎
-(25年-10月-23日)</t>
-        </is>
-      </c>
-      <c r="H32" s="21" t="inlineStr">
+$656万
+$15,701/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$988万
-$18,362/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="I32" s="21" t="inlineStr">
+$978万
+$18,180/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1002万
-$17,483/呎
-(26年-04月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="inlineStr">
+$992万
+$17,311/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -41059,70 +41161,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2086万
-$23,205/呎
+$2065万
+$22,974/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D33" s="21" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
+$827万
+$15,841/呎
+(26年-01月-05日)</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
 $835万
-$15,992/呎
-(26年-01月-21日)</t>
-        </is>
-      </c>
-      <c r="E33" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$843万
-$16,280/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="F33" s="21" t="inlineStr">
+$16,125/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$690万
-$15,801/呎
-(26年-02月-27日)</t>
-        </is>
-      </c>
-      <c r="G33" s="21" t="inlineStr">
+$684万
+$15,654/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$659万
-$15,773/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H33" s="21" t="inlineStr">
+$653万
+$15,624/呎
+(25年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$983万
-$18,270/呎
-(26年-07月-12日)</t>
-        </is>
-      </c>
-      <c r="I33" s="21" t="inlineStr">
+$973万
+$18,089/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$997万
-$17,396/呎
-(26年-04月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="58" customHeight="1">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B34" s="20" t="inlineStr">
+$987万
+$17,223/呎
+(26年-03月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -41130,70 +41232,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2076万
-$23,089/呎
+$2060万
+$22,917/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D34" s="21" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$831万
-$15,920/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
+$815万
+$15,615/呎
+(26年-02月-23日)</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$840万
-$16,207/呎
+$833万
+$16,087/呎
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="F34" s="21" t="inlineStr">
+      <c r="F36" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$688万
-$15,732/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="G34" s="21" t="inlineStr">
+$682万
+$15,616/呎
+(26年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$656万
-$15,701/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="H34" s="21" t="inlineStr">
+$674万
+$16,132/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="H36" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$978万
-$18,180/呎
-(26年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="I34" s="21" t="inlineStr">
+$971万
+$18,045/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="I36" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$992万
-$17,311/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="inlineStr">
+$973万
+$16,979/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -41201,70 +41303,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C37" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2065万
-$22,974/呎
+$2045万
+$22,746/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D35" s="21" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
+$819万
+$15,684/呎
+(26年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
 $827万
-$15,841/呎
-(26年-01月-05日)</t>
-        </is>
-      </c>
-      <c r="E35" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$835万
-$16,125/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F35" s="21" t="inlineStr">
+$15,967/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$684万
-$15,654/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="G35" s="21" t="inlineStr">
+$677万
+$15,499/呎
+(26年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$653万
-$15,624/呎
-(25年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="H35" s="21" t="inlineStr">
+$639万
+$15,285/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$973万
-$18,089/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="I35" s="21" t="inlineStr">
+$964万
+$17,911/呎
+(26年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="I37" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$987万
-$17,223/呎
-(26年-03月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="inlineStr">
+$966万
+$16,853/呎
+(26年-04月-16日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -41272,148 +41374,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2060万
-$22,917/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D36" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$815万
-$15,615/呎
-(26年-02月-23日)</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$833万
-$16,087/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="F36" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$682万
-$15,616/呎
-(26年-04月-01日)</t>
-        </is>
-      </c>
-      <c r="G36" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$674万
-$16,132/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="H36" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$971万
-$18,045/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="I36" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$973万
-$16,979/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B37" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2045万
-$22,746/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D37" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$819万
-$15,684/呎
-(26年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="E37" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$827万
-$15,967/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="F37" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$677万
-$15,499/呎
-(26年-04月-08日)</t>
-        </is>
-      </c>
-      <c r="G37" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$639万
-$15,285/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="H37" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$964万
-$17,911/呎
-(26年-07月-12日)</t>
-        </is>
-      </c>
-      <c r="I37" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$966万
-$16,853/呎
-(26年-04月-16日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="58" customHeight="1">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
@@ -41459,7 +41419,7 @@
           <t>G | 538呎 (2房)
 $959万
 $17,820/呎
-(26年-07月-12日)</t>
+(26年-08月-05日)</t>
         </is>
       </c>
       <c r="I38" s="21" t="inlineStr">
@@ -41689,7 +41649,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -41699,7 +41659,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>168</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -41866,7 +41826,7 @@
           <t>D | 538呎 (2房)
 $994万
 $18,485/呎
-(26年-07月-10日)</t>
+(26年-08月-05日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -42074,12 +42034,12 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$1153万
-$21,426/呎
-(在售)</t>
+$980万
+$18,212/呎
+(26年-08月-08日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -42224,12 +42184,12 @@
 (25年-10月-06日)</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1126万
-$20,965/呎
-(在售)</t>
+$957万
+$17,819/呎
+(26年-08月-09日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
@@ -42248,7 +42208,78 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1221万
+$21,304/呎
+(26年-08月-08日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$967万
+$17,676/呎
+(26年-04月-20日)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$949万
+$17,641/呎
+(26年-05月-15日)</t>
+        </is>
+      </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1119万
+$20,838/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$887万
+$17,330/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1084万
+$19,574/呎
+(26年-03月-31日)</t>
+        </is>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42257,13 +42288,13 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42271,7 +42302,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42279,47 +42310,118 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$967万
-$17,676/呎
-(26年-04月-20日)</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
+$963万
+$17,607/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$949万
-$17,641/呎
+$945万
+$17,572/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1115万
+$20,756/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$884万
+$17,262/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1076万
+$19,419/呎
+(25年-11月-27日)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1197万
+$20,883/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$959万
+$17,536/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$942万
+$17,500/呎
 (26年-05月-15日)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1119万
-$20,838/呎
+$1110万
+$20,672/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$887万
-$17,330/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
+$880万
+$17,193/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1084万
-$19,574/呎
-(26年-03月-31日)</t>
-        </is>
-      </c>
-      <c r="I12" s="22" t="inlineStr">
+$1067万
+$19,265/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42328,13 +42430,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42342,7 +42444,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42350,62 +42452,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$963万
-$17,607/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+$955万
+$17,466/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$945万
-$17,572/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
+$938万
+$17,431/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1115万
-$20,756/呎
+$1106万
+$20,590/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$884万
-$17,262/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
+$877万
+$17,125/呎
+(26年-06月-09日)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1076万
-$19,419/呎
-(25年-11月-27日)</t>
-        </is>
-      </c>
-      <c r="I13" s="21" t="inlineStr">
+$1059万
+$19,112/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1197万
-$20,883/呎
-(26年-07月-28日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42413,7 +42515,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42421,47 +42523,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$959万
-$17,536/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
+$952万
+$17,397/呎
+(25年-11月-21日)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$942万
-$17,500/呎
-(26年-05月-15日)</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
+$934万
+$17,362/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1110万
-$20,672/呎
+$1101万
+$20,508/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$880万
-$17,193/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-      <c r="H14" s="21" t="inlineStr">
+$1048万
+$20,469/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1067万
-$19,265/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="I14" s="22" t="inlineStr">
+$1050万
+$18,958/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42470,13 +42572,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42484,7 +42586,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42492,47 +42594,118 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$955万
-$17,466/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
+$937万
+$17,122/呎
+(26年-04月-14日)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$938万
-$17,431/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
+$930万
+$17,294/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1106万
-$20,590/呎
+$1097万
+$20,426/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$877万
-$17,125/呎
-(26年-06月-09日)</t>
-        </is>
-      </c>
-      <c r="H15" s="21" t="inlineStr">
+$1044万
+$20,387/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1059万
-$19,112/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="I15" s="22" t="inlineStr">
+$1042万
+$18,809/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1159万
+$20,229/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$944万
+$17,258/呎
+(26年-04月-10日)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$927万
+$17,225/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1093万
+$20,346/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1040万
+$20,305/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1034万
+$18,661/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42541,13 +42714,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42555,7 +42728,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42563,47 +42736,118 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$952万
-$17,397/呎
-(25年-11月-21日)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
+$940万
+$17,190/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$934万
-$17,362/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
+$923万
+$17,154/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1101万
-$20,508/呎
+$1088万
+$20,264/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$1048万
-$20,469/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
+$880万
+$17,191/呎
+(26年-07月-13日)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1050万
-$18,958/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I16" s="22" t="inlineStr">
+$1026万
+$18,511/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1141万
+$19,909/呎
+(26年-07月-31日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$938万
+$17,155/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$921万
+$17,121/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$923万
+$17,190/呎
+(26年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$878万
+$17,156/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1022万
+$18,451/呎
+(25年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42612,13 +42856,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42626,7 +42870,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42634,290 +42878,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$937万
-$17,122/呎
-(26年-04月-14日)</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$930万
-$17,294/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1097万
-$20,426/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G17" s="22" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$1044万
-$20,387/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1042万
-$18,809/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="I17" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1159万
-$20,229/呎
-(26年-07月-28日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$944万
-$17,258/呎
-(26年-04月-10日)</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$927万
-$17,225/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1093万
-$20,346/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$1040万
-$20,305/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1034万
-$18,661/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I18" s="22" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$940万
-$17,190/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$923万
-$17,154/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1088万
-$20,264/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$880万
-$17,191/呎
-(26年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1026万
-$18,511/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1141万
-$19,909/呎
-(26年-07月-31日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$938万
-$17,155/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$921万
-$17,121/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$1086万
-$20,223/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$878万
-$17,156/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1022万
-$18,451/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
@@ -42963,7 +42923,7 @@
           <t>H | 573呎 (2房)
 $1126万
 $19,653/呎
-(26年-07月-07日)</t>
+(26年-08月-07日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -1358,38 +1358,30 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>11772000</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>21881</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K12" s="5" t="n">
+        <v>11772000</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>21881</v>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
@@ -1398,7 +1390,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -18211,7 +18203,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -22840,38 +22832,30 @@
       </c>
       <c r="F347" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H347" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I347" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H347" s="5" t="n">
+        <v>12062000</v>
+      </c>
+      <c r="I347" s="5" t="n">
+        <v>21051</v>
       </c>
       <c r="J347" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K347" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L347" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K347" s="5" t="n">
+        <v>12062000</v>
+      </c>
+      <c r="L347" s="5" t="n">
+        <v>21051</v>
       </c>
       <c r="M347" s="3" t="inlineStr">
         <is>
@@ -22880,7 +22864,7 @@
       </c>
       <c r="N347" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -29762,34 +29746,34 @@
       </c>
       <c r="F454" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
-        <v>10624000</v>
+        <v>9030000</v>
       </c>
       <c r="I454" s="5" t="n">
-        <v>19784</v>
+        <v>16816</v>
       </c>
       <c r="J454" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K454" s="5" t="n">
-        <v>9030400</v>
+        <v>9030000</v>
       </c>
       <c r="L454" s="5" t="n">
         <v>16816</v>
       </c>
       <c r="M454" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N454" s="3" t="inlineStr">
@@ -32688,38 +32672,30 @@
       </c>
       <c r="F499" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H499" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I499" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H499" s="5" t="n">
+        <v>10713000</v>
+      </c>
+      <c r="I499" s="5" t="n">
+        <v>18696</v>
       </c>
       <c r="J499" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K499" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L499" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K499" s="5" t="n">
+        <v>10713000</v>
+      </c>
+      <c r="L499" s="5" t="n">
+        <v>18696</v>
       </c>
       <c r="M499" s="3" t="inlineStr">
         <is>
@@ -32728,7 +32704,7 @@
       </c>
       <c r="N499" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38946,7 +38922,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -38956,7 +38932,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>196</t>
+          <t>197</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -39142,7 +39118,504 @@
 (26年-06月-08日)</t>
         </is>
       </c>
-      <c r="H6" s="22" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1177万
+$21,881/呎
+(26年-08月-12日)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1215万
+$21,208/呎
+(26年-06月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$926万
+$17,749/呎
+(26年-02月-24日)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$936万
+$18,068/呎
+(26年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$766万
+$17,538/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$732万
+$17,505/呎
+(26年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1160万
+$21,556/呎
+(26年-07月-20日)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1190万
+$20,771/呎
+(26年-06月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$923万
+$17,678/呎
+(26年-02月-25日)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$932万
+$17,998/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$764万
+$17,471/呎
+(26年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$729万
+$17,435/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1172万
+$20,445/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$894万
+$17,125/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$930万
+$17,961/呎
+(26年-08月-05日)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$762万
+$17,435/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$753万
+$18,014/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1143万
+$21,238/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1159万
+$20,222/呎
+(25年-12月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$916万
+$17,538/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$925万
+$17,853/呎
+(26年-08月-05日)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$757万
+$17,332/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$723万
+$17,297/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1129万
+$20,987/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1145万
+$19,983/呎
+(26年-06月-18日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$901万
+$17,264/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$921万
+$17,782/呎
+(26年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$754万
+$17,263/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$720万
+$17,227/呎
+(26年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1120万
+$20,818/呎
+(26年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1136万
+$19,824/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$908万
+$17,398/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$918万
+$17,712/呎
+(26年-07月-18日)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$751万
+$17,192/呎
+(26年-06月-23日)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$717万
+$17,158/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1111万
+$20,654/呎
+(26年-08月-09日)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1127万
+$19,665/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$905万
+$17,330/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$914万
+$17,641/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$748万
+$17,124/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$714万
+$17,089/呎
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -39150,22 +39623,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1215万
-$21,208/呎
-(26年-06月-17日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
+$1118万
+$19,510/呎
+(26年-06月-18日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39173,7 +39646,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39181,62 +39654,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$926万
-$17,749/呎
-(26年-02月-24日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
+$901万
+$17,261/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$936万
-$18,068/呎
-(26年-08月-06日)</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
+$910万
+$17,571/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$766万
-$17,538/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
+$745万
+$17,057/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$732万
-$17,505/呎
-(26年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
+$712万
+$17,022/呎
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1160万
-$21,556/呎
-(26年-07月-20日)</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1190万
-$20,771/呎
-(26年-06月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
+$1109万
+$19,354/呎
+(26年-06月-18日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39244,7 +39717,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39252,62 +39725,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$923万
-$17,678/呎
-(26年-02月-25日)</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
+$897万
+$17,192/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$932万
-$17,998/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
+$906万
+$17,500/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$764万
-$17,471/呎
-(26年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr">
+$742万
+$16,989/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$729万
-$17,435/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
+$709万
+$16,955/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1172万
-$20,445/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
+$1100万
+$19,201/呎
+(26年-06月-23日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39315,7 +39788,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39323,62 +39796,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
 $894万
 $17,125/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$930万
-$17,961/呎
-(26年-08月-05日)</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
+$903万
+$17,432/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$762万
-$17,435/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="G9" s="21" t="inlineStr">
+$739万
+$16,920/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$753万
-$18,014/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
+$706万
+$16,885/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1143万
-$21,238/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="I9" s="21" t="inlineStr">
+$1076万
+$20,007/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1159万
-$20,222/呎
-(25年-12月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
+$1092万
+$19,049/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39386,7 +39859,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39394,62 +39867,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$916万
-$17,538/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
+$890万
+$17,056/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$925万
-$17,853/呎
-(26年-08月-05日)</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
+$899万
+$17,363/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$757万
-$17,332/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="G10" s="21" t="inlineStr">
+$736万
+$16,854/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$723万
-$17,297/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
+$703万
+$16,818/呎
+(25年-11月-13日)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1129万
-$20,987/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="I10" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1145万
-$19,983/呎
-(26年-06月-18日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
+$1083万
+$18,897/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39457,7 +39930,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39465,62 +39938,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$901万
-$17,264/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
+$888万
+$17,021/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$921万
-$17,782/呎
-(26年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
+$1056万
+$20,384/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$754万
-$17,263/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="G11" s="21" t="inlineStr">
+$735万
+$16,819/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$720万
-$17,227/呎
-(26年-04月-16日)</t>
-        </is>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
+$702万
+$16,787/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1120万
-$20,818/呎
-(26年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="I11" s="21" t="inlineStr">
+$1064万
+$19,783/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1136万
-$19,824/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
+$1079万
+$18,836/呎
+(25年-10月-09日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39528,7 +40001,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39536,62 +40009,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$908万
-$17,398/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
+$883万
+$16,920/呎
+(25年-12月-09日)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$918万
-$17,712/呎
-(26年-07月-18日)</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
+$892万
+$17,224/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$751万
-$17,192/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="G12" s="21" t="inlineStr">
+$731万
+$16,721/呎
+(26年-06月-09日)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$717万
-$17,158/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
+$698万
+$16,687/呎
+(25年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1111万
-$20,654/呎
-(26年-08月-09日)</t>
-        </is>
-      </c>
-      <c r="I12" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1127万
-$19,665/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
+$1069万
+$18,654/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39599,7 +40072,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39607,39 +40080,39 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$905万
-$17,330/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+$880万
+$16,852/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$914万
-$17,641/呎
-(26年-07月-24日)</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
+$889万
+$17,156/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$748万
-$17,124/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-      <c r="G13" s="21" t="inlineStr">
+$728万
+$16,652/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$714万
-$17,089/呎
-(26年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="H13" s="22" t="inlineStr">
+$719万
+$17,206/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -39647,22 +40120,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I13" s="21" t="inlineStr">
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1118万
-$19,510/呎
-(26年-06月-18日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
+$1064万
+$18,562/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39670,47 +40143,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
+$2377万
+$26,445/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$901万
-$17,261/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
+$876万
+$16,785/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$910万
-$17,571/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
+$885万
+$17,087/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$745万
-$17,057/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-      <c r="G14" s="21" t="inlineStr">
+$725万
+$16,586/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$712万
-$17,022/呎
-(26年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="inlineStr">
+$692万
+$16,553/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -39718,22 +40191,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1109万
-$19,354/呎
-(26年-06月-18日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
+$1027万
+$17,925/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39741,47 +40214,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
+$2348万
+$26,118/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$897万
-$17,192/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
+$873万
+$16,718/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$906万
-$17,500/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="F15" s="21" t="inlineStr">
+$882万
+$17,019/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$742万
-$16,989/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-      <c r="G15" s="21" t="inlineStr">
+$722万
+$16,519/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$709万
-$16,955/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="H15" s="22" t="inlineStr">
+$689万
+$16,488/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -39789,22 +40262,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1100万
-$19,201/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
+$1053万
+$18,379/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39812,70 +40285,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
+$2318万
+$25,783/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$869万
+$16,651/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$878万
+$16,952/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$719万
+$16,455/呎
+(26年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$711万
+$17,002/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$894万
-$17,125/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$903万
-$17,432/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$739万
-$16,920/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$706万
-$16,885/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1076万
-$20,007/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="I16" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1092万
-$19,049/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
+$1048万
+$18,286/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39883,47 +40356,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
+$2288万
+$25,452/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$890万
-$17,056/呎
+$856万
+$16,389/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$875万
+$16,884/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$716万
+$16,389/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$684万
+$16,356/呎
 (25年-09月-30日)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$899万
-$17,363/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$736万
-$16,854/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="G17" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$703万
-$16,818/呎
-(25年-11月-13日)</t>
-        </is>
-      </c>
-      <c r="H17" s="22" t="inlineStr">
+      <c r="H24" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -39931,22 +40404,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr">
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1083万
-$18,897/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
+$1043万
+$18,195/呎
+(26年-06月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39954,70 +40427,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
+$2259万
+$25,125/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$888万
-$17,021/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="E18" s="23" t="inlineStr">
+$883万
+$16,908/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$1056万
-$20,384/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
+$871万
+$16,817/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$735万
-$16,819/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
+$713万
+$16,323/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$702万
-$16,787/呎
+$681万
+$16,289/呎
 (25年-10月-03日)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1064万
-$19,783/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="I18" s="21" t="inlineStr">
+$1023万
+$19,015/呎
+(26年-08月-09日)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1079万
-$18,836/呎
-(25年-10月-09日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
+$1074万
+$18,743/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40025,70 +40498,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
+$2230万
+$24,803/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$883万
-$16,920/呎
-(25年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
+$859万
+$16,452/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$892万
-$17,224/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
+$868万
+$16,749/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$731万
-$16,721/呎
-(26年-06月-09日)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
+$710万
+$16,259/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$698万
-$16,687/呎
-(25年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="H19" s="22" t="inlineStr">
+$702万
+$16,799/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
+$1018万
+$18,920/呎
+(26年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 $1069万
-$18,654/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
+$18,651/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40096,70 +40569,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
+$2215万
+$24,643/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$880万
-$16,852/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
+$857万
+$16,420/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$889万
-$17,156/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
+$866万
+$16,716/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$728万
-$16,652/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
+$709万
+$16,227/呎
+(26年-02月-27日)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$719万
-$17,206/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="H20" s="22" t="inlineStr">
+$677万
+$16,194/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
+$1015万
+$18,872/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1064万
-$18,562/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
+$1030万
+$17,970/呎
+(25年-10月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40167,70 +40640,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2377万
-$26,445/呎
+$2173万
+$24,171/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$876万
-$16,785/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
+$852万
+$16,322/呎
+(25年-10月-10日)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$885万
-$17,087/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr">
+$861万
+$16,616/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$725万
-$16,586/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
+$705万
+$16,128/呎
+(26年-03月-20日)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$692万
-$16,553/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
+$673万
+$16,098/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
+$1008万
+$18,732/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1027万
-$17,925/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
+$1022万
+$17,836/呎
+(26年-03月-31日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40238,70 +40711,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2348万
-$26,118/呎
+$2145万
+$23,861/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$873万
-$16,718/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
+$849万
+$16,257/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$882万
-$17,019/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
+$857万
+$16,550/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$722万
-$16,519/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
+$702万
+$16,064/呎
+(25年-11月-28日)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$689万
-$16,488/呎
+$670万
+$16,033/呎
 (25年-09月-30日)</t>
         </is>
       </c>
-      <c r="H22" s="22" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I22" s="21" t="inlineStr">
+$1003万
+$18,638/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1053万
-$18,379/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
+$1017万
+$17,747/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40309,70 +40782,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2318万
-$25,783/呎
+$2126万
+$23,648/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$869万
-$16,651/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
+$845万
+$16,192/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$878万
-$16,952/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
+$854万
+$16,485/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$719万
-$16,455/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="inlineStr">
+$699万
+$16,000/呎
+(25年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$711万
-$17,002/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="H23" s="22" t="inlineStr">
+$668万
+$15,969/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I23" s="21" t="inlineStr">
+$998万
+$18,546/呎
+(26年-07月-29日)</t>
+        </is>
+      </c>
+      <c r="I30" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1048万
-$18,286/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
+$1012万
+$17,658/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40380,70 +40853,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C31" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2288万
-$25,452/呎
+$2107万
+$23,437/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$856万
-$16,389/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
+$842万
+$16,128/呎
+(25年-10月-09日)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$875万
-$16,884/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
+$850万
+$16,419/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$716万
-$16,389/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
+$696万
+$15,938/呎
+(26年-01月-22日)</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$684万
-$16,356/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="inlineStr">
+$665万
+$15,907/呎
+(25年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I24" s="21" t="inlineStr">
+$993万
+$18,454/呎
+(26年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1043万
-$18,195/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
+$1007万
+$17,571/呎
+(26年-05月-19日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40451,70 +40924,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C32" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2259万
-$25,125/呎
+$2096万
+$23,320/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$883万
-$16,908/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
+$838万
+$16,063/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$871万
-$16,817/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
+$847万
+$16,353/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$713万
-$16,323/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
+$694万
+$15,874/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$681万
-$16,289/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
+$686万
+$16,402/呎
+(25年-10月-23日)</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1023万
-$19,015/呎
-(26年-08月-09日)</t>
-        </is>
-      </c>
-      <c r="I25" s="21" t="inlineStr">
+$988万
+$18,362/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1074万
-$18,743/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
+$1002万
+$17,483/呎
+(26年-04月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40522,70 +40995,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C33" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2230万
-$24,803/呎
+$2086万
+$23,205/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D33" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$859万
-$16,452/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
+$835万
+$15,992/呎
+(26年-01月-21日)</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$868万
-$16,749/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="inlineStr">
+$843万
+$16,280/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$710万
-$16,259/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="inlineStr">
+$690万
+$15,801/呎
+(26年-02月-27日)</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$702万
-$16,799/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="H26" s="21" t="inlineStr">
+$659万
+$15,773/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1018万
-$18,920/呎
-(26年-08月-08日)</t>
-        </is>
-      </c>
-      <c r="I26" s="21" t="inlineStr">
+$983万
+$18,270/呎
+(26年-08月-05日)</t>
+        </is>
+      </c>
+      <c r="I33" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1069万
-$18,651/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
+$997万
+$17,396/呎
+(26年-04月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="58" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40593,70 +41066,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C34" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2215万
-$24,643/呎
+$2076万
+$23,089/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D34" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$857万
-$16,420/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
+$831万
+$15,920/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$866万
-$16,716/呎
+$840万
+$16,207/呎
 (26年-06月-30日)</t>
         </is>
       </c>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="F34" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$709万
-$16,227/呎
-(26年-02月-27日)</t>
-        </is>
-      </c>
-      <c r="G27" s="21" t="inlineStr">
+$688万
+$15,732/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="G34" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$677万
-$16,194/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="inlineStr">
+$656万
+$15,701/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="H34" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1015万
-$18,872/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="I27" s="21" t="inlineStr">
+$978万
+$18,180/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="I34" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1030万
-$17,970/呎
-(25年-10月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
+$992万
+$17,311/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="58" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40664,70 +41137,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C35" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2173万
-$24,171/呎
+$2065万
+$22,974/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D35" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$852万
-$16,322/呎
-(25年-10月-10日)</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
+$827万
+$15,841/呎
+(26年-01月-05日)</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$861万
-$16,616/呎
+$835万
+$16,125/呎
 (26年-07月-03日)</t>
         </is>
       </c>
-      <c r="F28" s="21" t="inlineStr">
+      <c r="F35" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$705万
-$16,128/呎
-(26年-03月-20日)</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
+$684万
+$15,654/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$673万
-$16,098/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
+$653万
+$15,624/呎
+(25年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1008万
-$18,732/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="I28" s="21" t="inlineStr">
+$973万
+$18,089/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1022万
-$17,836/呎
-(26年-03月-31日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
+$987万
+$17,223/呎
+(26年-03月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="58" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40735,70 +41208,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C36" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2145万
-$23,861/呎
+$2060万
+$22,917/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
+      <c r="D36" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$849万
-$16,257/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="inlineStr">
+$815万
+$15,615/呎
+(26年-02月-23日)</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$857万
-$16,550/呎
+$833万
+$16,087/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$682万
+$15,616/呎
+(26年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="G36" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$674万
+$16,132/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="H36" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$971万
+$18,045/呎
 (26年-07月-02日)</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$702万
-$16,064/呎
-(25年-11月-28日)</t>
-        </is>
-      </c>
-      <c r="G29" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$670万
-$16,033/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1003万
-$18,638/呎
-(26年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="I29" s="21" t="inlineStr">
+      <c r="I36" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1017万
-$17,747/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
+$973万
+$16,979/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="58" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40806,70 +41279,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C37" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2126万
-$23,648/呎
+$2045万
+$22,746/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D30" s="21" t="inlineStr">
+      <c r="D37" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$845万
-$16,192/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
+$819万
+$15,684/呎
+(26年-02月-26日)</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$854万
-$16,485/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="F30" s="21" t="inlineStr">
+$827万
+$15,967/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$699万
-$16,000/呎
-(25年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="G30" s="21" t="inlineStr">
+$677万
+$15,499/呎
+(26年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$668万
-$15,969/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
+$639万
+$15,285/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$998万
-$18,546/呎
-(26年-07月-29日)</t>
-        </is>
-      </c>
-      <c r="I30" s="21" t="inlineStr">
+$964万
+$17,911/呎
+(26年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="I37" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1012万
-$17,658/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
+$966万
+$16,853/呎
+(26年-04月-16日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="58" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40877,70 +41350,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C38" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2107万
-$23,437/呎
+$2035万
+$22,633/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D31" s="21" t="inlineStr">
+      <c r="D38" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$842万
-$16,128/呎
-(25年-10月-09日)</t>
-        </is>
-      </c>
-      <c r="E31" s="21" t="inlineStr">
+$805万
+$15,423/呎
+(26年-02月-27日)</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$850万
-$16,419/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
+$823万
+$15,888/呎
+(26年-06月-29日)</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$696万
-$15,938/呎
-(26年-01月-22日)</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
+$674万
+$15,421/呎
+(26年-04月-10日)</t>
+        </is>
+      </c>
+      <c r="G38" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$665万
-$15,907/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
+$643万
+$15,392/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H38" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$993万
-$18,454/呎
-(26年-08月-08日)</t>
-        </is>
-      </c>
-      <c r="I31" s="21" t="inlineStr">
+$959万
+$17,820/呎
+(26年-08月-05日)</t>
+        </is>
+      </c>
+      <c r="I38" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1007万
-$17,571/呎
-(26年-05月-19日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
+$972万
+$16,967/呎
+(26年-04月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="58" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40948,503 +41421,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2096万
-$23,320/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$838万
-$16,063/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$847万
-$16,353/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="F32" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$694万
-$15,874/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="G32" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$686万
-$16,402/呎
-(25年-10月-23日)</t>
-        </is>
-      </c>
-      <c r="H32" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$988万
-$18,362/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="I32" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1002万
-$17,483/呎
-(26年-04月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C33" s="24" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2086万
-$23,205/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D33" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$835万
-$15,992/呎
-(26年-01月-21日)</t>
-        </is>
-      </c>
-      <c r="E33" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$843万
-$16,280/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="F33" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$690万
-$15,801/呎
-(26年-02月-27日)</t>
-        </is>
-      </c>
-      <c r="G33" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$659万
-$15,773/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H33" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$983万
-$18,270/呎
-(26年-08月-05日)</t>
-        </is>
-      </c>
-      <c r="I33" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$997万
-$17,396/呎
-(26年-04月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="58" customHeight="1">
-      <c r="A34" s="19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B34" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2076万
-$23,089/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$831万
-$15,920/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="E34" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$840万
-$16,207/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="F34" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$688万
-$15,732/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="G34" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$656万
-$15,701/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="H34" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$978万
-$18,180/呎
-(26年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="I34" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$992万
-$17,311/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="58" customHeight="1">
-      <c r="A35" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2065万
-$22,974/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D35" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$827万
-$15,841/呎
-(26年-01月-05日)</t>
-        </is>
-      </c>
-      <c r="E35" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$835万
-$16,125/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F35" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$684万
-$15,654/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="G35" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$653万
-$15,624/呎
-(25年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="H35" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$973万
-$18,089/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="I35" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$987万
-$17,223/呎
-(26年-03月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="58" customHeight="1">
-      <c r="A36" s="19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B36" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2060万
-$22,917/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D36" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$815万
-$15,615/呎
-(26年-02月-23日)</t>
-        </is>
-      </c>
-      <c r="E36" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$833万
-$16,087/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="F36" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$682万
-$15,616/呎
-(26年-04月-01日)</t>
-        </is>
-      </c>
-      <c r="G36" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$674万
-$16,132/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="H36" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$971万
-$18,045/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="I36" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$973万
-$16,979/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="58" customHeight="1">
-      <c r="A37" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B37" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C37" s="24" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2045万
-$22,746/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D37" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$819万
-$15,684/呎
-(26年-02月-26日)</t>
-        </is>
-      </c>
-      <c r="E37" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$827万
-$15,967/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="F37" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$677万
-$15,499/呎
-(26年-04月-08日)</t>
-        </is>
-      </c>
-      <c r="G37" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$639万
-$15,285/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="H37" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$964万
-$17,911/呎
-(26年-08月-06日)</t>
-        </is>
-      </c>
-      <c r="I37" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$966万
-$16,853/呎
-(26年-04月-16日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="58" customHeight="1">
-      <c r="A38" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B38" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C38" s="24" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2035万
-$22,633/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D38" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$805万
-$15,423/呎
-(26年-02月-27日)</t>
-        </is>
-      </c>
-      <c r="E38" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$823万
-$15,888/呎
-(26年-06月-29日)</t>
-        </is>
-      </c>
-      <c r="F38" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$674万
-$15,421/呎
-(26年-04月-10日)</t>
-        </is>
-      </c>
-      <c r="G38" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$643万
-$15,392/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H38" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$959万
-$17,820/呎
-(26年-08月-05日)</t>
-        </is>
-      </c>
-      <c r="I38" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$972万
-$16,967/呎
-(26年-04月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="58" customHeight="1">
-      <c r="A39" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B39" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
@@ -41490,7 +41466,7 @@
           <t>G | 538呎 (2房)
 $954万
 $17,732/呎
-(26年-07月-18日)</t>
+(26年-08月-11日)</t>
         </is>
       </c>
       <c r="I39" s="21" t="inlineStr">
@@ -41649,7 +41625,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -41659,7 +41635,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>171</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -42279,7 +42255,149 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1206万
+$21,051/呎
+(26年-08月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$963万
+$17,607/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$945万
+$17,572/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1115万
+$20,756/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$884万
+$17,262/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1076万
+$19,419/呎
+(25年-11月-27日)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1197万
+$20,883/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$959万
+$17,536/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$942万
+$17,500/呎
+(26年-05月-15日)</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1110万
+$20,672/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$880万
+$17,193/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1067万
+$19,265/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42288,13 +42406,13 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42302,7 +42420,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42310,62 +42428,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$963万
-$17,607/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+$955万
+$17,466/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$945万
-$17,572/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
+$938万
+$17,431/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1115万
-$20,756/呎
+$1106万
+$20,590/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$884万
-$17,262/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="H13" s="21" t="inlineStr">
+$877万
+$17,125/呎
+(26年-06月-09日)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1076万
-$19,419/呎
-(25年-11月-27日)</t>
-        </is>
-      </c>
-      <c r="I13" s="21" t="inlineStr">
+$1059万
+$19,112/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1197万
-$20,883/呎
-(26年-07月-28日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42373,7 +42491,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42381,47 +42499,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$959万
-$17,536/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
+$952万
+$17,397/呎
+(25年-11月-21日)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$942万
-$17,500/呎
-(26年-05月-15日)</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
+$934万
+$17,362/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1110万
-$20,672/呎
+$1101万
+$20,508/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$880万
-$17,193/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-      <c r="H14" s="21" t="inlineStr">
+$1048万
+$20,469/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1067万
-$19,265/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="I14" s="22" t="inlineStr">
+$1050万
+$18,958/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42430,13 +42548,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42444,7 +42562,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42452,47 +42570,118 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$955万
-$17,466/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
+$937万
+$17,122/呎
+(26年-04月-14日)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$938万
-$17,431/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
+$930万
+$17,294/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1106万
-$20,590/呎
+$1097万
+$20,426/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$877万
-$17,125/呎
-(26年-06月-09日)</t>
-        </is>
-      </c>
-      <c r="H15" s="21" t="inlineStr">
+$1044万
+$20,387/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1059万
-$19,112/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="I15" s="22" t="inlineStr">
+$1042万
+$18,809/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1159万
+$20,229/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$944万
+$17,258/呎
+(26年-04月-10日)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$927万
+$17,225/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1093万
+$20,346/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1040万
+$20,305/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1034万
+$18,661/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42501,13 +42690,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42515,7 +42704,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42523,47 +42712,118 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$952万
-$17,397/呎
-(25年-11月-21日)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
+$940万
+$17,190/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$934万
-$17,362/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
+$923万
+$17,154/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1101万
-$20,508/呎
+$1088万
+$20,264/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$1048万
-$20,469/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
+$880万
+$17,191/呎
+(26年-07月-13日)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1050万
-$18,958/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I16" s="22" t="inlineStr">
+$1026万
+$18,511/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1141万
+$19,909/呎
+(26年-07月-31日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$938万
+$17,155/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$921万
+$17,121/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$923万
+$17,190/呎
+(26年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$878万
+$17,156/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1022万
+$18,451/呎
+(25年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42572,13 +42832,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42586,7 +42846,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42594,62 +42854,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$937万
-$17,122/呎
-(26年-04月-14日)</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
+$933万
+$17,053/呎
+(26年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$930万
-$17,294/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
+$905万
+$16,818/呎
+(26年-03月-09日)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1097万
-$20,426/呎
+$1080万
+$20,102/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$1044万
-$20,387/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
+$856万
+$16,719/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1042万
-$18,809/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="I17" s="21" t="inlineStr">
+$1012万
+$18,274/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1159万
-$20,229/呎
-(26年-07月-28日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
+$1126万
+$19,653/呎
+(26年-08月-07日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42657,7 +42917,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42665,47 +42925,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$944万
-$17,258/呎
-(26年-04月-10日)</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
+$902万
+$16,484/呎
+(26年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$927万
-$17,225/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
+$912万
+$16,952/呎
+(26年-03月-13日)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1093万
-$20,346/呎
+$1075万
+$20,022/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$1040万
-$20,305/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
+$853万
+$16,652/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1034万
-$18,661/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I18" s="22" t="inlineStr">
+$996万
+$17,969/呎
+(26年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42714,13 +42974,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42728,7 +42988,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42736,62 +42996,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$940万
-$17,190/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
+$914万
+$16,718/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$923万
-$17,154/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
+$908万
+$16,885/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1088万
-$20,264/呎
+$1071万
+$19,944/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$880万
-$17,191/呎
-(26年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
+$849万
+$16,586/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1026万
-$18,511/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
+$1002万
+$18,092/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1141万
-$19,909/呎
-(26年-07月-31日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42799,7 +43059,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42807,47 +43067,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$938万
-$17,155/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
+$922万
+$16,850/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$921万
-$17,121/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
+$894万
+$16,619/呎
+(26年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$923万
-$17,190/呎
-(26年-08月-08日)</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
+$907万
+$16,885/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$878万
-$17,156/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
+$846万
+$16,520/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1022万
-$18,451/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
+$986万
+$17,791/呎
+(26年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42856,13 +43116,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42870,7 +43130,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42878,62 +43138,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$933万
-$17,053/呎
-(26年-04月-08日)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
+$918万
+$16,782/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$905万
-$16,818/呎
-(26年-03月-09日)</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="inlineStr">
+$901万
+$16,751/呎
+(26年-03月-18日)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1080万
-$20,102/呎
+$903万
+$16,816/呎
+(26年-08月-10日)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$842万
+$16,453/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$992万
+$17,913/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
 (在售)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$856万
-$16,719/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="H21" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1012万
-$18,274/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1126万
-$19,653/呎
-(26年-08月-07日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42941,7 +43201,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42949,47 +43209,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$902万
-$16,484/呎
-(26年-04月-01日)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
+$914万
+$16,715/呎
+(26年-04月-10日)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$912万
-$16,952/呎
-(26年-03月-13日)</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
+$887万
+$16,487/呎
+(26年-03月-02日)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1075万
-$20,022/呎
+$1058万
+$19,706/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$853万
-$16,652/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
+$839万
+$16,389/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$996万
-$17,969/呎
-(26年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="I22" s="22" t="inlineStr">
+$987万
+$17,823/呎
+(26年-03月-31日)</t>
+        </is>
+      </c>
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42998,13 +43258,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43012,7 +43272,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43020,47 +43280,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$914万
-$16,718/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
+$911万
+$16,649/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$908万
-$16,885/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
+$894万
+$16,615/呎
+(26年-03月-25日)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1071万
-$19,944/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="inlineStr">
+$878万
+$16,356/呎
+(26年-06月-04日)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$849万
-$16,586/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
+$836万
+$16,324/呎
+(26年-03月-25日)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1002万
-$18,092/呎
+$982万
+$17,735/呎
 (25年-10月-02日)</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="I27" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43069,13 +43329,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43083,7 +43343,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43091,47 +43351,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
+$907万
+$16,581/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
 $922万
-$16,850/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$894万
-$16,619/呎
-(26年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
+$17,134/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$907万
-$16,885/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
+$875万
+$16,291/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$846万
-$16,520/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="H24" s="21" t="inlineStr">
+$832万
+$16,258/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$986万
-$17,791/呎
-(26年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="I24" s="22" t="inlineStr">
+$978万
+$17,648/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43140,13 +43400,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43154,7 +43414,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43162,47 +43422,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$918万
-$16,782/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
+$905万
+$16,550/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$901万
-$16,751/呎
-(26年-03月-18日)</t>
-        </is>
-      </c>
-      <c r="F25" s="22" t="inlineStr">
+$889万
+$16,517/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1062万
-$19,784/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
+$873万
+$16,259/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$842万
-$16,453/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
+$831万
+$16,227/呎
+(25年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$992万
-$17,913/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="I25" s="22" t="inlineStr">
+$964万
+$17,395/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43211,13 +43471,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43225,7 +43485,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43233,47 +43493,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$914万
-$16,715/呎
-(26年-04月-10日)</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
+$900万
+$16,452/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$887万
-$16,487/呎
-(26年-03月-02日)</t>
-        </is>
-      </c>
-      <c r="F26" s="22" t="inlineStr">
+$883万
+$16,418/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1058万
-$19,706/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="inlineStr">
+$868万
+$16,162/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$839万
-$16,389/呎
+$826万
+$16,131/呎
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$987万
-$17,823/呎
-(26年-03月-31日)</t>
-        </is>
-      </c>
-      <c r="I26" s="22" t="inlineStr">
+$968万
+$17,471/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43282,13 +43542,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43296,7 +43556,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43304,290 +43564,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$911万
-$16,649/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$894万
-$16,615/呎
-(26年-03月-25日)</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$878万
-$16,356/呎
-(26年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="G27" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$836万
-$16,324/呎
-(26年-03月-25日)</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$982万
-$17,735/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I27" s="22" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$907万
-$16,581/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$922万
-$17,134/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$875万
-$16,291/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$832万
-$16,258/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$978万
-$17,648/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="I28" s="22" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$905万
-$16,550/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$889万
-$16,517/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="F29" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$873万
-$16,259/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="G29" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$831万
-$16,227/呎
-(25年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$964万
-$17,395/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="I29" s="22" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$900万
-$16,452/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$883万
-$16,418/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="F30" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$868万
-$16,162/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="G30" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$826万
-$16,131/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$968万
-$17,471/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I30" s="22" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
@@ -43628,12 +43604,12 @@
 (26年-03月-19日)</t>
         </is>
       </c>
-      <c r="I31" s="22" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
+$1071万
+$18,696/呎
+(26年-08月-12日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -4629,7 +4629,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -39525,7 +39525,7 @@
           <t>D | 518呎 (2房)
 $918万
 $17,712/呎
-(26年-07月-18日)</t>
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr">

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -838,38 +838,30 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>11948000</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>22208</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K4" s="5" t="n">
+        <v>11948000</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>22208</v>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
@@ -878,7 +870,7 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -4950,38 +4942,30 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>11024000</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>20491</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K68" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K68" s="5" t="n">
+        <v>11024000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>20491</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
@@ -4990,7 +4974,7 @@
       </c>
       <c r="N68" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -5470,38 +5454,30 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I76" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>10936000</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>20327</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K76" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L76" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K76" s="5" t="n">
+        <v>10936000</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>20327</v>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
@@ -5510,7 +5486,7 @@
       </c>
       <c r="N76" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -9606,38 +9582,30 @@
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H140" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I140" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H140" s="5" t="n">
+        <v>10384000</v>
+      </c>
+      <c r="I140" s="5" t="n">
+        <v>19301</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K140" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L140" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K140" s="5" t="n">
+        <v>10384000</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>19301</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
@@ -9646,7 +9614,7 @@
       </c>
       <c r="N140" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -10118,38 +10086,30 @@
       </c>
       <c r="F148" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H148" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I148" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H148" s="5" t="n">
+        <v>10332000</v>
+      </c>
+      <c r="I148" s="5" t="n">
+        <v>19204</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K148" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L148" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K148" s="5" t="n">
+        <v>10332000</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>19204</v>
       </c>
       <c r="M148" s="3" t="inlineStr">
         <is>
@@ -10158,7 +10118,7 @@
       </c>
       <c r="N148" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -24376,38 +24336,30 @@
       </c>
       <c r="F371" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H371" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I371" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H371" s="5" t="n">
+        <v>11778000</v>
+      </c>
+      <c r="I371" s="5" t="n">
+        <v>20555</v>
       </c>
       <c r="J371" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K371" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L371" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K371" s="5" t="n">
+        <v>11778000</v>
+      </c>
+      <c r="L371" s="5" t="n">
+        <v>20555</v>
       </c>
       <c r="M371" s="3" t="inlineStr">
         <is>
@@ -24416,7 +24368,7 @@
       </c>
       <c r="N371" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -30266,34 +30218,34 @@
       </c>
       <c r="F462" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G462" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="H462" s="5" t="n">
-        <v>10582000</v>
+        <v>8995000</v>
       </c>
       <c r="I462" s="5" t="n">
-        <v>19706</v>
+        <v>16750</v>
       </c>
       <c r="J462" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K462" s="5" t="n">
-        <v>8994700</v>
+        <v>8995000</v>
       </c>
       <c r="L462" s="5" t="n">
         <v>16750</v>
       </c>
       <c r="M462" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N462" s="3" t="inlineStr">
@@ -38922,7 +38874,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -38932,7 +38884,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>202</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -39047,7 +38999,717 @@
 (26年-06月-18日)</t>
         </is>
       </c>
-      <c r="H5" s="22" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1195万
+$22,208/呎
+(26年-08月-16日)</t>
+        </is>
+      </c>
+      <c r="I5" s="21" t="inlineStr">
+        <is>
+          <t>H | 571呎 (2房)
+$1236万
+$21,651/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$933万
+$17,874/呎
+(25年-12月-11日)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$943万
+$18,197/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$772万
+$17,664/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+      <c r="G6" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$737万
+$17,627/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1177万
+$21,881/呎
+(26年-08月-12日)</t>
+        </is>
+      </c>
+      <c r="I6" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1215万
+$21,208/呎
+(26年-06月-17日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$926万
+$17,749/呎
+(26年-02月-24日)</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$936万
+$18,068/呎
+(26年-08月-06日)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$766万
+$17,538/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$732万
+$17,505/呎
+(26年-06月-11日)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1160万
+$21,556/呎
+(26年-07月-20日)</t>
+        </is>
+      </c>
+      <c r="I7" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1190万
+$20,771/呎
+(26年-06月-11日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$923万
+$17,678/呎
+(26年-02月-25日)</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$932万
+$17,998/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$764万
+$17,471/呎
+(26年-08月-03日)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$729万
+$17,435/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="H8" s="20" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I8" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1172万
+$20,445/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$894万
+$17,125/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$930万
+$17,961/呎
+(26年-08月-05日)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$762万
+$17,435/呎
+(26年-06月-24日)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$753万
+$18,014/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1143万
+$21,238/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="I9" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1159万
+$20,222/呎
+(25年-12月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$916万
+$17,538/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$925万
+$17,853/呎
+(26年-08月-05日)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$757万
+$17,332/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$723万
+$17,297/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1129万
+$20,987/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="I10" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1145万
+$19,983/呎
+(26年-06月-18日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$901万
+$17,264/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$921万
+$17,782/呎
+(26年-07月-15日)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$754万
+$17,263/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$720万
+$17,227/呎
+(26年-04月-16日)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1120万
+$20,818/呎
+(26年-07月-16日)</t>
+        </is>
+      </c>
+      <c r="I11" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1136万
+$19,824/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$908万
+$17,398/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$918万
+$17,712/呎
+(26年-08月-14日)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$751万
+$17,192/呎
+(26年-06月-23日)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$717万
+$17,158/呎
+(26年-05月-07日)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1111万
+$20,654/呎
+(26年-08月-09日)</t>
+        </is>
+      </c>
+      <c r="I12" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1127万
+$19,665/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$905万
+$17,330/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$914万
+$17,641/呎
+(26年-07月-24日)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$748万
+$17,124/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$714万
+$17,089/呎
+(26年-05月-08日)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1102万
+$20,491/呎
+(26年-08月-15日)</t>
+        </is>
+      </c>
+      <c r="I13" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1118万
+$19,510/呎
+(26年-06月-18日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$901万
+$17,261/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="E14" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$910万
+$17,571/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$745万
+$17,057/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$712万
+$17,022/呎
+(26年-05月-06日)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1094万
+$20,327/呎
+(26年-08月-17日)</t>
+        </is>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1109万
+$19,354/呎
+(26年-06月-18日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$897万
+$17,192/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$906万
+$17,500/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$742万
+$16,989/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$709万
+$16,955/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -39055,22 +39717,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I5" s="21" t="inlineStr">
-        <is>
-          <t>H | 571呎 (2房)
-$1236万
-$21,651/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1100万
+$19,201/呎
+(26年-06月-23日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39078,7 +39740,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39086,62 +39748,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$933万
-$17,874/呎
-(25年-12月-11日)</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="inlineStr">
+$894万
+$17,125/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$943万
-$18,197/呎
+$903万
+$17,432/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$739万
+$16,920/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$706万
+$16,885/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1076万
+$20,007/呎
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$772万
-$17,664/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-      <c r="G6" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$737万
-$17,627/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1177万
-$21,881/呎
-(26年-08月-12日)</t>
-        </is>
-      </c>
-      <c r="I6" s="21" t="inlineStr">
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1215万
-$21,208/呎
-(26年-06月-17日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
+$1092万
+$19,049/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39149,7 +39811,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39157,62 +39819,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$926万
-$17,749/呎
-(26年-02月-24日)</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
+$890万
+$17,056/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$936万
-$18,068/呎
-(26年-08月-06日)</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
+$899万
+$17,363/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$766万
-$17,538/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
+$736万
+$16,854/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$732万
-$17,505/呎
-(26年-06月-11日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
+$703万
+$16,818/呎
+(25年-11月-13日)</t>
+        </is>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1160万
-$21,556/呎
-(26年-07月-20日)</t>
-        </is>
-      </c>
-      <c r="I7" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1190万
-$20,771/呎
-(26年-06月-11日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
+$1083万
+$18,897/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39220,7 +39882,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39228,62 +39890,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$923万
-$17,678/呎
-(26年-02月-25日)</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="inlineStr">
+$888万
+$17,021/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$932万
-$17,998/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="F8" s="21" t="inlineStr">
+$1056万
+$20,384/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$764万
-$17,471/呎
-(26年-08月-03日)</t>
-        </is>
-      </c>
-      <c r="G8" s="21" t="inlineStr">
+$735万
+$16,819/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$729万
-$17,435/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
+$702万
+$16,787/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I8" s="21" t="inlineStr">
+$1064万
+$19,783/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1172万
-$20,445/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="58" customHeight="1">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
+$1079万
+$18,836/呎
+(25年-10月-09日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39291,7 +39953,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39299,62 +39961,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$894万
-$17,125/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
+$883万
+$16,920/呎
+(25年-12月-09日)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$930万
-$17,961/呎
-(26年-08月-05日)</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
+$892万
+$17,224/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$762万
-$17,435/呎
-(26年-06月-24日)</t>
-        </is>
-      </c>
-      <c r="G9" s="21" t="inlineStr">
+$731万
+$16,721/呎
+(26年-06月-09日)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$753万
-$18,014/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
+$698万
+$16,687/呎
+(25年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1143万
-$21,238/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="I9" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1159万
-$20,222/呎
-(25年-12月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="58" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
+$1069万
+$18,654/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39362,7 +40024,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39370,62 +40032,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$916万
-$17,538/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="inlineStr">
+$880万
+$16,852/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$925万
-$17,853/呎
-(26年-08月-05日)</t>
-        </is>
-      </c>
-      <c r="F10" s="21" t="inlineStr">
+$889万
+$17,156/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$757万
-$17,332/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="G10" s="21" t="inlineStr">
+$728万
+$16,652/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$723万
-$17,297/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H10" s="21" t="inlineStr">
+$719万
+$17,206/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1129万
-$20,987/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="I10" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1145万
-$19,983/呎
-(26年-06月-18日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="58" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
+$1064万
+$18,562/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39433,70 +40095,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
+$2377万
+$26,445/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$876万
+$16,785/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$885万
+$17,087/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$725万
+$16,586/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$692万
+$16,553/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$901万
-$17,264/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$921万
-$17,782/呎
-(26年-07月-15日)</t>
-        </is>
-      </c>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$754万
-$17,263/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="G11" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$720万
-$17,227/呎
-(26年-04月-16日)</t>
-        </is>
-      </c>
-      <c r="H11" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1120万
-$20,818/呎
-(26年-07月-16日)</t>
-        </is>
-      </c>
-      <c r="I11" s="21" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1136万
-$19,824/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="58" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
+$1027万
+$17,925/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39504,70 +40166,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="inlineStr">
+$2348万
+$26,118/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$908万
-$17,398/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="inlineStr">
+$873万
+$16,718/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$918万
-$17,712/呎
-(26年-08月-14日)</t>
-        </is>
-      </c>
-      <c r="F12" s="21" t="inlineStr">
+$882万
+$17,019/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$751万
-$17,192/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-      <c r="G12" s="21" t="inlineStr">
+$722万
+$16,519/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$717万
-$17,158/呎
-(26年-05月-07日)</t>
-        </is>
-      </c>
-      <c r="H12" s="21" t="inlineStr">
+$689万
+$16,488/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1111万
-$20,654/呎
-(26年-08月-09日)</t>
-        </is>
-      </c>
-      <c r="I12" s="21" t="inlineStr">
+$1038万
+$19,301/呎
+(26年-08月-16日)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1127万
-$19,665/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="58" customHeight="1">
-      <c r="A13" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
+$1053万
+$18,379/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39575,716 +40237,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D13" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$905万
-$17,330/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$914万
-$17,641/呎
-(26年-07月-24日)</t>
-        </is>
-      </c>
-      <c r="F13" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$748万
-$17,124/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-      <c r="G13" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$714万
-$17,089/呎
-(26年-05月-08日)</t>
-        </is>
-      </c>
-      <c r="H13" s="22" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I13" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1118万
-$19,510/呎
-(26年-06月-18日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="58" customHeight="1">
-      <c r="A14" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$901万
-$17,261/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="E14" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$910万
-$17,571/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$745万
-$17,057/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-      <c r="G14" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$712万
-$17,022/呎
-(26年-05月-06日)</t>
-        </is>
-      </c>
-      <c r="H14" s="22" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I14" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1109万
-$19,354/呎
-(26年-06月-18日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$897万
-$17,192/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$906万
-$17,500/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="F15" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$742万
-$16,989/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-      <c r="G15" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$709万
-$16,955/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="H15" s="22" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I15" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1100万
-$19,201/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$894万
-$17,125/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$903万
-$17,432/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$739万
-$16,920/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$706万
-$16,885/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1076万
-$20,007/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="I16" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1092万
-$19,049/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$890万
-$17,056/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$899万
-$17,363/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$736万
-$16,854/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="G17" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$703万
-$16,818/呎
-(25年-11月-13日)</t>
-        </is>
-      </c>
-      <c r="H17" s="22" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I17" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1083万
-$18,897/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$888万
-$17,021/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="E18" s="23" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$1056万
-$20,384/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$735万
-$16,819/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$702万
-$16,787/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1064万
-$19,783/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="I18" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1079万
-$18,836/呎
-(25年-10月-09日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$883万
-$16,920/呎
-(25年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$892万
-$17,224/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$731万
-$16,721/呎
-(26年-06月-09日)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$698万
-$16,687/呎
-(25年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="H19" s="22" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1069万
-$18,654/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$880万
-$16,852/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$889万
-$17,156/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$728万
-$16,652/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$719万
-$17,206/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="H20" s="22" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1064万
-$18,562/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2377万
-$26,445/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D21" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$876万
-$16,785/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$885万
-$17,087/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$725万
-$16,586/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$692万
-$16,553/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1027万
-$17,925/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="24" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2348万
-$26,118/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$873万
-$16,718/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$882万
-$17,019/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$722万
-$16,519/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$689万
-$16,488/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I22" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1053万
-$18,379/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
@@ -40325,12 +40277,12 @@
 (25年-09月-26日)</t>
         </is>
       </c>
-      <c r="H23" s="22" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
+$1033万
+$19,204/呎
+(26年-08月-16日)</t>
         </is>
       </c>
       <c r="I23" s="21" t="inlineStr">
@@ -41625,7 +41577,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -41635,7 +41587,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>173</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -42468,7 +42420,78 @@
 (25年-09月-29日)</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1178万
+$20,555/呎
+(26年-08月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$952万
+$17,397/呎
+(25年-11月-21日)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$934万
+$17,362/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1101万
+$20,508/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1048万
+$20,469/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1050万
+$18,958/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42477,13 +42500,13 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42491,7 +42514,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42499,47 +42522,118 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$952万
-$17,397/呎
-(25年-11月-21日)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
+$937万
+$17,122/呎
+(26年-04月-14日)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$934万
-$17,362/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
+$930万
+$17,294/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1101万
-$20,508/呎
+$1097万
+$20,426/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$1048万
-$20,469/呎
+$1044万
+$20,387/呎
 (在售)</t>
         </is>
       </c>
-      <c r="H16" s="21" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1050万
-$18,958/呎
+$1042万
+$18,809/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1159万
+$20,229/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$944万
+$17,258/呎
+(26年-04月-10日)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$927万
+$17,225/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1093万
+$20,346/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1040万
+$20,305/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1034万
+$18,661/呎
 (25年-10月-02日)</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42548,13 +42642,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42562,7 +42656,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42570,62 +42664,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$937万
-$17,122/呎
-(26年-04月-14日)</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
+$940万
+$17,190/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$930万
-$17,294/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
+$923万
+$17,154/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1097万
-$20,426/呎
+$1088万
+$20,264/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$1044万
-$20,387/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
+$880万
+$17,191/呎
+(26年-07月-13日)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1042万
-$18,809/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="I17" s="21" t="inlineStr">
+$1026万
+$18,511/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1159万
-$20,229/呎
-(26年-07月-28日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
+$1141万
+$19,909/呎
+(26年-07月-31日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42633,7 +42727,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42641,47 +42735,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$944万
-$17,258/呎
-(26年-04月-10日)</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
+$938万
+$17,155/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$927万
-$17,225/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
+$921万
+$17,121/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1093万
-$20,346/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="inlineStr">
+$923万
+$17,190/呎
+(26年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$1040万
-$20,305/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
+$878万
+$17,156/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1034万
-$18,661/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I18" s="22" t="inlineStr">
+$1022万
+$18,451/呎
+(25年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42690,13 +42784,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42704,7 +42798,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C21" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42712,62 +42806,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$940万
-$17,190/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
+$933万
+$17,053/呎
+(26年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$923万
-$17,154/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
+$905万
+$16,818/呎
+(26年-03月-09日)</t>
+        </is>
+      </c>
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1088万
-$20,264/呎
+$1080万
+$20,102/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$880万
-$17,191/呎
-(26年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
+$856万
+$16,719/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1026万
-$18,511/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
+$1012万
+$18,274/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1141万
-$19,909/呎
-(26年-07月-31日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
+$1126万
+$19,653/呎
+(26年-08月-07日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42775,7 +42869,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C22" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42783,47 +42877,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$938万
-$17,155/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
+$902万
+$16,484/呎
+(26年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$921万
-$17,121/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
+$912万
+$16,952/呎
+(26年-03月-13日)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$923万
-$17,190/呎
-(26年-08月-08日)</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
+$1075万
+$20,022/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$878万
-$17,156/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
+$853万
+$16,652/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1022万
-$18,451/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
+$996万
+$17,969/呎
+(26年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42832,13 +42926,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42846,7 +42940,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42854,62 +42948,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$933万
-$17,053/呎
-(26年-04月-08日)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
+$914万
+$16,718/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$905万
-$16,818/呎
-(26年-03月-09日)</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="inlineStr">
+$908万
+$16,885/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1080万
-$20,102/呎
+$1071万
+$19,944/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$856万
-$16,719/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="H21" s="21" t="inlineStr">
+$849万
+$16,586/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1012万
-$18,274/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
+$1002万
+$18,092/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1126万
-$19,653/呎
-(26年-08月-07日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42917,7 +43011,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42925,47 +43019,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$902万
-$16,484/呎
-(26年-04月-01日)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
+$922万
+$16,850/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$912万
-$16,952/呎
-(26年-03月-13日)</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
+$894万
+$16,619/呎
+(26年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1075万
-$20,022/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
+$907万
+$16,885/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$853万
-$16,652/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
+$846万
+$16,520/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$996万
-$17,969/呎
+$986万
+$17,791/呎
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42974,13 +43068,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42988,7 +43082,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42996,47 +43090,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$914万
-$16,718/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
+$918万
+$16,782/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$908万
-$16,885/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
+$901万
+$16,751/呎
+(26年-03月-18日)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1071万
-$19,944/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="inlineStr">
+$903万
+$16,816/呎
+(26年-08月-10日)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$849万
-$16,586/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
+$842万
+$16,453/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1002万
-$18,092/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I23" s="22" t="inlineStr">
+$992万
+$17,913/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43045,13 +43139,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43059,7 +43153,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43067,148 +43161,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$922万
-$16,850/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$894万
-$16,619/呎
-(26年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$907万
-$16,885/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$846万
-$16,520/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="H24" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$986万
-$17,791/呎
-(26年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="I24" s="22" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$918万
-$16,782/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$901万
-$16,751/呎
-(26年-03月-18日)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$903万
-$16,816/呎
-(26年-08月-10日)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$842万
-$16,453/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$992万
-$17,913/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="I25" s="22" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
@@ -43225,12 +43177,12 @@
 (26年-03月-02日)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1058万
-$19,706/呎
-(在售)</t>
+$900万
+$16,750/呎
+(26年-08月-15日)</t>
         </is>
       </c>
       <c r="G26" s="21" t="inlineStr">

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -127,13 +127,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
@@ -278,10 +278,10 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5966,38 +5966,30 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H84" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>10849000</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>20165</v>
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K84" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L84" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K84" s="5" t="n">
+        <v>10849000</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>20165</v>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
@@ -6006,7 +5998,7 @@
       </c>
       <c r="N84" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -6998,38 +6990,30 @@
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I100" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>10678000</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>19848</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K100" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L100" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K100" s="5" t="n">
+        <v>10678000</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>19848</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
@@ -7038,7 +7022,7 @@
       </c>
       <c r="N100" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -10590,38 +10574,30 @@
       </c>
       <c r="F156" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H156" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I156" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H156" s="5" t="n">
+        <v>10281000</v>
+      </c>
+      <c r="I156" s="5" t="n">
+        <v>19110</v>
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K156" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L156" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K156" s="5" t="n">
+        <v>10281000</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>19110</v>
       </c>
       <c r="M156" s="3" t="inlineStr">
         <is>
@@ -10630,7 +10606,7 @@
       </c>
       <c r="N156" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -13627,7 +13603,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -19416,34 +19392,34 @@
       </c>
       <c r="F295" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
-        <v>11782000</v>
+        <v>10015000</v>
       </c>
       <c r="I295" s="5" t="n">
-        <v>21900</v>
+        <v>18615</v>
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K295" s="5" t="n">
-        <v>10014700</v>
+        <v>10015000</v>
       </c>
       <c r="L295" s="5" t="n">
         <v>18615</v>
       </c>
       <c r="M295" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N295" s="3" t="inlineStr">
@@ -20456,34 +20432,34 @@
       </c>
       <c r="F311" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
-        <v>11619000</v>
+        <v>9876000</v>
       </c>
       <c r="I311" s="5" t="n">
-        <v>21597</v>
+        <v>18357</v>
       </c>
       <c r="J311" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K311" s="5" t="n">
-        <v>9876150</v>
+        <v>9876000</v>
       </c>
       <c r="L311" s="5" t="n">
         <v>18357</v>
       </c>
       <c r="M311" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N311" s="3" t="inlineStr">
@@ -20976,34 +20952,34 @@
       </c>
       <c r="F319" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
-        <v>11573000</v>
+        <v>9837000</v>
       </c>
       <c r="I319" s="5" t="n">
-        <v>21511</v>
+        <v>18284</v>
       </c>
       <c r="J319" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K319" s="5" t="n">
-        <v>9837050</v>
+        <v>9837000</v>
       </c>
       <c r="L319" s="5" t="n">
         <v>18284</v>
       </c>
       <c r="M319" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N319" s="3" t="inlineStr">
@@ -23816,38 +23792,30 @@
       </c>
       <c r="F363" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H363" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I363" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="H363" s="5" t="n">
+        <v>11871000</v>
+      </c>
+      <c r="I363" s="5" t="n">
+        <v>20717</v>
       </c>
       <c r="J363" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K363" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L363" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K363" s="5" t="n">
+        <v>11871000</v>
+      </c>
+      <c r="L363" s="5" t="n">
+        <v>20717</v>
       </c>
       <c r="M363" s="3" t="inlineStr">
         <is>
@@ -23856,7 +23824,7 @@
       </c>
       <c r="N363" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26012,34 +25980,34 @@
       </c>
       <c r="F397" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G397" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="H397" s="5" t="n">
-        <v>10396000</v>
+        <v>8837000</v>
       </c>
       <c r="I397" s="5" t="n">
-        <v>20305</v>
+        <v>17260</v>
       </c>
       <c r="J397" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K397" s="5" t="n">
-        <v>8836600</v>
+        <v>8837000</v>
       </c>
       <c r="L397" s="5" t="n">
-        <v>17259</v>
+        <v>17260</v>
       </c>
       <c r="M397" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N397" s="3" t="inlineStr">
@@ -26405,7 +26373,7 @@
       </c>
       <c r="G403" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H403" s="5" t="n">
@@ -26912,38 +26880,30 @@
       </c>
       <c r="F411" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G411" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H411" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I411" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H411" s="5" t="n">
+        <v>11370000</v>
+      </c>
+      <c r="I411" s="5" t="n">
+        <v>19843</v>
       </c>
       <c r="J411" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K411" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L411" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K411" s="5" t="n">
+        <v>11370000</v>
+      </c>
+      <c r="L411" s="5" t="n">
+        <v>19843</v>
       </c>
       <c r="M411" s="3" t="inlineStr">
         <is>
@@ -26952,7 +26912,7 @@
       </c>
       <c r="N411" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -28658,34 +28618,34 @@
       </c>
       <c r="F438" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G438" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="H438" s="5" t="n">
-        <v>10710000</v>
+        <v>9104000</v>
       </c>
       <c r="I438" s="5" t="n">
-        <v>19944</v>
+        <v>16953</v>
       </c>
       <c r="J438" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K438" s="5" t="n">
-        <v>9103500</v>
+        <v>9104000</v>
       </c>
       <c r="L438" s="5" t="n">
         <v>16953</v>
       </c>
       <c r="M438" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N438" s="3" t="inlineStr">
@@ -33648,38 +33608,30 @@
       </c>
       <c r="F515" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G515" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H515" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I515" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="H515" s="5" t="n">
+        <v>10607000</v>
+      </c>
+      <c r="I515" s="5" t="n">
+        <v>18511</v>
       </c>
       <c r="J515" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K515" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L515" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K515" s="5" t="n">
+        <v>10607000</v>
+      </c>
+      <c r="L515" s="5" t="n">
+        <v>18511</v>
       </c>
       <c r="M515" s="3" t="inlineStr">
         <is>
@@ -33688,7 +33640,7 @@
       </c>
       <c r="N515" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38874,7 +38826,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -38884,7 +38836,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>205</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -39709,7 +39661,291 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="H15" s="22" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1085万
+$20,165/呎
+(26年-08月-18日)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1100万
+$19,201/呎
+(26年-06月-23日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$894万
+$17,125/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$903万
+$17,432/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$739万
+$16,920/呎
+(26年-06月-03日)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$706万
+$16,885/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1076万
+$20,007/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1092万
+$19,049/呎
+(26年-06月-25日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$890万
+$17,056/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$899万
+$17,363/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$736万
+$16,854/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$703万
+$16,818/呎
+(25年-11月-13日)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1068万
+$19,848/呎
+(26年-08月-20日)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1083万
+$18,897/呎
+(26年-06月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$888万
+$17,021/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$1056万
+$20,384/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$735万
+$16,819/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$702万
+$16,787/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
+        <is>
+          <t>G | 538呎 (2房)
+$1064万
+$19,783/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1079万
+$18,836/呎
+(25年-10月-09日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>C | 522呎 (2房)
+$883万
+$16,920/呎
+(25年-12月-09日)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$892万
+$17,224/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$731万
+$16,721/呎
+(26年-06月-09日)</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$698万
+$16,687/呎
+(25年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -39717,22 +39953,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I15" s="21" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1100万
-$19,201/呎
-(26年-06月-23日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
+$1069万
+$18,654/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39740,7 +39976,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -39748,62 +39984,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$894万
-$17,125/呎
+$880万
+$16,852/呎
 (25年-09月-26日)</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$903万
-$17,432/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F16" s="21" t="inlineStr">
+$889万
+$17,156/呎
+(26年-07月-06日)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$739万
-$16,920/呎
-(26年-06月-03日)</t>
-        </is>
-      </c>
-      <c r="G16" s="21" t="inlineStr">
+$728万
+$16,652/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$706万
-$16,885/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
+$719万
+$17,206/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1076万
-$20,007/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="I16" s="21" t="inlineStr">
+招标单位
+-
+(在售)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1092万
-$19,049/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
+$1064万
+$18,562/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39811,47 +40047,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
+$2377万
+$26,445/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$890万
-$17,056/呎
+$876万
+$16,785/呎
 (25年-09月-30日)</t>
         </is>
       </c>
-      <c r="E17" s="21" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$899万
-$17,363/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="F17" s="21" t="inlineStr">
+$885万
+$17,087/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$736万
-$16,854/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="G17" s="21" t="inlineStr">
+$725万
+$16,586/呎
+(26年-06月-08日)</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$703万
-$16,818/呎
-(25年-11月-13日)</t>
-        </is>
-      </c>
-      <c r="H17" s="22" t="inlineStr">
+$692万
+$16,553/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
 招标单位
@@ -39859,22 +40095,22 @@
 (在售)</t>
         </is>
       </c>
-      <c r="I17" s="21" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1083万
-$18,897/呎
-(26年-06月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
+$1027万
+$17,925/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39882,70 +40118,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
+$2348万
+$26,118/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$888万
-$17,021/呎
+$873万
+$16,718/呎
 (25年-10月-02日)</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$1056万
-$20,384/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F18" s="21" t="inlineStr">
+$882万
+$17,019/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$735万
-$16,819/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="G18" s="21" t="inlineStr">
+$722万
+$16,519/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="G22" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$702万
-$16,787/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H18" s="21" t="inlineStr">
+$689万
+$16,488/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1064万
-$19,783/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="I18" s="21" t="inlineStr">
+$1038万
+$19,301/呎
+(26年-08月-16日)</t>
+        </is>
+      </c>
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1079万
-$18,836/呎
-(25年-10月-09日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
+$1053万
+$18,379/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -39953,70 +40189,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
+$2318万
+$25,783/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$883万
-$16,920/呎
-(25年-12月-09日)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
+$869万
+$16,651/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$892万
-$17,224/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="F19" s="21" t="inlineStr">
+$878万
+$16,952/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$731万
-$16,721/呎
-(26年-06月-09日)</t>
-        </is>
-      </c>
-      <c r="G19" s="21" t="inlineStr">
+$719万
+$16,455/呎
+(26年-04月-21日)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$698万
-$16,687/呎
-(25年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="H19" s="22" t="inlineStr">
+$711万
+$17,002/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
+$1033万
+$19,204/呎
+(26年-08月-16日)</t>
+        </is>
+      </c>
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1069万
-$18,654/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
+$1048万
+$18,286/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40024,70 +40260,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
+$2288万
+$25,452/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$880万
-$16,852/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
+$856万
+$16,389/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$889万
-$17,156/呎
-(26年-07月-06日)</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
+$875万
+$16,884/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$728万
-$16,652/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
+$716万
+$16,389/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$719万
-$17,206/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="H20" s="22" t="inlineStr">
+$684万
+$16,356/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
+$1028万
+$19,110/呎
+(26年-08月-18日)</t>
+        </is>
+      </c>
+      <c r="I24" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1064万
-$18,562/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
+$1043万
+$18,195/呎
+(26年-06月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40095,70 +40331,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2377万
-$26,445/呎
+$2259万
+$25,125/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$876万
-$16,785/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
+$883万
+$16,908/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$885万
-$17,087/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="F21" s="21" t="inlineStr">
+$871万
+$16,817/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$725万
-$16,586/呎
-(26年-06月-08日)</t>
-        </is>
-      </c>
-      <c r="G21" s="21" t="inlineStr">
+$713万
+$16,323/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$692万
-$16,553/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="H21" s="22" t="inlineStr">
+$681万
+$16,289/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
+$1023万
+$19,015/呎
+(26年-08月-09日)</t>
+        </is>
+      </c>
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1027万
-$17,925/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
+$1074万
+$18,743/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40166,70 +40402,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2348万
-$26,118/呎
+$2230万
+$24,803/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$873万
-$16,718/呎
+$859万
+$16,452/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$868万
+$16,749/呎
+(26年-06月-26日)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$710万
+$16,259/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$702万
+$16,799/呎
 (25年-10月-02日)</t>
         </is>
       </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$882万
-$17,019/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F22" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$722万
-$16,519/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$689万
-$16,488/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1038万
-$19,301/呎
-(26年-08月-16日)</t>
-        </is>
-      </c>
-      <c r="I22" s="21" t="inlineStr">
+$1018万
+$18,920/呎
+(26年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="I26" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1053万
-$18,379/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
+$1069万
+$18,651/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40237,70 +40473,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C27" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2318万
-$25,783/呎
+$2215万
+$24,643/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$869万
-$16,651/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
+$857万
+$16,420/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$878万
-$16,952/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F23" s="21" t="inlineStr">
+$866万
+$16,716/呎
+(26年-06月-30日)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$719万
-$16,455/呎
-(26年-04月-21日)</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="inlineStr">
+$709万
+$16,227/呎
+(26年-02月-27日)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$711万
-$17,002/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
+$677万
+$16,194/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1033万
-$19,204/呎
-(26年-08月-16日)</t>
-        </is>
-      </c>
-      <c r="I23" s="21" t="inlineStr">
+$1015万
+$18,872/呎
+(26年-07月-09日)</t>
+        </is>
+      </c>
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1048万
-$18,286/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
+$1030万
+$17,970/呎
+(25年-10月-10日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40308,70 +40544,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C28" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2288万
-$25,452/呎
+$2173万
+$24,171/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$856万
-$16,389/呎
+$852万
+$16,322/呎
+(25年-10月-10日)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 518呎 (2房)
+$861万
+$16,616/呎
+(26年-07月-03日)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
+        <is>
+          <t>E | 437呎 (1房)
+$705万
+$16,128/呎
+(26年-03月-20日)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
+        <is>
+          <t>F | 418呎 (1房)
+$673万
+$16,098/呎
 (25年-10月-03日)</t>
         </is>
       </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$875万
-$16,884/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$716万
-$16,389/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$684万
-$16,356/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="H24" s="22" t="inlineStr">
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="I24" s="21" t="inlineStr">
+$1008万
+$18,732/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="I28" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1043万
-$18,195/呎
-(26年-06月-02日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
+$1022万
+$17,836/呎
+(26年-03月-31日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40379,70 +40615,70 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
-$2259万
-$25,125/呎
+$2145万
+$23,861/呎
 (暂停销售)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 522呎 (2房)
-$883万
-$16,908/呎
+$849万
+$16,257/呎
 (25年-09月-29日)</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$871万
-$16,817/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
+$857万
+$16,550/呎
+(26年-07月-02日)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 437呎 (1房)
-$713万
-$16,323/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
+$702万
+$16,064/呎
+(25年-11月-28日)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>F | 418呎 (1房)
-$681万
-$16,289/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
+$670万
+$16,033/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-$1023万
-$19,015/呎
-(26年-08月-09日)</t>
-        </is>
-      </c>
-      <c r="I25" s="21" t="inlineStr">
+$1003万
+$18,638/呎
+(26年-07月-10日)</t>
+        </is>
+      </c>
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1074万
-$18,743/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
+$1017万
+$17,747/呎
+(26年-04月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -40450,290 +40686,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2230万
-$24,803/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D26" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$859万
-$16,452/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$868万
-$16,749/呎
-(26年-06月-26日)</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$710万
-$16,259/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$702万
-$16,799/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="H26" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1018万
-$18,920/呎
-(26年-08月-08日)</t>
-        </is>
-      </c>
-      <c r="I26" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1069万
-$18,651/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="24" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2215万
-$24,643/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$857万
-$16,420/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$866万
-$16,716/呎
-(26年-06月-30日)</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$709万
-$16,227/呎
-(26年-02月-27日)</t>
-        </is>
-      </c>
-      <c r="G27" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$677万
-$16,194/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1015万
-$18,872/呎
-(26年-07月-09日)</t>
-        </is>
-      </c>
-      <c r="I27" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1030万
-$17,970/呎
-(25年-10月-10日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="24" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2173万
-$24,171/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$852万
-$16,322/呎
-(25年-10月-10日)</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$861万
-$16,616/呎
-(26年-07月-03日)</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$705万
-$16,128/呎
-(26年-03月-20日)</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$673万
-$16,098/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1008万
-$18,732/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="I28" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1022万
-$17,836/呎
-(26年-03月-31日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C29" s="24" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
-$2145万
-$23,861/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D29" s="21" t="inlineStr">
-        <is>
-          <t>C | 522呎 (2房)
-$849万
-$16,257/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="inlineStr">
-        <is>
-          <t>D | 518呎 (2房)
-$857万
-$16,550/呎
-(26年-07月-02日)</t>
-        </is>
-      </c>
-      <c r="F29" s="21" t="inlineStr">
-        <is>
-          <t>E | 437呎 (1房)
-$702万
-$16,064/呎
-(25年-11月-28日)</t>
-        </is>
-      </c>
-      <c r="G29" s="21" t="inlineStr">
-        <is>
-          <t>F | 418呎 (1房)
-$670万
-$16,033/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
-        <is>
-          <t>G | 538呎 (2房)
-$1003万
-$18,638/呎
-(26年-07月-10日)</t>
-        </is>
-      </c>
-      <c r="I29" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1017万
-$17,747/呎
-(26年-04月-22日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="C30" s="24" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
@@ -40779,7 +40731,7 @@
           <t>G | 538呎 (2房)
 $998万
 $18,546/呎
-(26年-07月-29日)</t>
+(26年-08月-21日)</t>
         </is>
       </c>
       <c r="I30" s="21" t="inlineStr">
@@ -41577,7 +41529,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -41587,7 +41539,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>181</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -41678,15 +41630,15 @@
 (26年-05月-14日)</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$1178万
-$21,900/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F5" s="22" t="inlineStr">
+$1002万
+$18,615/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1158万
@@ -41694,7 +41646,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G5" s="22" t="inlineStr">
+      <c r="G5" s="23" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
 $1102万
@@ -41710,7 +41662,7 @@
 (26年-07月-13日)</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="23" t="inlineStr">
         <is>
           <t>H | 571呎 (2房)
 招标单位
@@ -41757,7 +41709,7 @@
 (26年-08月-05日)</t>
         </is>
       </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1150万
@@ -41765,7 +41717,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
 $1094万
@@ -41781,7 +41733,7 @@
 (26年-05月-14日)</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="23" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -41820,15 +41772,15 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$1162万
-$21,597/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F7" s="22" t="inlineStr">
+$988万
+$18,357/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1142万
@@ -41836,7 +41788,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
 $1086万
@@ -41852,7 +41804,7 @@
 (26年-05月-05日)</t>
         </is>
       </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -41891,15 +41843,15 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$1157万
-$21,511/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
+$984万
+$18,284/呎
+(26年-08月-18日)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1137万
@@ -41907,7 +41859,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
 $1082万
@@ -41923,7 +41875,7 @@
 (26年-06月-04日)</t>
         </is>
       </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="I8" s="23" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -41970,7 +41922,7 @@
 (26年-08月-08日)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1132万
@@ -41978,7 +41930,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
 $1078万
@@ -41994,7 +41946,7 @@
 (26年-06月-02日)</t>
         </is>
       </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="I9" s="23" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42041,7 +41993,7 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1128万
@@ -42049,7 +42001,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
 $1073万
@@ -42183,7 +42135,7 @@
 (26年-05月-15日)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1119万
@@ -42254,7 +42206,7 @@
 (25年-09月-30日)</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1115万
@@ -42325,7 +42277,7 @@
 (26年-05月-15日)</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1110万
@@ -42349,7 +42301,149 @@
 (25年-09月-30日)</t>
         </is>
       </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1187万
+$20,717/呎
+(26年-08月-18日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$955万
+$17,466/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$938万
+$17,431/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1106万
+$20,590/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$877万
+$17,125/呎
+(26年-06月-09日)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1059万
+$19,112/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1178万
+$20,555/呎
+(26年-08月-15日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$952万
+$17,397/呎
+(25年-11月-21日)</t>
+        </is>
+      </c>
+      <c r="E16" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$934万
+$17,362/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1101万
+$20,508/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$1048万
+$20,469/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1050万
+$18,958/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42358,13 +42452,13 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="58" customHeight="1">
-      <c r="A15" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42372,7 +42466,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42380,62 +42474,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$955万
-$17,466/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="E15" s="21" t="inlineStr">
+$937万
+$17,122/呎
+(26年-04月-14日)</t>
+        </is>
+      </c>
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$938万
-$17,431/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
+$930万
+$17,294/呎
+(26年-05月-12日)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1106万
-$20,590/呎
+$1097万
+$20,426/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$877万
-$17,125/呎
-(26年-06月-09日)</t>
-        </is>
-      </c>
-      <c r="H15" s="21" t="inlineStr">
+$1044万
+$20,387/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1059万
-$19,112/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="I15" s="21" t="inlineStr">
+$1042万
+$18,809/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1178万
-$20,555/呎
-(26年-08月-15日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="58" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
+$1159万
+$20,229/呎
+(26年-07月-28日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42443,7 +42537,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C18" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42451,47 +42545,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$952万
-$17,397/呎
-(25年-11月-21日)</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
+$944万
+$17,258/呎
+(26年-04月-10日)</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$934万
-$17,362/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
+$927万
+$17,225/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1101万
-$20,508/呎
+$1093万
+$20,346/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$1048万
-$20,469/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H16" s="21" t="inlineStr">
+$884万
+$17,260/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="H18" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1050万
-$18,958/呎
+$1034万
+$18,661/呎
 (25年-10月-02日)</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42500,13 +42594,13 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="58" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42514,7 +42608,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42522,62 +42616,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D17" s="21" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$937万
-$17,122/呎
-(26年-04月-14日)</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="inlineStr">
+$940万
+$17,190/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$930万
-$17,294/呎
-(26年-05月-12日)</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
+$923万
+$17,154/呎
+(26年-05月-13日)</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1097万
-$20,426/呎
+$1088万
+$20,264/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$1044万
-$20,387/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H17" s="21" t="inlineStr">
+$880万
+$17,191/呎
+(26年-07月-13日)</t>
+        </is>
+      </c>
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1042万
-$18,809/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="I17" s="21" t="inlineStr">
+$1026万
+$18,511/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-$1159万
-$20,229/呎
-(26年-07月-28日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="58" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
+$1141万
+$19,909/呎
+(26年-08月-24日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42585,7 +42679,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42593,47 +42687,189 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D18" s="21" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$944万
-$17,258/呎
-(26年-04月-10日)</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="inlineStr">
+$938万
+$17,155/呎
+(26年-04月-13日)</t>
+        </is>
+      </c>
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$927万
-$17,225/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
+$921万
+$17,121/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1093万
-$20,346/呎
+$923万
+$17,190/呎
+(26年-08月-08日)</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$878万
+$17,156/呎
+(26年-07月-07日)</t>
+        </is>
+      </c>
+      <c r="H20" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1022万
+$18,451/呎
+(25年-10月-08日)</t>
+        </is>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1137万
+$19,843/呎
+(26年-08月-22日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$933万
+$17,053/呎
+(26年-04月-08日)</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$905万
+$16,818/呎
+(26年-03月-09日)</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1080万
+$20,102/呎
 (在售)</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$1040万
-$20,305/呎
+$856万
+$16,719/呎
+(26年-06月-01日)</t>
+        </is>
+      </c>
+      <c r="H21" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1012万
+$18,274/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="I21" s="21" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+$1126万
+$19,653/呎
+(26年-08月-07日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 912呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 899呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>C | 547呎 (2房)
+$902万
+$16,484/呎
+(26年-04月-01日)</t>
+        </is>
+      </c>
+      <c r="E22" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
+$912万
+$16,952/呎
+(26年-03月-13日)</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>E | 537呎 (2房)
+$1075万
+$20,022/呎
 (在售)</t>
         </is>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="G22" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$853万
+$16,652/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="H22" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1034万
-$18,661/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I18" s="22" t="inlineStr">
+$996万
+$17,969/呎
+(26年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="I22" s="23" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42642,13 +42878,13 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="58" customHeight="1">
-      <c r="A19" s="19" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42656,7 +42892,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
+      <c r="C23" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42664,62 +42900,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D23" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$940万
-$17,190/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="inlineStr">
+$914万
+$16,718/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$923万
-$17,154/呎
-(26年-05月-13日)</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
+$908万
+$16,885/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1088万
-$20,264/呎
+$910万
+$16,953/呎
+(26年-08月-23日)</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$849万
+$16,586/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="H23" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$1002万
+$18,092/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I23" s="23" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
 (在售)</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$880万
-$17,191/呎
-(26年-07月-13日)</t>
-        </is>
-      </c>
-      <c r="H19" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1026万
-$18,511/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1141万
-$19,909/呎
-(26年-07月-31日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="58" customHeight="1">
-      <c r="A20" s="19" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42727,7 +42963,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C24" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42735,47 +42971,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D20" s="21" t="inlineStr">
+      <c r="D24" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$938万
-$17,155/呎
-(26年-04月-13日)</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
+$922万
+$16,850/呎
+(26年-04月-09日)</t>
+        </is>
+      </c>
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$921万
-$17,121/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="F20" s="21" t="inlineStr">
+$894万
+$16,619/呎
+(26年-03月-10日)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$923万
-$17,190/呎
-(26年-08月-08日)</t>
-        </is>
-      </c>
-      <c r="G20" s="21" t="inlineStr">
+$907万
+$16,885/呎
+(26年-07月-08日)</t>
+        </is>
+      </c>
+      <c r="G24" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$878万
-$17,156/呎
-(26年-07月-07日)</t>
-        </is>
-      </c>
-      <c r="H20" s="21" t="inlineStr">
+$846万
+$16,520/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="H24" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1022万
-$18,451/呎
-(25年-10月-08日)</t>
-        </is>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
+$986万
+$17,791/呎
+(26年-03月-27日)</t>
+        </is>
+      </c>
+      <c r="I24" s="23" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42784,13 +43020,13 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="58" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B21" s="20" t="inlineStr">
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42798,7 +43034,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
+      <c r="C25" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42806,62 +43042,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D25" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$933万
-$17,053/呎
-(26年-04月-08日)</t>
-        </is>
-      </c>
-      <c r="E21" s="21" t="inlineStr">
+$918万
+$16,782/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$905万
-$16,818/呎
-(26年-03月-09日)</t>
-        </is>
-      </c>
-      <c r="F21" s="22" t="inlineStr">
+$901万
+$16,751/呎
+(26年-03月-18日)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1080万
-$20,102/呎
+$903万
+$16,816/呎
+(26年-08月-10日)</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
+        <is>
+          <t>F | 512呎 (2房)
+$842万
+$16,453/呎
+(26年-05月-21日)</t>
+        </is>
+      </c>
+      <c r="H25" s="21" t="inlineStr">
+        <is>
+          <t>G | 554呎 (2房)
+$992万
+$17,913/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="I25" s="23" t="inlineStr">
+        <is>
+          <t>H | 573呎 (2房)
+招标单位
+-
 (在售)</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$856万
-$16,719/呎
-(26年-06月-01日)</t>
-        </is>
-      </c>
-      <c r="H21" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$1012万
-$18,274/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="I21" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1126万
-$19,653/呎
-(26年-08月-07日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="58" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B22" s="20" t="inlineStr">
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42869,7 +43105,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42877,47 +43113,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D22" s="21" t="inlineStr">
+      <c r="D26" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$902万
-$16,484/呎
-(26年-04月-01日)</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
+$914万
+$16,715/呎
+(26年-04月-10日)</t>
+        </is>
+      </c>
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$912万
-$16,952/呎
-(26年-03月-13日)</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
+$887万
+$16,487/呎
+(26年-03月-02日)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1075万
-$20,022/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G22" s="21" t="inlineStr">
+$900万
+$16,750/呎
+(26年-08月-15日)</t>
+        </is>
+      </c>
+      <c r="G26" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$853万
-$16,652/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="H22" s="21" t="inlineStr">
+$839万
+$16,389/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="H26" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$996万
-$17,969/呎
-(26年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="I22" s="22" t="inlineStr">
+$987万
+$17,823/呎
+(26年-03月-31日)</t>
+        </is>
+      </c>
+      <c r="I26" s="23" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42926,13 +43162,13 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="58" customHeight="1">
-      <c r="A23" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B23" s="20" t="inlineStr">
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -42940,7 +43176,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C27" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -42948,47 +43184,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D23" s="21" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$914万
-$16,718/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="E23" s="21" t="inlineStr">
+$911万
+$16,649/呎
+(26年-04月-15日)</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$908万
-$16,885/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="F23" s="22" t="inlineStr">
+$894万
+$16,615/呎
+(26年-03月-25日)</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1071万
-$19,944/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="G23" s="21" t="inlineStr">
+$878万
+$16,356/呎
+(26年-06月-04日)</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$849万
-$16,586/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="H23" s="21" t="inlineStr">
+$836万
+$16,324/呎
+(26年-03月-25日)</t>
+        </is>
+      </c>
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$1002万
-$18,092/呎
+$982万
+$17,735/呎
 (25年-10月-02日)</t>
         </is>
       </c>
-      <c r="I23" s="22" t="inlineStr">
+      <c r="I27" s="23" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42997,13 +43233,13 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43011,7 +43247,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
+      <c r="C28" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43019,47 +43255,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D24" s="21" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
+$907万
+$16,581/呎
+(26年-04月-23日)</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="inlineStr">
+        <is>
+          <t>D | 538呎 (2房)
 $922万
-$16,850/呎
-(26年-04月-09日)</t>
-        </is>
-      </c>
-      <c r="E24" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$894万
-$16,619/呎
-(26年-03月-10日)</t>
-        </is>
-      </c>
-      <c r="F24" s="21" t="inlineStr">
+$17,134/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$907万
-$16,885/呎
-(26年-07月-08日)</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="inlineStr">
+$875万
+$16,291/呎
+(26年-05月-26日)</t>
+        </is>
+      </c>
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$846万
-$16,520/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="H24" s="21" t="inlineStr">
+$832万
+$16,258/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="H28" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$986万
-$17,791/呎
-(26年-03月-27日)</t>
-        </is>
-      </c>
-      <c r="I24" s="22" t="inlineStr">
+$978万
+$17,648/呎
+(25年-10月-03日)</t>
+        </is>
+      </c>
+      <c r="I28" s="23" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43068,13 +43304,13 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="58" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B25" s="20" t="inlineStr">
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43082,7 +43318,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
+      <c r="C29" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43090,47 +43326,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D29" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$918万
-$16,782/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
+$905万
+$16,550/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$901万
-$16,751/呎
-(26年-03月-18日)</t>
-        </is>
-      </c>
-      <c r="F25" s="21" t="inlineStr">
+$889万
+$16,517/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$903万
-$16,816/呎
-(26年-08月-10日)</t>
-        </is>
-      </c>
-      <c r="G25" s="21" t="inlineStr">
+$873万
+$16,259/呎
+(25年-09月-26日)</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$842万
-$16,453/呎
-(26年-05月-21日)</t>
-        </is>
-      </c>
-      <c r="H25" s="21" t="inlineStr">
+$831万
+$16,227/呎
+(25年-10月-06日)</t>
+        </is>
+      </c>
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$992万
-$17,913/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="I25" s="22" t="inlineStr">
+$964万
+$17,395/呎
+(26年-04月-02日)</t>
+        </is>
+      </c>
+      <c r="I29" s="23" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43139,13 +43375,13 @@
         </is>
       </c>
     </row>
-    <row r="26" ht="58" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B26" s="20" t="inlineStr">
+    <row r="30" ht="58" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43153,7 +43389,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
+      <c r="C30" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43161,47 +43397,47 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D26" s="21" t="inlineStr">
+      <c r="D30" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$914万
-$16,715/呎
-(26年-04月-10日)</t>
-        </is>
-      </c>
-      <c r="E26" s="21" t="inlineStr">
+$900万
+$16,452/呎
+(26年-04月-24日)</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$887万
-$16,487/呎
-(26年-03月-02日)</t>
-        </is>
-      </c>
-      <c r="F26" s="21" t="inlineStr">
+$883万
+$16,418/呎
+(25年-09月-30日)</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$900万
-$16,750/呎
-(26年-08月-15日)</t>
-        </is>
-      </c>
-      <c r="G26" s="21" t="inlineStr">
+$868万
+$16,162/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="G30" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$839万
-$16,389/呎
+$826万
+$16,131/呎
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="H26" s="21" t="inlineStr">
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$987万
-$17,823/呎
-(26年-03月-31日)</t>
-        </is>
-      </c>
-      <c r="I26" s="22" t="inlineStr">
+$968万
+$17,471/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I30" s="23" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43210,13 +43446,13 @@
         </is>
       </c>
     </row>
-    <row r="27" ht="58" customHeight="1">
-      <c r="A27" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B27" s="20" t="inlineStr">
+    <row r="31" ht="58" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43224,7 +43460,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
+      <c r="C31" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43232,62 +43468,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D27" s="21" t="inlineStr">
+      <c r="D31" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$911万
-$16,649/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="E27" s="21" t="inlineStr">
+$896万
+$16,384/呎
+(26年-04月-27日)</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$894万
-$16,615/呎
-(26年-03月-25日)</t>
-        </is>
-      </c>
-      <c r="F27" s="21" t="inlineStr">
+$870万
+$16,162/呎
+(25年-09月-29日)</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$878万
-$16,356/呎
-(26年-06月-04日)</t>
-        </is>
-      </c>
-      <c r="G27" s="21" t="inlineStr">
+$864万
+$16,099/呎
+(26年-05月-22日)</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$836万
-$16,324/呎
-(26年-03月-25日)</t>
-        </is>
-      </c>
-      <c r="H27" s="21" t="inlineStr">
+$822万
+$16,064/呎
+(26年-03月-09日)</t>
+        </is>
+      </c>
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$982万
-$17,735/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I27" s="22" t="inlineStr">
+$963万
+$17,384/呎
+(26年-03月-19日)</t>
+        </is>
+      </c>
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="58" customHeight="1">
-      <c r="A28" s="19" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="B28" s="20" t="inlineStr">
+$1071万
+$18,696/呎
+(26年-08月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="58" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43295,7 +43531,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C32" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43303,62 +43539,62 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D28" s="21" t="inlineStr">
+      <c r="D32" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
-$907万
-$16,581/呎
-(26年-04月-23日)</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
+$893万
+$16,320/呎
+(26年-05月-18日)</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>D | 538呎 (2房)
-$922万
-$17,134/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="F28" s="21" t="inlineStr">
+$876万
+$16,288/呎
+(25年-11月-28日)</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$875万
-$16,291/呎
-(26年-05月-26日)</t>
-        </is>
-      </c>
-      <c r="G28" s="21" t="inlineStr">
+$861万
+$16,034/呎
+(26年-06月-05日)</t>
+        </is>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$832万
-$16,258/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="H28" s="21" t="inlineStr">
+$819万
+$16,000/呎
+(26年-04月-14日)</t>
+        </is>
+      </c>
+      <c r="H32" s="21" t="inlineStr">
         <is>
           <t>G | 554呎 (2房)
-$978万
-$17,648/呎
-(25年-10月-03日)</t>
-        </is>
-      </c>
-      <c r="I28" s="22" t="inlineStr">
+$992万
+$17,908/呎
+(25年-10月-02日)</t>
+        </is>
+      </c>
+      <c r="I32" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="58" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B29" s="20" t="inlineStr">
+$1066万
+$18,604/呎
+(26年-07月-13日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="58" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>A | 912呎 (3房)
 -
@@ -43366,7 +43602,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr">
+      <c r="C33" s="20" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 -
@@ -43374,290 +43610,6 @@
 (待售)</t>
         </is>
       </c>
-      <c r="D29" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$905万
-$16,550/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="E29" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$889万
-$16,517/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="F29" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$873万
-$16,259/呎
-(25年-09月-26日)</t>
-        </is>
-      </c>
-      <c r="G29" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$831万
-$16,227/呎
-(25年-10月-06日)</t>
-        </is>
-      </c>
-      <c r="H29" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$964万
-$17,395/呎
-(26年-04月-02日)</t>
-        </is>
-      </c>
-      <c r="I29" s="22" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="58" customHeight="1">
-      <c r="A30" s="19" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B30" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D30" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$900万
-$16,452/呎
-(26年-04月-24日)</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$883万
-$16,418/呎
-(25年-09月-30日)</t>
-        </is>
-      </c>
-      <c r="F30" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$868万
-$16,162/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="G30" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$826万
-$16,131/呎
-(26年-04月-15日)</t>
-        </is>
-      </c>
-      <c r="H30" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$968万
-$17,471/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I30" s="22" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="58" customHeight="1">
-      <c r="A31" s="19" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B31" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D31" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$896万
-$16,384/呎
-(26年-04月-27日)</t>
-        </is>
-      </c>
-      <c r="E31" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$870万
-$16,162/呎
-(25年-09月-29日)</t>
-        </is>
-      </c>
-      <c r="F31" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$864万
-$16,099/呎
-(26年-05月-22日)</t>
-        </is>
-      </c>
-      <c r="G31" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$822万
-$16,064/呎
-(26年-03月-09日)</t>
-        </is>
-      </c>
-      <c r="H31" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$963万
-$17,384/呎
-(26年-03月-19日)</t>
-        </is>
-      </c>
-      <c r="I31" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1071万
-$18,696/呎
-(26年-08月-12日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="58" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B32" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D32" s="21" t="inlineStr">
-        <is>
-          <t>C | 547呎 (2房)
-$893万
-$16,320/呎
-(26年-05月-18日)</t>
-        </is>
-      </c>
-      <c r="E32" s="21" t="inlineStr">
-        <is>
-          <t>D | 538呎 (2房)
-$876万
-$16,288/呎
-(25年-11月-28日)</t>
-        </is>
-      </c>
-      <c r="F32" s="21" t="inlineStr">
-        <is>
-          <t>E | 537呎 (2房)
-$861万
-$16,034/呎
-(26年-06月-05日)</t>
-        </is>
-      </c>
-      <c r="G32" s="21" t="inlineStr">
-        <is>
-          <t>F | 512呎 (2房)
-$819万
-$16,000/呎
-(26年-04月-14日)</t>
-        </is>
-      </c>
-      <c r="H32" s="21" t="inlineStr">
-        <is>
-          <t>G | 554呎 (2房)
-$992万
-$17,908/呎
-(25年-10月-02日)</t>
-        </is>
-      </c>
-      <c r="I32" s="21" t="inlineStr">
-        <is>
-          <t>H | 573呎 (2房)
-$1066万
-$18,604/呎
-(26年-07月-13日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="58" customHeight="1">
-      <c r="A33" s="19" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B33" s="20" t="inlineStr">
-        <is>
-          <t>A | 912呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C33" s="20" t="inlineStr">
-        <is>
-          <t>B | 899呎 (3房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="D33" s="21" t="inlineStr">
         <is>
           <t>C | 547呎 (2房)
@@ -43698,12 +43650,12 @@
 (25年-10月-02日)</t>
         </is>
       </c>
-      <c r="I33" s="22" t="inlineStr">
+      <c r="I33" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
+$1061万
+$18,511/呎
+(26年-08月-22日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -127,11 +127,6 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00004D00"/>
       <sz val="8"/>
@@ -213,7 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -278,13 +273,10 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7688,7 +7680,7 @@
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G111" s="3" t="inlineStr">
@@ -7696,31 +7688,39 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H111" s="5" t="n">
-        <v>10559000</v>
-      </c>
-      <c r="I111" s="5" t="n">
-        <v>20384</v>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="I111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
-        </is>
-      </c>
-      <c r="K111" s="5" t="n">
-        <v>8975150</v>
-      </c>
-      <c r="L111" s="5" t="n">
-        <v>17327</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N111" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8014,38 +8014,30 @@
       </c>
       <c r="F116" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I116" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="H116" s="5" t="n">
+        <v>10540000</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>19591</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K116" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L116" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K116" s="5" t="n">
+        <v>10540000</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>19591</v>
       </c>
       <c r="M116" s="3" t="inlineStr">
         <is>
@@ -8054,7 +8046,7 @@
       </c>
       <c r="N116" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -8534,38 +8526,30 @@
       </c>
       <c r="F124" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I124" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>10488000</v>
+      </c>
+      <c r="I124" s="5" t="n">
+        <v>19494</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K124" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L124" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K124" s="5" t="n">
+        <v>10488000</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>19494</v>
       </c>
       <c r="M124" s="3" t="inlineStr">
         <is>
@@ -8574,7 +8558,7 @@
       </c>
       <c r="N124" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -9054,38 +9038,30 @@
       </c>
       <c r="F132" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H132" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I132" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="H132" s="5" t="n">
+        <v>10435000</v>
+      </c>
+      <c r="I132" s="5" t="n">
+        <v>19396</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K132" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L132" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K132" s="5" t="n">
+        <v>10435000</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>19396</v>
       </c>
       <c r="M132" s="3" t="inlineStr">
         <is>
@@ -9094,7 +9070,7 @@
       </c>
       <c r="N132" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -24948,23 +24924,23 @@
       </c>
       <c r="F381" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G381" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H381" s="5" t="n">
-        <v>10480000</v>
+        <v>8908000</v>
       </c>
       <c r="I381" s="5" t="n">
-        <v>20469</v>
+        <v>17398</v>
       </c>
       <c r="J381" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K381" s="5" t="n">
@@ -24975,7 +24951,7 @@
       </c>
       <c r="M381" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N381" s="3" t="inlineStr">
@@ -25460,34 +25436,34 @@
       </c>
       <c r="F389" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G389" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H389" s="5" t="n">
-        <v>10438000</v>
+        <v>8872000</v>
       </c>
       <c r="I389" s="5" t="n">
-        <v>20387</v>
+        <v>17328</v>
       </c>
       <c r="J389" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K389" s="5" t="n">
-        <v>8872300</v>
+        <v>8872000</v>
       </c>
       <c r="L389" s="5" t="n">
-        <v>17329</v>
+        <v>17328</v>
       </c>
       <c r="M389" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N389" s="3" t="inlineStr">
@@ -28098,34 +28074,34 @@
       </c>
       <c r="F430" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G430" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="H430" s="5" t="n">
-        <v>10752000</v>
+        <v>9139000</v>
       </c>
       <c r="I430" s="5" t="n">
-        <v>20022</v>
+        <v>17019</v>
       </c>
       <c r="J430" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K430" s="5" t="n">
-        <v>9139200</v>
+        <v>9139000</v>
       </c>
       <c r="L430" s="5" t="n">
         <v>17019</v>
       </c>
       <c r="M430" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N430" s="3" t="inlineStr">
@@ -32064,38 +32040,30 @@
       </c>
       <c r="F491" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G491" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H491" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I491" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="H491" s="5" t="n">
+        <v>10767000</v>
+      </c>
+      <c r="I491" s="5" t="n">
+        <v>18791</v>
       </c>
       <c r="J491" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K491" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L491" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K491" s="5" t="n">
+        <v>10767000</v>
+      </c>
+      <c r="L491" s="5" t="n">
+        <v>18791</v>
       </c>
       <c r="M491" s="3" t="inlineStr">
         <is>
@@ -32104,7 +32072,7 @@
       </c>
       <c r="N491" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38826,17 +38794,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>205</t>
+          <t>208</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -39853,9 +39821,9 @@
       <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 518呎 (2房)
-$1056万
-$20,384/呎
-(已定价未售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr">
@@ -39945,12 +39913,12 @@
 (25年-10月-06日)</t>
         </is>
       </c>
-      <c r="H19" s="23" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
+$1054万
+$19,591/呎
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="I19" s="21" t="inlineStr">
@@ -40016,12 +39984,12 @@
 (25年-10月-02日)</t>
         </is>
       </c>
-      <c r="H20" s="23" t="inlineStr">
+      <c r="H20" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
+$1049万
+$19,494/呎
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -40047,7 +40015,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C21" s="24" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2377万
@@ -40087,12 +40055,12 @@
 (25年-09月-30日)</t>
         </is>
       </c>
-      <c r="H21" s="23" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>G | 538呎 (2房)
-招标单位
--
-(在售)</t>
+$1044万
+$19,396/呎
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="I21" s="21" t="inlineStr">
@@ -40118,7 +40086,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C22" s="24" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2348万
@@ -40189,7 +40157,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2318万
@@ -40260,7 +40228,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C24" s="24" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2288万
@@ -40331,7 +40299,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C25" s="24" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2259万
@@ -40402,7 +40370,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C26" s="24" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2230万
@@ -40473,7 +40441,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2215万
@@ -40544,7 +40512,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C28" s="24" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2173万
@@ -40615,7 +40583,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C29" s="24" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2145万
@@ -40686,7 +40654,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2126万
@@ -40757,7 +40725,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C31" s="24" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2107万
@@ -40828,7 +40796,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C32" s="24" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2096万
@@ -40899,7 +40867,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2086万
@@ -40970,7 +40938,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C34" s="24" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2076万
@@ -41041,7 +41009,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C35" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2065万
@@ -41112,7 +41080,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C36" s="24" t="inlineStr">
+      <c r="C36" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2060万
@@ -41183,7 +41151,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2045万
@@ -41254,7 +41222,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C38" s="24" t="inlineStr">
+      <c r="C38" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2035万
@@ -41325,7 +41293,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C39" s="24" t="inlineStr">
+      <c r="C39" s="23" t="inlineStr">
         <is>
           <t>B | 899呎 (3房)
 $2024万
@@ -41529,7 +41497,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -41539,7 +41507,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>185</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -41638,7 +41606,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="F5" s="23" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1158万
@@ -41646,7 +41614,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G5" s="23" t="inlineStr">
+      <c r="G5" s="22" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
 $1102万
@@ -41662,7 +41630,7 @@
 (26年-07月-13日)</t>
         </is>
       </c>
-      <c r="I5" s="23" t="inlineStr">
+      <c r="I5" s="22" t="inlineStr">
         <is>
           <t>H | 571呎 (2房)
 招标单位
@@ -41709,7 +41677,7 @@
 (26年-08月-05日)</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1150万
@@ -41717,7 +41685,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G6" s="22" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
 $1094万
@@ -41733,7 +41701,7 @@
 (26年-05月-14日)</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -41780,7 +41748,7 @@
 (26年-08月-23日)</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1142万
@@ -41788,7 +41756,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="22" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
 $1086万
@@ -41804,7 +41772,7 @@
 (26年-05月-05日)</t>
         </is>
       </c>
-      <c r="I7" s="23" t="inlineStr">
+      <c r="I7" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -41851,7 +41819,7 @@
 (26年-08月-18日)</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1137万
@@ -41859,7 +41827,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
 $1082万
@@ -41875,7 +41843,7 @@
 (26年-06月-04日)</t>
         </is>
       </c>
-      <c r="I8" s="23" t="inlineStr">
+      <c r="I8" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -41922,7 +41890,7 @@
 (26年-08月-08日)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1132万
@@ -41930,7 +41898,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
 $1078万
@@ -41946,7 +41914,7 @@
 (26年-06月-02日)</t>
         </is>
       </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -41993,7 +41961,7 @@
 (26年-07月-09日)</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1128万
@@ -42001,7 +41969,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
 $1073万
@@ -42135,7 +42103,7 @@
 (26年-05月-15日)</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1119万
@@ -42206,7 +42174,7 @@
 (25年-09月-30日)</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1115万
@@ -42277,7 +42245,7 @@
 (26年-05月-15日)</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1110万
@@ -42348,7 +42316,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1106万
@@ -42419,7 +42387,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1101万
@@ -42427,12 +42395,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$1048万
-$20,469/呎
-(在售)</t>
+$891万
+$17,398/呎
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="H16" s="21" t="inlineStr">
@@ -42443,7 +42411,7 @@
 (25年-10月-02日)</t>
         </is>
       </c>
-      <c r="I16" s="23" t="inlineStr">
+      <c r="I16" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42490,7 +42458,7 @@
 (26年-05月-12日)</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1097万
@@ -42498,12 +42466,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>F | 512呎 (2房)
-$1044万
-$20,387/呎
-(在售)</t>
+$887万
+$17,328/呎
+(26年-08月-24日)</t>
         </is>
       </c>
       <c r="H17" s="21" t="inlineStr">
@@ -42561,7 +42529,7 @@
 (26年-04月-09日)</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1093万
@@ -42585,7 +42553,7 @@
 (25年-10月-02日)</t>
         </is>
       </c>
-      <c r="I18" s="23" t="inlineStr">
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42632,7 +42600,7 @@
 (26年-05月-13日)</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1088万
@@ -42774,7 +42742,7 @@
 (26年-03月-09日)</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
 $1080万
@@ -42845,12 +42813,12 @@
 (26年-03月-13日)</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F22" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1075万
-$20,022/呎
-(在售)</t>
+$914万
+$17,019/呎
+(26年-08月-24日)</t>
         </is>
       </c>
       <c r="G22" s="21" t="inlineStr">
@@ -42869,7 +42837,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="I22" s="23" t="inlineStr">
+      <c r="I22" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -42940,7 +42908,7 @@
 (25年-10月-02日)</t>
         </is>
       </c>
-      <c r="I23" s="23" t="inlineStr">
+      <c r="I23" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43011,7 +42979,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="I24" s="23" t="inlineStr">
+      <c r="I24" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43082,7 +43050,7 @@
 (25年-09月-30日)</t>
         </is>
       </c>
-      <c r="I25" s="23" t="inlineStr">
+      <c r="I25" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43153,7 +43121,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="I26" s="23" t="inlineStr">
+      <c r="I26" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43224,7 +43192,7 @@
 (25年-10月-02日)</t>
         </is>
       </c>
-      <c r="I27" s="23" t="inlineStr">
+      <c r="I27" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43295,7 +43263,7 @@
 (25年-10月-03日)</t>
         </is>
       </c>
-      <c r="I28" s="23" t="inlineStr">
+      <c r="I28" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43366,7 +43334,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="I29" s="23" t="inlineStr">
+      <c r="I29" s="22" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
 招标单位
@@ -43437,12 +43405,12 @@
 (25年-10月-02日)</t>
         </is>
       </c>
-      <c r="I30" s="23" t="inlineStr">
+      <c r="I30" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
+$1077万
+$18,791/呎
+(26年-08月-24日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -22749,7 +22749,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -24792,38 +24792,30 @@
       </c>
       <c r="F379" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H379" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I379" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="H379" s="5" t="n">
+        <v>11684000</v>
+      </c>
+      <c r="I379" s="5" t="n">
+        <v>20391</v>
       </c>
       <c r="J379" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K379" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L379" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K379" s="5" t="n">
+        <v>11684000</v>
+      </c>
+      <c r="L379" s="5" t="n">
+        <v>20391</v>
       </c>
       <c r="M379" s="3" t="inlineStr">
         <is>
@@ -24832,7 +24824,7 @@
       </c>
       <c r="N379" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -25824,38 +25816,30 @@
       </c>
       <c r="F395" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G395" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H395" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I395" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H395" s="5" t="n">
+        <v>11499000</v>
+      </c>
+      <c r="I395" s="5" t="n">
+        <v>20068</v>
       </c>
       <c r="J395" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K395" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L395" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K395" s="5" t="n">
+        <v>11499000</v>
+      </c>
+      <c r="L395" s="5" t="n">
+        <v>20068</v>
       </c>
       <c r="M395" s="3" t="inlineStr">
         <is>
@@ -25864,7 +25848,7 @@
       </c>
       <c r="N395" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -41497,7 +41481,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -41507,7 +41491,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>185</t>
+          <t>187</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -42132,7 +42116,7 @@
           <t>H | 573呎 (2房)
 $1206万
 $21,051/呎
-(26年-08月-10日)</t>
+(26年-08月-27日)</t>
         </is>
       </c>
     </row>
@@ -42411,12 +42395,12 @@
 (25年-10月-02日)</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
+$1168万
+$20,391/呎
+(26年-08月-26日)</t>
         </is>
       </c>
     </row>
@@ -42553,12 +42537,12 @@
 (25年-10月-02日)</t>
         </is>
       </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
+$1150万
+$20,068/呎
+(26年-08月-27日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -2045,7 +2045,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -39026,7 +39026,7 @@
           <t>D | 518呎 (2房)
 $936万
 $18,068/呎
-(26年-08月-06日)</t>
+(26年-08月-28日)</t>
         </is>
       </c>
       <c r="F7" s="21" t="inlineStr">

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -27538,34 +27538,34 @@
       </c>
       <c r="F422" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G422" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H422" s="5" t="n">
-        <v>10795000</v>
+        <v>9176000</v>
       </c>
       <c r="I422" s="5" t="n">
-        <v>20102</v>
+        <v>17088</v>
       </c>
       <c r="J422" s="3" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K422" s="5" t="n">
-        <v>9175750</v>
+        <v>9176000</v>
       </c>
       <c r="L422" s="5" t="n">
-        <v>17087</v>
+        <v>17088</v>
       </c>
       <c r="M422" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N422" s="3" t="inlineStr">
@@ -27864,38 +27864,30 @@
       </c>
       <c r="F427" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G427" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H427" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I427" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="H427" s="5" t="n">
+        <v>11205000</v>
+      </c>
+      <c r="I427" s="5" t="n">
+        <v>19555</v>
       </c>
       <c r="J427" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K427" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L427" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K427" s="5" t="n">
+        <v>11205000</v>
+      </c>
+      <c r="L427" s="5" t="n">
+        <v>19555</v>
       </c>
       <c r="M427" s="3" t="inlineStr">
         <is>
@@ -27904,7 +27896,7 @@
       </c>
       <c r="N427" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -41481,7 +41473,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -41491,7 +41483,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>187</t>
+          <t>189</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -42726,12 +42718,12 @@
 (26年-03月-09日)</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="21" t="inlineStr">
         <is>
           <t>E | 537呎 (2房)
-$1080万
-$20,102/呎
-(在售)</t>
+$918万
+$17,088/呎
+(26年-08月-30日)</t>
         </is>
       </c>
       <c r="G21" s="21" t="inlineStr">
@@ -42821,12 +42813,12 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="I22" s="22" t="inlineStr">
+      <c r="I22" s="21" t="inlineStr">
         <is>
           <t>H | 573呎 (2房)
-招标单位
--
-(在售)</t>
+$1120万
+$19,555/呎
+(26年-08月-30日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -21453,7 +21453,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -22237,7 +22237,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -27031,7 +27031,7 @@
       </c>
       <c r="G414" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H414" s="5" t="n">
@@ -29615,7 +29615,7 @@
       </c>
       <c r="G454" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="H454" s="5" t="n">
@@ -32533,7 +32533,7 @@
       </c>
       <c r="G499" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H499" s="5" t="n">
@@ -38876,7 +38876,7 @@
           <t>D | 518呎 (2房)
 $949万
 $18,322/呎
-(26年-08月-07日)</t>
+(26年-09月-01日)</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
@@ -38971,7 +38971,7 @@
           <t>G | 538呎 (2房)
 $1177万
 $21,881/呎
-(26年-08月-12日)</t>
+(26年-08月-31日)</t>
         </is>
       </c>
       <c r="I6" s="21" t="inlineStr">
@@ -40320,7 +40320,7 @@
           <t>G | 538呎 (2房)
 $1023万
 $19,015/呎
-(26年-08月-09日)</t>
+(26年-09月-01日)</t>
         </is>
       </c>
       <c r="I25" s="21" t="inlineStr">
@@ -40391,7 +40391,7 @@
           <t>G | 538呎 (2房)
 $1018万
 $18,920/呎
-(26年-08月-08日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="I26" s="21" t="inlineStr">
@@ -41863,7 +41863,7 @@
           <t>D | 538呎 (2房)
 $980万
 $18,212/呎
-(26年-08月-08日)</t>
+(26年-09月-01日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -42037,7 +42037,7 @@
           <t>H | 573呎 (2房)
 $1221万
 $21,304/呎
-(26年-08月-08日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
     </row>
@@ -42652,7 +42652,7 @@
           <t>E | 537呎 (2房)
 $923万
 $17,190/呎
-(26年-08月-08日)</t>
+(26年-09月-01日)</t>
         </is>
       </c>
       <c r="G20" s="21" t="inlineStr">
@@ -43007,7 +43007,7 @@
           <t>E | 537呎 (2房)
 $903万
 $16,816/呎
-(26年-08月-10日)</t>
+(26年-09月-02日)</t>
         </is>
       </c>
       <c r="G25" s="21" t="inlineStr">
@@ -43457,7 +43457,7 @@
           <t>H | 573呎 (2房)
 $1071万
 $18,696/呎
-(26年-08月-12日)</t>
+(26年-08月-31日)</t>
         </is>
       </c>
     </row>

--- a/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
+++ b/港岛-柴湾-海德园第1期/海德园第1期_销控明细表.xlsx
@@ -22423,7 +22423,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -42013,7 +42013,7 @@
           <t>E | 537呎 (2房)
 $957万
 $17,819/呎
-(26年-08月-09日)</t>
+(26年-09月-03日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr">
